--- a/rss/2p-scanning.xlsx
+++ b/rss/2p-scanning.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MaxD2b\resiliosync\rnd\rigs\duke\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Max\Documents\codes\repos\NL-2p1\rss\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BBF3BCB-96E5-4367-AC98-4CD444189E08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBC5FCAA-15FE-4745-ABF6-86FC21B60A30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="15885" windowWidth="29040" windowHeight="15720" tabRatio="839" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="839" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="rigs" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5179" uniqueCount="2639">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5204" uniqueCount="2655">
   <si>
     <t>cat2</t>
   </si>
@@ -5627,9 +5627,6 @@
     <t>DIY Pike camera mount</t>
   </si>
   <si>
-    <t>pump filter&lt;</t>
-  </si>
-  <si>
     <t xml:space="preserve">Edmund #64-648, 875nm 25mm Diameter, OD 2 Shortpass Filter </t>
   </si>
   <si>
@@ -7965,6 +7962,57 @@
   </si>
   <si>
     <t>https://www.idex-hs.com/store/product-detail/ff01_842_sp_25/fl-009671</t>
+  </si>
+  <si>
+    <t>pump filter</t>
+  </si>
+  <si>
+    <t>NIR behavioral camera filters&lt;</t>
+  </si>
+  <si>
+    <t>https://www.idex-hs.com/store/product-detail/fbp01_825_22_12_5/fl-431335</t>
+  </si>
+  <si>
+    <t>FBP01-825/22-25</t>
+  </si>
+  <si>
+    <t>825/22 nm Nanopede# single-band bandpass</t>
+  </si>
+  <si>
+    <t>notice that this filter isn't available directly from the web site. The version available is 12.5mm in diameter, which works with a custom adapter, but isn't as good as it blocks light. To order, contact AVR optics rep directly.</t>
+  </si>
+  <si>
+    <t>SM05-Threaded Kinematic Mount for Thin Ø1/2" Optics, 8-32 Taps</t>
+  </si>
+  <si>
+    <t>https://www.thorlabs.com/thorproduct.cfm?partnumber=KM05T</t>
+  </si>
+  <si>
+    <t>KM05T</t>
+  </si>
+  <si>
+    <t>MECCANIXITY PMMA Side Glow Fiber Optic Cable 2mm 1M for LED Light Guide in Home, Hotel</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com/gp/product/B09J14WPS4</t>
+  </si>
+  <si>
+    <t>SM1 Lens Tube, 1.00" Thread Depth, One Retaining Ring Included</t>
+  </si>
+  <si>
+    <t>https://www.thorlabs.com/thorproduct.cfm?partnumber=SM1L10</t>
+  </si>
+  <si>
+    <t>bahavioral IR illumination&lt;</t>
+  </si>
+  <si>
+    <t>Modification of the Thorlabs M780L3 for fiber optics &lt;</t>
+  </si>
+  <si>
+    <t>Actual diameter is 2.08mm. Nothing special about this fiber. For other fibers and diameter modify the corresponding parameters in the Fusion 360 files.</t>
+  </si>
+  <si>
+    <t>It's supposed to be attached to one of the Thorlabs mounted LED's: https://www.thorlabs.com/newgrouppage9.cfm?objectgroup_id=2692</t>
   </si>
 </sst>
 </file>
@@ -8580,7 +8628,7 @@
     </row>
     <row r="2" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B2" s="1" t="s">
-        <v>2462</v>
+        <v>2461</v>
       </c>
       <c r="E2" s="41"/>
       <c r="G2" s="41"/>
@@ -8595,11 +8643,11 @@
     </row>
     <row r="3" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C3" s="41" t="s">
-        <v>2518</v>
+        <v>2517</v>
       </c>
       <c r="E3" s="41"/>
       <c r="F3" s="29" t="s">
-        <v>2517</v>
+        <v>2516</v>
       </c>
       <c r="G3" s="41"/>
       <c r="H3" s="41"/>
@@ -8613,11 +8661,11 @@
     </row>
     <row r="4" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C4" s="41" t="s">
-        <v>2460</v>
+        <v>2459</v>
       </c>
       <c r="E4" s="41"/>
       <c r="F4" s="41" t="s">
-        <v>2516</v>
+        <v>2515</v>
       </c>
       <c r="G4" s="41"/>
       <c r="H4" s="41"/>
@@ -8628,12 +8676,12 @@
       <c r="M4" s="41"/>
       <c r="N4" s="41"/>
       <c r="O4" s="41" t="s">
-        <v>2465</v>
+        <v>2464</v>
       </c>
     </row>
     <row r="5" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="C5" s="41" t="s">
-        <v>2461</v>
+        <v>2460</v>
       </c>
       <c r="E5" s="41"/>
       <c r="F5" s="29" t="str">
@@ -8653,10 +8701,10 @@
     <row r="6" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A6" s="42"/>
       <c r="B6" s="42" t="s">
+        <v>2462</v>
+      </c>
+      <c r="F6" t="s">
         <v>2463</v>
-      </c>
-      <c r="F6" t="s">
-        <v>2464</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.35">
@@ -8736,7 +8784,7 @@
     <row r="17" spans="3:15" x14ac:dyDescent="0.35">
       <c r="C17" s="21"/>
       <c r="D17" s="42" t="s">
-        <v>2552</v>
+        <v>2551</v>
       </c>
       <c r="E17" s="30"/>
       <c r="G17" s="21"/>
@@ -8959,14 +9007,14 @@
         <v>28</v>
       </c>
       <c r="F26" s="29" t="str">
-        <f>'beh im'!$C$68</f>
+        <f>'beh im'!$C$73</f>
         <v>Grasshopper3NIR, singlet lens focusing 1 &lt;</v>
       </c>
       <c r="G26">
         <v>1</v>
       </c>
       <c r="H26">
-        <f>'beh im'!$F$68</f>
+        <f>'beh im'!$F$73</f>
         <v>2091.6400000000003</v>
       </c>
       <c r="O26" s="2" t="s">
@@ -9237,7 +9285,7 @@
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.35">
       <c r="D49" s="42" t="s">
-        <v>2551</v>
+        <v>2550</v>
       </c>
       <c r="E49" s="6">
         <f>SUMPRODUCT(G51:G80,H51:H80)</f>
@@ -9700,7 +9748,7 @@
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.35">
       <c r="C74" t="s">
-        <v>2550</v>
+        <v>2549</v>
       </c>
       <c r="F74" t="str">
         <f>detection!$D$80</f>
@@ -9731,10 +9779,10 @@
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>2548</v>
+        <v>2547</v>
       </c>
       <c r="F76" t="s">
-        <v>2429</v>
+        <v>2428</v>
       </c>
       <c r="G76">
         <v>1</v>
@@ -9743,13 +9791,13 @@
         <v>2380</v>
       </c>
       <c r="I76" s="29" t="s">
+        <v>2429</v>
+      </c>
+      <c r="J76" t="s">
         <v>2430</v>
       </c>
-      <c r="J76" t="s">
+      <c r="K76" t="s">
         <v>2431</v>
-      </c>
-      <c r="K76" t="s">
-        <v>2432</v>
       </c>
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.35">
@@ -9817,14 +9865,14 @@
         <v>51</v>
       </c>
       <c r="F80" t="str">
-        <f>'beh im'!$C$68</f>
+        <f>'beh im'!$C$73</f>
         <v>Grasshopper3NIR, singlet lens focusing 1 &lt;</v>
       </c>
       <c r="G80">
         <v>1</v>
       </c>
       <c r="H80">
-        <f>'beh im'!$F$68</f>
+        <f>'beh im'!$F$73</f>
         <v>2091.6400000000003</v>
       </c>
     </row>
@@ -10769,7 +10817,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
-  <dimension ref="A1:L73"/>
+  <dimension ref="A1:L78"/>
   <sheetFormatPr defaultColWidth="8.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="10.453125" customWidth="1"/>
@@ -10905,16 +10953,16 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="C7" t="s">
-        <v>1859</v>
+        <v>2639</v>
       </c>
       <c r="F7" s="32">
-        <f>SUMPRODUCT(E8:E13,F8:F13)</f>
-        <v>2539</v>
+        <f>SUMPRODUCT(E8:E14,F8:F14)</f>
+        <v>2721</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="D8" t="s">
-        <v>1860</v>
+        <v>1859</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -10923,21 +10971,24 @@
         <v>125</v>
       </c>
       <c r="G8" s="29" t="s">
-        <v>1861</v>
+        <v>1860</v>
       </c>
       <c r="H8" t="s">
         <v>1309</v>
       </c>
       <c r="I8" t="s">
-        <v>1862</v>
+        <v>1861</v>
       </c>
       <c r="J8" t="s">
-        <v>2637</v>
+        <v>2636</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>2638</v>
+      </c>
       <c r="D9" t="s">
-        <v>2627</v>
+        <v>2626</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -10946,21 +10997,24 @@
         <v>260</v>
       </c>
       <c r="G9" s="29" t="s">
-        <v>2625</v>
+        <v>2624</v>
       </c>
       <c r="H9" t="s">
         <v>1309</v>
       </c>
       <c r="I9" t="s">
-        <v>2626</v>
+        <v>2625</v>
       </c>
       <c r="J9" t="s">
-        <v>2636</v>
+        <v>2635</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>2638</v>
+      </c>
       <c r="D10" t="s">
-        <v>2628</v>
+        <v>2627</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -10969,7 +11023,7 @@
         <v>435</v>
       </c>
       <c r="G10" s="29" t="s">
-        <v>2624</v>
+        <v>2623</v>
       </c>
       <c r="H10" t="s">
         <v>682</v>
@@ -10978,12 +11032,15 @@
         <v>1438</v>
       </c>
       <c r="J10" t="s">
-        <v>2633</v>
+        <v>2632</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>2638</v>
+      </c>
       <c r="D11" t="s">
-        <v>2629</v>
+        <v>2628</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -10992,21 +11049,24 @@
         <v>435</v>
       </c>
       <c r="G11" s="29" t="s">
-        <v>2623</v>
+        <v>2622</v>
       </c>
       <c r="H11" t="s">
         <v>682</v>
       </c>
       <c r="I11" t="s">
-        <v>2630</v>
+        <v>2629</v>
       </c>
       <c r="J11" t="s">
-        <v>2634</v>
+        <v>2633</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>2638</v>
+      </c>
       <c r="D12" t="s">
-        <v>2632</v>
+        <v>2631</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -11015,7 +11075,7 @@
         <v>1200</v>
       </c>
       <c r="G12" s="29" t="s">
-        <v>2631</v>
+        <v>2630</v>
       </c>
       <c r="H12" t="s">
         <v>682</v>
@@ -11024,85 +11084,85 @@
         <v>1441</v>
       </c>
       <c r="J12" t="s">
-        <v>2635</v>
+        <v>2634</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="C13" t="s">
-        <v>17</v>
-      </c>
       <c r="D13" t="s">
-        <v>1863</v>
+        <v>2642</v>
       </c>
       <c r="E13">
         <v>1</v>
       </c>
       <c r="F13" s="32">
-        <v>84</v>
+        <v>182</v>
       </c>
       <c r="G13" s="29" t="s">
-        <v>1864</v>
+        <v>2640</v>
       </c>
       <c r="H13" t="s">
-        <v>67</v>
+        <v>682</v>
       </c>
       <c r="I13" t="s">
-        <v>1865</v>
+        <v>2641</v>
       </c>
       <c r="J13" t="s">
-        <v>9</v>
+        <v>2643</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="C14" t="s">
-        <v>1866</v>
+        <v>17</v>
+      </c>
+      <c r="D14" t="s">
+        <v>1862</v>
+      </c>
+      <c r="E14">
+        <v>1</v>
       </c>
       <c r="F14" s="32">
-        <f>SUMPRODUCT(E15:E18,F15:F18)</f>
+        <v>84</v>
+      </c>
+      <c r="G14" s="29" t="s">
+        <v>1863</v>
+      </c>
+      <c r="H14" t="s">
+        <v>67</v>
+      </c>
+      <c r="I14" t="s">
+        <v>1864</v>
+      </c>
+      <c r="J14" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="C15" t="s">
+        <v>1865</v>
+      </c>
+      <c r="F15" s="32">
+        <f>SUMPRODUCT(E16:E19,F16:F19)</f>
         <v>183.64</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="D15" t="s">
-        <v>1867</v>
-      </c>
-      <c r="E15">
-        <v>1</v>
-      </c>
-      <c r="F15" s="32">
-        <v>149</v>
-      </c>
-      <c r="G15" s="29" t="s">
-        <v>1868</v>
-      </c>
-      <c r="H15" t="s">
-        <v>1309</v>
-      </c>
-      <c r="I15" t="s">
-        <v>1869</v>
-      </c>
-      <c r="J15" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="D16" t="s">
-        <v>1870</v>
+        <v>1866</v>
       </c>
       <c r="E16">
         <v>1</v>
       </c>
       <c r="F16" s="32">
-        <v>19.690000000000001</v>
+        <v>149</v>
       </c>
       <c r="G16" s="29" t="s">
-        <v>1871</v>
+        <v>1867</v>
       </c>
       <c r="H16" t="s">
-        <v>67</v>
+        <v>1309</v>
       </c>
       <c r="I16" t="s">
-        <v>1872</v>
+        <v>1868</v>
       </c>
       <c r="J16" t="s">
         <v>9</v>
@@ -11110,48 +11170,45 @@
     </row>
     <row r="17" spans="2:12" x14ac:dyDescent="0.35">
       <c r="D17" t="s">
-        <v>185</v>
+        <v>1869</v>
       </c>
       <c r="E17">
         <v>1</v>
       </c>
       <c r="F17" s="32">
-        <v>9.76</v>
+        <v>19.690000000000001</v>
       </c>
       <c r="G17" s="29" t="s">
-        <v>1873</v>
+        <v>1870</v>
       </c>
       <c r="H17" t="s">
         <v>67</v>
       </c>
       <c r="I17" t="s">
-        <v>187</v>
+        <v>1871</v>
       </c>
       <c r="J17" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="C18" t="s">
-        <v>17</v>
-      </c>
       <c r="D18" t="s">
-        <v>1874</v>
+        <v>185</v>
       </c>
       <c r="E18">
         <v>1</v>
       </c>
       <c r="F18" s="32">
-        <v>5.19</v>
+        <v>9.76</v>
       </c>
       <c r="G18" s="29" t="s">
-        <v>1875</v>
+        <v>1872</v>
       </c>
       <c r="H18" t="s">
         <v>67</v>
       </c>
       <c r="I18" t="s">
-        <v>162</v>
+        <v>187</v>
       </c>
       <c r="J18" t="s">
         <v>9</v>
@@ -11159,110 +11216,143 @@
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.35">
       <c r="C19" t="s">
-        <v>1683</v>
+        <v>17</v>
+      </c>
+      <c r="D19" t="s">
+        <v>1873</v>
+      </c>
+      <c r="E19">
+        <v>1</v>
       </c>
       <c r="F19" s="32">
-        <f>SUMPRODUCT(E21:E22,F21:F22)</f>
-        <v>0</v>
-      </c>
-      <c r="G19" s="29"/>
+        <v>5.19</v>
+      </c>
+      <c r="G19" s="29" t="s">
+        <v>1874</v>
+      </c>
+      <c r="H19" t="s">
+        <v>67</v>
+      </c>
+      <c r="I19" t="s">
+        <v>162</v>
+      </c>
+      <c r="J19" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="20" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="C20" t="s">
+        <v>2651</v>
+      </c>
+      <c r="F20" s="32">
+        <f>SUMPRODUCT(E22:E23,F22:F23)</f>
+        <v>0</v>
+      </c>
+      <c r="G20" s="29"/>
     </row>
     <row r="21" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="D21" t="s">
-        <v>1876</v>
+      <c r="D21" t="str">
+        <f>'parts-vendors'!$E$214</f>
+        <v>M780L3 - 780 nm, 200 mW (Min) Mounted LED, 800 mA </v>
       </c>
       <c r="E21">
         <v>1</v>
       </c>
-      <c r="G21" s="29"/>
+      <c r="F21" s="32">
+        <f>'parts-vendors'!G214</f>
+        <v>220.32</v>
+      </c>
+      <c r="G21" s="30" t="str">
+        <f>'parts-vendors'!H214</f>
+        <v xml:space="preserve">https://www.thorlabs.com/thorproduct.cfm?partnumber=M780L3 </v>
+      </c>
+      <c r="H21" s="30" t="str">
+        <f>'parts-vendors'!I214</f>
+        <v>thorlabs</v>
+      </c>
+      <c r="I21" s="29" t="s">
+        <v>678</v>
+      </c>
+      <c r="J21" s="30"/>
+      <c r="K21" s="30">
+        <f>'parts-vendors'!L214</f>
+        <v>0</v>
+      </c>
+      <c r="L21" s="30">
+        <f>'parts-vendors'!M214</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="22" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="C22" t="s">
-        <v>17</v>
-      </c>
       <c r="D22" t="s">
-        <v>1877</v>
+        <v>1875</v>
       </c>
       <c r="E22">
         <v>1</v>
       </c>
+      <c r="G22" s="29"/>
     </row>
     <row r="23" spans="2:12" x14ac:dyDescent="0.35">
       <c r="C23" t="s">
-        <v>1878</v>
-      </c>
-      <c r="F23" s="32">
-        <f>SUMPRODUCT(E24:E26,F24:F26)</f>
+        <v>17</v>
+      </c>
+      <c r="D23" t="s">
+        <v>1876</v>
+      </c>
+      <c r="E23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="C24" t="s">
+        <v>1877</v>
+      </c>
+      <c r="F24" s="32">
+        <f>SUMPRODUCT(E25:E27,F25:F27)</f>
         <v>18.09</v>
-      </c>
-    </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="D24" t="s">
-        <v>1874</v>
-      </c>
-      <c r="E24">
-        <v>1</v>
-      </c>
-      <c r="F24" s="32">
-        <v>5.19</v>
-      </c>
-      <c r="G24" s="29" t="s">
-        <v>1875</v>
-      </c>
-      <c r="H24" t="s">
-        <v>67</v>
-      </c>
-      <c r="I24" t="s">
-        <v>162</v>
-      </c>
-      <c r="J24" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.35">
       <c r="D25" t="s">
-        <v>1879</v>
+        <v>1873</v>
       </c>
       <c r="E25">
         <v>1</v>
       </c>
       <c r="F25" s="32">
-        <v>7.7</v>
+        <v>5.19</v>
       </c>
       <c r="G25" s="29" t="s">
-        <v>1880</v>
+        <v>1874</v>
       </c>
       <c r="H25" t="s">
         <v>67</v>
       </c>
       <c r="I25" t="s">
-        <v>136</v>
+        <v>162</v>
       </c>
       <c r="J25" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="C26" t="s">
-        <v>17</v>
-      </c>
       <c r="D26" t="s">
-        <v>101</v>
+        <v>1878</v>
       </c>
       <c r="E26">
         <v>1</v>
       </c>
       <c r="F26" s="32">
-        <v>5.2</v>
+        <v>7.7</v>
       </c>
       <c r="G26" s="29" t="s">
-        <v>1881</v>
+        <v>1879</v>
       </c>
       <c r="H26" t="s">
         <v>67</v>
       </c>
       <c r="I26" t="s">
-        <v>103</v>
+        <v>136</v>
       </c>
       <c r="J26" t="s">
         <v>9</v>
@@ -11270,101 +11360,104 @@
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.35">
       <c r="C27" t="s">
-        <v>1882</v>
+        <v>17</v>
+      </c>
+      <c r="D27" t="s">
+        <v>101</v>
+      </c>
+      <c r="E27">
+        <v>1</v>
       </c>
       <c r="F27" s="32">
-        <f>SUMPRODUCT(E28:E35,F28:F35)</f>
+        <v>5.2</v>
+      </c>
+      <c r="G27" s="29" t="s">
+        <v>1880</v>
+      </c>
+      <c r="H27" t="s">
+        <v>67</v>
+      </c>
+      <c r="I27" t="s">
+        <v>103</v>
+      </c>
+      <c r="J27" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="28" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="C28" t="s">
+        <v>1881</v>
+      </c>
+      <c r="F28" s="32">
+        <f>SUMPRODUCT(E29:E36,F29:F36)</f>
         <v>1389.33</v>
       </c>
     </row>
-    <row r="28" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B28" s="34">
+    <row r="29" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B29" s="34">
         <v>43446</v>
       </c>
-      <c r="D28" t="s">
+      <c r="D29" t="s">
         <v>1343</v>
       </c>
-      <c r="E28">
-        <v>1</v>
-      </c>
-      <c r="F28" s="32">
+      <c r="E29">
+        <v>1</v>
+      </c>
+      <c r="F29" s="32">
         <v>1295</v>
       </c>
-      <c r="G28" s="29" t="s">
+      <c r="G29" s="29" t="s">
         <v>1344</v>
-      </c>
-      <c r="H28" t="s">
-        <v>1345</v>
-      </c>
-      <c r="I28" t="s">
-        <v>1346</v>
-      </c>
-    </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="D29" t="s">
-        <v>1349</v>
-      </c>
-      <c r="E29">
-        <v>1</v>
-      </c>
-      <c r="F29" s="6">
-        <v>15</v>
-      </c>
-      <c r="G29" s="29" t="s">
-        <v>1350</v>
       </c>
       <c r="H29" t="s">
         <v>1345</v>
       </c>
-      <c r="I29" s="14" t="s">
-        <v>1351</v>
-      </c>
-      <c r="J29" t="s">
-        <v>1352</v>
-      </c>
-      <c r="L29" s="1"/>
+      <c r="I29" t="s">
+        <v>1346</v>
+      </c>
     </row>
     <row r="30" spans="2:12" x14ac:dyDescent="0.35">
       <c r="D30" t="s">
-        <v>348</v>
+        <v>1349</v>
       </c>
       <c r="E30">
         <v>1</v>
       </c>
-      <c r="F30" s="32">
-        <v>19.989999999999998</v>
+      <c r="F30" s="6">
+        <v>15</v>
       </c>
       <c r="G30" s="29" t="s">
-        <v>1883</v>
+        <v>1350</v>
       </c>
       <c r="H30" t="s">
-        <v>67</v>
-      </c>
-      <c r="I30" t="s">
-        <v>350</v>
+        <v>1345</v>
+      </c>
+      <c r="I30" s="14" t="s">
+        <v>1351</v>
       </c>
       <c r="J30" t="s">
-        <v>9</v>
-      </c>
+        <v>1352</v>
+      </c>
+      <c r="L30" s="1"/>
     </row>
     <row r="31" spans="2:12" x14ac:dyDescent="0.35">
       <c r="D31" t="s">
-        <v>321</v>
+        <v>348</v>
       </c>
       <c r="E31">
         <v>1</v>
       </c>
       <c r="F31" s="32">
-        <v>19.79</v>
+        <v>19.989999999999998</v>
       </c>
       <c r="G31" s="29" t="s">
-        <v>1884</v>
+        <v>1882</v>
       </c>
       <c r="H31" t="s">
         <v>67</v>
       </c>
       <c r="I31" t="s">
-        <v>323</v>
+        <v>350</v>
       </c>
       <c r="J31" t="s">
         <v>9</v>
@@ -11372,672 +11465,767 @@
     </row>
     <row r="32" spans="2:12" x14ac:dyDescent="0.35">
       <c r="D32" t="s">
-        <v>1885</v>
+        <v>321</v>
       </c>
       <c r="E32">
         <v>1</v>
       </c>
       <c r="F32" s="32">
-        <v>22</v>
+        <v>19.79</v>
       </c>
       <c r="G32" s="29" t="s">
-        <v>1886</v>
+        <v>1883</v>
       </c>
       <c r="H32" t="s">
         <v>67</v>
       </c>
       <c r="I32" t="s">
-        <v>1887</v>
+        <v>323</v>
+      </c>
+      <c r="J32" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="33" spans="3:9" x14ac:dyDescent="0.35">
       <c r="D33" t="s">
-        <v>1888</v>
+        <v>1884</v>
       </c>
       <c r="E33">
         <v>1</v>
+      </c>
+      <c r="F33" s="32">
+        <v>22</v>
+      </c>
+      <c r="G33" s="29" t="s">
+        <v>1885</v>
+      </c>
+      <c r="H33" t="s">
+        <v>67</v>
+      </c>
+      <c r="I33" t="s">
+        <v>1886</v>
       </c>
     </row>
     <row r="34" spans="3:9" x14ac:dyDescent="0.35">
       <c r="D34" t="s">
-        <v>1889</v>
+        <v>1887</v>
       </c>
       <c r="E34">
         <v>1</v>
       </c>
     </row>
     <row r="35" spans="3:9" x14ac:dyDescent="0.35">
-      <c r="C35" t="s">
-        <v>17</v>
-      </c>
       <c r="D35" t="s">
-        <v>1890</v>
+        <v>1888</v>
       </c>
       <c r="E35">
-        <v>3</v>
-      </c>
-      <c r="F35" s="30">
-        <v>5.85</v>
-      </c>
-      <c r="G35" s="29" t="s">
-        <v>1413</v>
-      </c>
-      <c r="H35" t="s">
-        <v>67</v>
-      </c>
-      <c r="I35" t="s">
-        <v>382</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C36" t="s">
-        <v>1891</v>
-      </c>
-      <c r="F36" s="32">
-        <f>SUMPRODUCT(E37:E42,F37:F42)</f>
+        <v>17</v>
+      </c>
+      <c r="D36" t="s">
+        <v>1889</v>
+      </c>
+      <c r="E36">
+        <v>3</v>
+      </c>
+      <c r="F36" s="30">
+        <v>5.85</v>
+      </c>
+      <c r="G36" s="29" t="s">
+        <v>1413</v>
+      </c>
+      <c r="H36" t="s">
+        <v>67</v>
+      </c>
+      <c r="I36" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="37" spans="3:9" x14ac:dyDescent="0.35">
+      <c r="C37" t="s">
+        <v>1890</v>
+      </c>
+      <c r="F37" s="32">
+        <f>SUMPRODUCT(E38:E43,F38:F43)</f>
         <v>231.89999999999998</v>
-      </c>
-    </row>
-    <row r="37" spans="3:9" x14ac:dyDescent="0.35">
-      <c r="D37" t="s">
-        <v>297</v>
-      </c>
-      <c r="E37">
-        <v>1</v>
-      </c>
-      <c r="F37" s="32">
-        <v>40</v>
-      </c>
-      <c r="G37" s="29" t="s">
-        <v>1490</v>
-      </c>
-      <c r="H37" t="s">
-        <v>67</v>
-      </c>
-      <c r="I37" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="38" spans="3:9" x14ac:dyDescent="0.35">
       <c r="D38" t="s">
-        <v>1892</v>
+        <v>297</v>
       </c>
       <c r="E38">
-        <v>2</v>
-      </c>
-      <c r="F38" s="30">
-        <v>38.76</v>
+        <v>1</v>
+      </c>
+      <c r="F38" s="32">
+        <v>40</v>
       </c>
       <c r="G38" s="29" t="s">
-        <v>1521</v>
+        <v>1490</v>
       </c>
       <c r="H38" t="s">
         <v>67</v>
       </c>
       <c r="I38" t="s">
-        <v>331</v>
+        <v>299</v>
       </c>
     </row>
     <row r="39" spans="3:9" x14ac:dyDescent="0.35">
       <c r="D39" t="s">
-        <v>1893</v>
+        <v>1891</v>
       </c>
       <c r="E39">
-        <v>1</v>
-      </c>
-      <c r="F39" s="32">
-        <v>39.270000000000003</v>
+        <v>2</v>
+      </c>
+      <c r="F39" s="30">
+        <v>38.76</v>
       </c>
       <c r="G39" s="29" t="s">
-        <v>1894</v>
+        <v>1521</v>
       </c>
       <c r="H39" t="s">
         <v>67</v>
       </c>
       <c r="I39" t="s">
-        <v>1895</v>
+        <v>331</v>
       </c>
     </row>
     <row r="40" spans="3:9" x14ac:dyDescent="0.35">
       <c r="D40" t="s">
-        <v>1896</v>
+        <v>1892</v>
       </c>
       <c r="E40">
         <v>1</v>
       </c>
       <c r="F40" s="32">
-        <v>43.61</v>
+        <v>39.270000000000003</v>
       </c>
       <c r="G40" s="29" t="s">
-        <v>1897</v>
+        <v>1893</v>
       </c>
       <c r="H40" t="s">
         <v>67</v>
       </c>
       <c r="I40" t="s">
-        <v>1898</v>
+        <v>1894</v>
       </c>
     </row>
     <row r="41" spans="3:9" x14ac:dyDescent="0.35">
       <c r="D41" t="s">
+        <v>1895</v>
+      </c>
+      <c r="E41">
+        <v>1</v>
+      </c>
+      <c r="F41" s="32">
+        <v>43.61</v>
+      </c>
+      <c r="G41" s="29" t="s">
+        <v>1896</v>
+      </c>
+      <c r="H41" t="s">
+        <v>67</v>
+      </c>
+      <c r="I41" t="s">
+        <v>1897</v>
+      </c>
+    </row>
+    <row r="42" spans="3:9" x14ac:dyDescent="0.35">
+      <c r="D42" t="s">
         <v>404</v>
-      </c>
-      <c r="E41">
-        <v>2</v>
-      </c>
-      <c r="F41" s="30">
-        <v>7.1</v>
-      </c>
-      <c r="G41" s="29" t="s">
-        <v>1899</v>
-      </c>
-      <c r="H41" t="s">
-        <v>67</v>
-      </c>
-      <c r="I41" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="42" spans="3:9" x14ac:dyDescent="0.35">
-      <c r="C42" t="s">
-        <v>17</v>
-      </c>
-      <c r="D42" t="s">
-        <v>246</v>
       </c>
       <c r="E42">
         <v>2</v>
       </c>
       <c r="F42" s="30">
-        <v>8.65</v>
+        <v>7.1</v>
       </c>
       <c r="G42" s="29" t="s">
-        <v>1900</v>
+        <v>1898</v>
       </c>
       <c r="H42" t="s">
         <v>67</v>
       </c>
       <c r="I42" t="s">
-        <v>248</v>
+        <v>406</v>
       </c>
     </row>
     <row r="43" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C43" t="s">
+        <v>17</v>
+      </c>
+      <c r="D43" t="s">
+        <v>246</v>
+      </c>
+      <c r="E43">
+        <v>2</v>
+      </c>
+      <c r="F43" s="30">
+        <v>8.65</v>
+      </c>
+      <c r="G43" s="29" t="s">
+        <v>1899</v>
+      </c>
+      <c r="H43" t="s">
+        <v>67</v>
+      </c>
+      <c r="I43" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="44" spans="3:9" x14ac:dyDescent="0.35">
+      <c r="C44" t="s">
+        <v>1900</v>
+      </c>
+      <c r="F44" s="32">
+        <f>SUMPRODUCT(E45:E46,F45:F46)</f>
+        <v>86.7</v>
+      </c>
+      <c r="G44" s="29"/>
+    </row>
+    <row r="45" spans="3:9" x14ac:dyDescent="0.35">
+      <c r="D45" t="s">
         <v>1901</v>
       </c>
-      <c r="F43" s="32">
-        <f>SUMPRODUCT(E44:E45,F44:F45)</f>
-        <v>86.7</v>
-      </c>
-      <c r="G43" s="29"/>
-    </row>
-    <row r="44" spans="3:9" x14ac:dyDescent="0.35">
-      <c r="D44" t="s">
+      <c r="E45">
+        <v>1</v>
+      </c>
+      <c r="F45" s="30">
+        <v>26</v>
+      </c>
+      <c r="G45" s="29" t="s">
         <v>1902</v>
       </c>
-      <c r="E44">
-        <v>1</v>
-      </c>
-      <c r="F44" s="30">
-        <v>26</v>
-      </c>
-      <c r="G44" s="29" t="s">
+      <c r="H45" t="s">
+        <v>67</v>
+      </c>
+      <c r="I45" t="s">
         <v>1903</v>
-      </c>
-      <c r="H44" t="s">
-        <v>67</v>
-      </c>
-      <c r="I44" t="s">
-        <v>1904</v>
-      </c>
-    </row>
-    <row r="45" spans="3:9" x14ac:dyDescent="0.35">
-      <c r="C45" t="s">
-        <v>17</v>
-      </c>
-      <c r="D45" t="s">
-        <v>332</v>
-      </c>
-      <c r="E45">
-        <v>2</v>
-      </c>
-      <c r="F45" s="32">
-        <v>30.35</v>
-      </c>
-      <c r="G45" s="29" t="s">
-        <v>333</v>
-      </c>
-      <c r="H45" t="s">
-        <v>67</v>
-      </c>
-      <c r="I45" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="46" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C46" t="s">
-        <v>1905</v>
+        <v>17</v>
+      </c>
+      <c r="D46" t="s">
+        <v>332</v>
+      </c>
+      <c r="E46">
+        <v>2</v>
       </c>
       <c r="F46" s="32">
-        <f>SUMPRODUCT(E47:E50,F47:F50)</f>
+        <v>30.35</v>
+      </c>
+      <c r="G46" s="29" t="s">
+        <v>333</v>
+      </c>
+      <c r="H46" t="s">
+        <v>67</v>
+      </c>
+      <c r="I46" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="47" spans="3:9" x14ac:dyDescent="0.35">
+      <c r="C47" t="s">
+        <v>1904</v>
+      </c>
+      <c r="F47" s="32">
+        <f>SUMPRODUCT(E48:E51,F48:F51)</f>
         <v>56.44</v>
-      </c>
-    </row>
-    <row r="47" spans="3:9" x14ac:dyDescent="0.35">
-      <c r="D47" t="s">
-        <v>1874</v>
-      </c>
-      <c r="E47">
-        <v>2</v>
-      </c>
-      <c r="F47" s="30">
-        <v>5.19</v>
-      </c>
-      <c r="G47" s="29" t="s">
-        <v>1875</v>
-      </c>
-      <c r="H47" t="s">
-        <v>67</v>
-      </c>
-      <c r="I47" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="48" spans="3:9" x14ac:dyDescent="0.35">
       <c r="D48" t="s">
-        <v>181</v>
+        <v>1873</v>
       </c>
       <c r="E48">
         <v>2</v>
       </c>
       <c r="F48" s="30">
+        <v>5.19</v>
+      </c>
+      <c r="G48" s="29" t="s">
+        <v>1874</v>
+      </c>
+      <c r="H48" t="s">
+        <v>67</v>
+      </c>
+      <c r="I48" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="49" spans="3:10" x14ac:dyDescent="0.35">
+      <c r="D49" t="s">
+        <v>181</v>
+      </c>
+      <c r="E49">
+        <v>2</v>
+      </c>
+      <c r="F49" s="30">
         <v>10.81</v>
       </c>
-      <c r="G48" s="29" t="s">
+      <c r="G49" s="29" t="s">
         <v>1688</v>
       </c>
-      <c r="H48" t="s">
-        <v>67</v>
-      </c>
-      <c r="I48" t="s">
+      <c r="H49" t="s">
+        <v>67</v>
+      </c>
+      <c r="I49" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="D49" t="s">
+    <row r="50" spans="3:10" x14ac:dyDescent="0.35">
+      <c r="D50" t="s">
+        <v>1905</v>
+      </c>
+      <c r="E50">
+        <v>1</v>
+      </c>
+      <c r="F50" s="30">
+        <v>4.97</v>
+      </c>
+      <c r="G50" s="29" t="s">
         <v>1906</v>
       </c>
-      <c r="E49">
-        <v>1</v>
-      </c>
-      <c r="F49" s="30">
-        <v>4.97</v>
-      </c>
-      <c r="G49" s="29" t="s">
+      <c r="H50" t="s">
+        <v>67</v>
+      </c>
+      <c r="I50" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="51" spans="3:10" x14ac:dyDescent="0.35">
+      <c r="C51" t="s">
+        <v>17</v>
+      </c>
+      <c r="D51" t="s">
         <v>1907</v>
       </c>
-      <c r="H49" t="s">
-        <v>67</v>
-      </c>
-      <c r="I49" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="C50" t="s">
+      <c r="E51">
+        <v>1</v>
+      </c>
+      <c r="F51" s="32">
+        <v>19.47</v>
+      </c>
+      <c r="G51" s="29" t="s">
+        <v>1908</v>
+      </c>
+      <c r="H51" t="s">
+        <v>67</v>
+      </c>
+      <c r="I51" t="s">
+        <v>1909</v>
+      </c>
+    </row>
+    <row r="52" spans="3:10" x14ac:dyDescent="0.35">
+      <c r="C52" t="s">
+        <v>1910</v>
+      </c>
+      <c r="F52" s="32">
+        <f>SUMPRODUCT(E53:E56,F53:F56)</f>
+        <v>383.71000000000004</v>
+      </c>
+    </row>
+    <row r="53" spans="3:10" x14ac:dyDescent="0.35">
+      <c r="D53" t="s">
+        <v>1911</v>
+      </c>
+      <c r="E53">
+        <v>1</v>
+      </c>
+      <c r="F53" s="32">
+        <v>165</v>
+      </c>
+      <c r="G53" s="29" t="s">
+        <v>1912</v>
+      </c>
+      <c r="H53" t="s">
+        <v>1309</v>
+      </c>
+      <c r="I53" t="s">
+        <v>1913</v>
+      </c>
+    </row>
+    <row r="54" spans="3:10" x14ac:dyDescent="0.35">
+      <c r="D54" s="29" t="str">
+        <f>$C$47</f>
+        <v>45 degree filter holder arm &lt;</v>
+      </c>
+      <c r="E54">
+        <v>2</v>
+      </c>
+      <c r="F54" s="32">
+        <f>$F$47</f>
+        <v>56.44</v>
+      </c>
+    </row>
+    <row r="55" spans="3:10" x14ac:dyDescent="0.35">
+      <c r="D55" t="s">
+        <v>1914</v>
+      </c>
+      <c r="E55">
+        <v>1</v>
+      </c>
+      <c r="F55" s="32">
+        <v>75.48</v>
+      </c>
+      <c r="G55" s="29" t="s">
+        <v>1915</v>
+      </c>
+      <c r="H55" t="s">
+        <v>67</v>
+      </c>
+      <c r="I55" t="s">
+        <v>1916</v>
+      </c>
+    </row>
+    <row r="56" spans="3:10" x14ac:dyDescent="0.35">
+      <c r="C56" t="s">
         <v>17</v>
       </c>
-      <c r="D50" t="s">
-        <v>1908</v>
-      </c>
-      <c r="E50">
-        <v>1</v>
-      </c>
-      <c r="F50" s="32">
-        <v>19.47</v>
-      </c>
-      <c r="G50" s="29" t="s">
-        <v>1909</v>
-      </c>
-      <c r="H50" t="s">
-        <v>67</v>
-      </c>
-      <c r="I50" t="s">
-        <v>1910</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="C51" t="s">
-        <v>1911</v>
-      </c>
-      <c r="F51" s="32">
-        <f>SUMPRODUCT(E52:E55,F52:F55)</f>
-        <v>383.71000000000004</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="D52" t="s">
-        <v>1912</v>
-      </c>
-      <c r="E52">
-        <v>1</v>
-      </c>
-      <c r="F52" s="32">
-        <v>165</v>
-      </c>
-      <c r="G52" s="29" t="s">
-        <v>1913</v>
-      </c>
-      <c r="H52" t="s">
-        <v>1309</v>
-      </c>
-      <c r="I52" t="s">
-        <v>1914</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="D53" s="29" t="str">
-        <f>$C$46</f>
-        <v>45 degree filter holder arm &lt;</v>
-      </c>
-      <c r="E53">
-        <v>2</v>
-      </c>
-      <c r="F53" s="32">
-        <f>$F$46</f>
-        <v>56.44</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="D54" t="s">
-        <v>1915</v>
-      </c>
-      <c r="E54">
-        <v>1</v>
-      </c>
-      <c r="F54" s="32">
-        <v>75.48</v>
-      </c>
-      <c r="G54" s="29" t="s">
-        <v>1916</v>
-      </c>
-      <c r="H54" t="s">
-        <v>67</v>
-      </c>
-      <c r="I54" t="s">
+      <c r="D56" t="s">
+        <v>332</v>
+      </c>
+      <c r="E56">
+        <v>1</v>
+      </c>
+      <c r="F56" s="32">
+        <v>30.35</v>
+      </c>
+      <c r="G56" s="29" t="s">
+        <v>333</v>
+      </c>
+      <c r="H56" t="s">
+        <v>67</v>
+      </c>
+      <c r="I56" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="57" spans="3:10" x14ac:dyDescent="0.35">
+      <c r="C57" t="s">
+        <v>1682</v>
+      </c>
+    </row>
+    <row r="58" spans="3:10" x14ac:dyDescent="0.35">
+      <c r="D58" t="s">
         <v>1917</v>
       </c>
-    </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="C55" t="s">
+      <c r="I58" t="s">
+        <v>1918</v>
+      </c>
+    </row>
+    <row r="59" spans="3:10" x14ac:dyDescent="0.35">
+      <c r="D59" t="s">
+        <v>1919</v>
+      </c>
+      <c r="E59">
+        <v>1</v>
+      </c>
+      <c r="F59" s="32">
+        <v>27.29</v>
+      </c>
+      <c r="G59" s="29" t="s">
+        <v>1920</v>
+      </c>
+      <c r="H59" t="s">
+        <v>67</v>
+      </c>
+      <c r="I59" t="s">
+        <v>1921</v>
+      </c>
+    </row>
+    <row r="60" spans="3:10" x14ac:dyDescent="0.35">
+      <c r="D60" t="s">
+        <v>335</v>
+      </c>
+      <c r="E60">
+        <v>1</v>
+      </c>
+      <c r="F60" s="32">
+        <v>49.98</v>
+      </c>
+      <c r="G60" s="29" t="s">
+        <v>336</v>
+      </c>
+      <c r="H60" t="s">
+        <v>67</v>
+      </c>
+      <c r="I60" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="61" spans="3:10" x14ac:dyDescent="0.35">
+      <c r="C61" t="s">
         <v>17</v>
       </c>
-      <c r="D55" t="s">
-        <v>332</v>
-      </c>
-      <c r="E55">
-        <v>1</v>
-      </c>
-      <c r="F55" s="32">
-        <v>30.35</v>
-      </c>
-      <c r="G55" s="29" t="s">
-        <v>333</v>
-      </c>
-      <c r="H55" t="s">
-        <v>67</v>
-      </c>
-      <c r="I55" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="C56" t="s">
-        <v>1682</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="D57" t="s">
-        <v>1918</v>
-      </c>
-      <c r="I57" t="s">
-        <v>1919</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="D58" t="s">
-        <v>1920</v>
-      </c>
-      <c r="E58">
-        <v>1</v>
-      </c>
-      <c r="F58" s="32">
-        <v>27.29</v>
-      </c>
-      <c r="G58" s="29" t="s">
-        <v>1921</v>
-      </c>
-      <c r="H58" t="s">
-        <v>67</v>
-      </c>
-      <c r="I58" t="s">
+      <c r="D61" t="s">
         <v>1922</v>
       </c>
-    </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="D59" t="s">
-        <v>335</v>
-      </c>
-      <c r="E59">
-        <v>1</v>
-      </c>
-      <c r="F59" s="32">
-        <v>49.98</v>
-      </c>
-      <c r="G59" s="29" t="s">
-        <v>336</v>
-      </c>
-      <c r="H59" t="s">
-        <v>67</v>
-      </c>
-      <c r="I59" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="C60" t="s">
+      <c r="G61" s="29" t="s">
+        <v>1923</v>
+      </c>
+      <c r="H61" t="s">
+        <v>67</v>
+      </c>
+      <c r="I61" t="s">
+        <v>1924</v>
+      </c>
+    </row>
+    <row r="62" spans="3:10" x14ac:dyDescent="0.35">
+      <c r="C62" t="s">
+        <v>2652</v>
+      </c>
+      <c r="G62" s="29"/>
+    </row>
+    <row r="63" spans="3:10" x14ac:dyDescent="0.35">
+      <c r="D63" t="s">
+        <v>2644</v>
+      </c>
+      <c r="E63">
+        <v>1</v>
+      </c>
+      <c r="F63">
+        <v>65.63</v>
+      </c>
+      <c r="G63" s="29" t="s">
+        <v>2645</v>
+      </c>
+      <c r="H63" t="s">
+        <v>67</v>
+      </c>
+      <c r="I63" t="s">
+        <v>2646</v>
+      </c>
+    </row>
+    <row r="64" spans="3:10" x14ac:dyDescent="0.35">
+      <c r="D64" t="s">
+        <v>2647</v>
+      </c>
+      <c r="E64">
+        <v>1</v>
+      </c>
+      <c r="F64">
+        <v>6.99</v>
+      </c>
+      <c r="G64" s="29" t="s">
+        <v>2648</v>
+      </c>
+      <c r="H64" t="s">
+        <v>844</v>
+      </c>
+      <c r="J64" t="s">
+        <v>2653</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="C65" t="s">
         <v>17</v>
       </c>
-      <c r="D60" t="s">
-        <v>1923</v>
-      </c>
-      <c r="G60" s="29" t="s">
-        <v>1924</v>
-      </c>
-      <c r="H60" t="s">
-        <v>67</v>
-      </c>
-      <c r="I60" t="s">
+      <c r="D65" t="s">
+        <v>2649</v>
+      </c>
+      <c r="E65">
+        <v>1</v>
+      </c>
+      <c r="F65">
+        <v>15.41</v>
+      </c>
+      <c r="G65" s="29" t="s">
+        <v>2650</v>
+      </c>
+      <c r="H65" t="s">
+        <v>67</v>
+      </c>
+      <c r="I65" t="s">
+        <v>272</v>
+      </c>
+      <c r="J65" t="s">
+        <v>2654</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A66" t="s">
         <v>1925</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A61" t="s">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="C67" s="21" t="s">
         <v>1926</v>
       </c>
-    </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="C62" s="21" t="s">
-        <v>1927</v>
-      </c>
-      <c r="F62" s="32">
-        <f>SUMPRODUCT(E63:E67,F63:F67)</f>
-        <v>5112</v>
-      </c>
-      <c r="J62" t="s">
+      <c r="F67" s="32">
+        <f>SUMPRODUCT(E68:E72,F68:F72)</f>
+        <v>5294</v>
+      </c>
+      <c r="J67" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="D63" s="29" t="str">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="D68" s="29" t="str">
         <f>$C$2</f>
         <v>Pike camera assembly &lt;</v>
       </c>
-      <c r="E63">
-        <v>1</v>
-      </c>
-      <c r="F63" s="32">
+      <c r="E68">
+        <v>1</v>
+      </c>
+      <c r="F68" s="32">
         <f>$F$2</f>
         <v>2317</v>
       </c>
-      <c r="J63" t="s">
+      <c r="J68" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="D64" s="29" t="str">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="D69" s="29" t="str">
         <f>$C$7</f>
-        <v>pump filter&lt;</v>
-      </c>
-      <c r="E64">
-        <v>1</v>
-      </c>
-      <c r="F64" s="32">
+        <v>NIR behavioral camera filters&lt;</v>
+      </c>
+      <c r="E69">
+        <v>1</v>
+      </c>
+      <c r="F69" s="32">
         <f>$F$7</f>
-        <v>2539</v>
-      </c>
-      <c r="J64" t="s">
+        <v>2721</v>
+      </c>
+      <c r="J69" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="65" spans="3:10" x14ac:dyDescent="0.35">
-      <c r="D65" s="29" t="str">
-        <f>$C$14</f>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="D70" s="29" t="str">
+        <f>$C$15</f>
         <v>hot mirror&lt;</v>
       </c>
-      <c r="E65">
-        <v>1</v>
-      </c>
-      <c r="F65" s="32">
-        <f>$F$14</f>
+      <c r="E70">
+        <v>1</v>
+      </c>
+      <c r="F70" s="32">
+        <f>$F$15</f>
         <v>183.64</v>
       </c>
-      <c r="J65" t="s">
+      <c r="J70" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="66" spans="3:10" x14ac:dyDescent="0.35">
-      <c r="D66" s="29" t="str">
-        <f>$C$19</f>
-        <v>IR illumination&lt;</v>
-      </c>
-      <c r="E66">
-        <v>1</v>
-      </c>
-      <c r="F66" s="32">
-        <f>$F$19</f>
-        <v>0</v>
-      </c>
-      <c r="J66" t="s">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="D71" s="29" t="str">
+        <f>$C$20</f>
+        <v>bahavioral IR illumination&lt;</v>
+      </c>
+      <c r="E71">
+        <v>1</v>
+      </c>
+      <c r="F71" s="32">
+        <f>$F$20</f>
+        <v>0</v>
+      </c>
+      <c r="J71" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="67" spans="3:10" x14ac:dyDescent="0.35">
-      <c r="C67" t="s">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="C72" t="s">
         <v>17</v>
       </c>
-      <c r="D67" s="29" t="str">
-        <f>$C$23</f>
+      <c r="D72" s="29" t="str">
+        <f>$C$24</f>
         <v>2" post with short base: TR2+PH2+BA1S &lt;</v>
       </c>
-      <c r="E67">
+      <c r="E72">
         <v>4</v>
       </c>
-      <c r="F67" s="32">
-        <f>$F$23</f>
+      <c r="F72" s="32">
+        <f>$F$24</f>
         <v>18.09</v>
       </c>
     </row>
-    <row r="68" spans="3:10" x14ac:dyDescent="0.35">
-      <c r="C68" s="21" t="s">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="C73" s="21" t="s">
+        <v>1927</v>
+      </c>
+      <c r="F73" s="32">
+        <f>SUMPRODUCT(E74:E77,F74:F77)</f>
+        <v>2091.6400000000003</v>
+      </c>
+      <c r="J73" t="s">
         <v>1928</v>
       </c>
-      <c r="F68" s="32">
-        <f>SUMPRODUCT(E69:E72,F69:F72)</f>
-        <v>2091.6400000000003</v>
-      </c>
-      <c r="J68" t="s">
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="D74" s="29" t="str">
+        <f>$C$28</f>
+        <v>Grasshopper3NIR-30 mm cage system &lt;</v>
+      </c>
+      <c r="E74">
+        <v>1</v>
+      </c>
+      <c r="F74" s="32">
+        <f>$F$28</f>
+        <v>1389.33</v>
+      </c>
+      <c r="J74" t="s">
         <v>1929</v>
       </c>
     </row>
-    <row r="69" spans="3:10" x14ac:dyDescent="0.35">
-      <c r="D69" s="29" t="str">
-        <f>$C$27</f>
-        <v>Grasshopper3NIR-30 mm cage system &lt;</v>
-      </c>
-      <c r="E69">
-        <v>1</v>
-      </c>
-      <c r="F69" s="32">
-        <f>$F$27</f>
-        <v>1389.33</v>
-      </c>
-      <c r="J69" t="s">
-        <v>1930</v>
-      </c>
-    </row>
-    <row r="70" spans="3:10" x14ac:dyDescent="0.35">
-      <c r="D70" s="29" t="str">
-        <f>$C$36</f>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="D75" s="29" t="str">
+        <f>$C$37</f>
         <v>200&amp;75mm lenses on 60mm cage &lt;</v>
       </c>
-      <c r="E70">
-        <v>1</v>
-      </c>
-      <c r="F70" s="32">
-        <f>$F$36</f>
+      <c r="E75">
+        <v>1</v>
+      </c>
+      <c r="F75" s="32">
+        <f>$F$37</f>
         <v>231.89999999999998</v>
       </c>
     </row>
-    <row r="71" spans="3:10" x14ac:dyDescent="0.35">
-      <c r="D71" s="29" t="str">
-        <f>$C$43</f>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="D76" s="29" t="str">
+        <f>$C$44</f>
         <v>60 mm cage system mount &lt;</v>
       </c>
-      <c r="E71">
-        <v>1</v>
-      </c>
-      <c r="F71" s="32">
-        <f>$F$43</f>
+      <c r="E76">
+        <v>1</v>
+      </c>
+      <c r="F76" s="32">
+        <f>$F$44</f>
         <v>86.7</v>
       </c>
     </row>
-    <row r="72" spans="3:10" x14ac:dyDescent="0.35">
-      <c r="D72" s="29" t="str">
-        <f>$C$51</f>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="D77" s="29" t="str">
+        <f>$C$52</f>
         <v>hot mirror asmbly, 100mm+ &lt;</v>
       </c>
-      <c r="E72">
-        <v>1</v>
-      </c>
-      <c r="F72" s="32">
-        <f>$F$51</f>
+      <c r="E77">
+        <v>1</v>
+      </c>
+      <c r="F77" s="32">
+        <f>$F$52</f>
         <v>383.71000000000004</v>
       </c>
     </row>
-    <row r="73" spans="3:10" x14ac:dyDescent="0.35">
-      <c r="C73" t="s">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="C78" t="s">
         <v>17</v>
       </c>
-      <c r="D73" s="29" t="str">
-        <f>$C$19</f>
-        <v>IR illumination&lt;</v>
-      </c>
-      <c r="E73">
-        <v>1</v>
-      </c>
-      <c r="F73" s="32">
-        <f>$F$19</f>
+      <c r="D78" s="29" t="str">
+        <f>$C$20</f>
+        <v>bahavioral IR illumination&lt;</v>
+      </c>
+      <c r="E78">
+        <v>1</v>
+      </c>
+      <c r="F78" s="32">
+        <f>$F$20</f>
         <v>0</v>
       </c>
     </row>
@@ -12047,42 +12235,47 @@
     <hyperlink ref="G4" r:id="rId2" xr:uid="{00000000-0004-0000-0A00-000001000000}"/>
     <hyperlink ref="G5" r:id="rId3" xr:uid="{00000000-0004-0000-0A00-000002000000}"/>
     <hyperlink ref="G8" r:id="rId4" location="downloads%20" xr:uid="{00000000-0004-0000-0A00-000003000000}"/>
-    <hyperlink ref="G13" r:id="rId5" display="https://www.thorlabs.com/thorproduct.cfm?partnumber=TRF90 " xr:uid="{00000000-0004-0000-0A00-000004000000}"/>
-    <hyperlink ref="G15" r:id="rId6" xr:uid="{00000000-0004-0000-0A00-000005000000}"/>
-    <hyperlink ref="G16" r:id="rId7" display="https://www.thorlabs.com/thorproduct.cfm?partnumber=FH2 " xr:uid="{00000000-0004-0000-0A00-000006000000}"/>
-    <hyperlink ref="G17" r:id="rId8" display="https://www.thorlabs.com/thorproduct.cfm?partnumber=RA90 " xr:uid="{00000000-0004-0000-0A00-000007000000}"/>
-    <hyperlink ref="G18" r:id="rId9" location="TR2" xr:uid="{00000000-0004-0000-0A00-000008000000}"/>
-    <hyperlink ref="G24" r:id="rId10" location="TR2" xr:uid="{00000000-0004-0000-0A00-000009000000}"/>
-    <hyperlink ref="G25" r:id="rId11" display="https://www.thorlabs.com/thorproduct.cfm?partnumber=PH2 " xr:uid="{00000000-0004-0000-0A00-00000A000000}"/>
-    <hyperlink ref="G26" r:id="rId12" display="https://www.thorlabs.com/thorproduct.cfm?partnumber=BA1S " xr:uid="{00000000-0004-0000-0A00-00000B000000}"/>
-    <hyperlink ref="G28" r:id="rId13" xr:uid="{00000000-0004-0000-0A00-00000C000000}"/>
-    <hyperlink ref="G29" r:id="rId14" xr:uid="{00000000-0004-0000-0A00-00000D000000}"/>
-    <hyperlink ref="G30" r:id="rId15" display="https://www.thorlabs.com/thorproduct.cfm?partnumber=SM1A39" xr:uid="{00000000-0004-0000-0A00-00000E000000}"/>
-    <hyperlink ref="G31" r:id="rId16" display="https://www.thorlabs.com/thorproduct.cfm?partnumber=CP08" xr:uid="{00000000-0004-0000-0A00-00000F000000}"/>
-    <hyperlink ref="G32" r:id="rId17" display="https://www.thorlabs.com/thorproduct.cfm?partnumber=DCP1" xr:uid="{00000000-0004-0000-0A00-000010000000}"/>
-    <hyperlink ref="G35" r:id="rId18" display="https://www.thorlabs.com/thorproduct.cfm?partnumber=ER1.5" xr:uid="{00000000-0004-0000-0A00-000011000000}"/>
-    <hyperlink ref="G37" r:id="rId19" display="https://www.thorlabs.com/thorproduct.cfm?partnumber=LCP02" xr:uid="{00000000-0004-0000-0A00-000012000000}"/>
-    <hyperlink ref="G38" r:id="rId20" display="https://www.thorlabs.com/thorproduct.cfm?partnumber=LCP01" xr:uid="{00000000-0004-0000-0A00-000013000000}"/>
-    <hyperlink ref="G39" r:id="rId21" display="https://www.thorlabs.com/thorproduct.cfm?partnumber=LA1979-B" xr:uid="{00000000-0004-0000-0A00-000014000000}"/>
-    <hyperlink ref="G40" r:id="rId22" display="https://www.thorlabs.com/thorproduct.cfm?partnumber=LA1145-B" xr:uid="{00000000-0004-0000-0A00-000015000000}"/>
-    <hyperlink ref="G41" r:id="rId23" display="https://www.thorlabs.com/thorproduct.cfm?partnumber=ER4" xr:uid="{00000000-0004-0000-0A00-000016000000}"/>
-    <hyperlink ref="G42" r:id="rId24" display="https://www.thorlabs.com/thorproduct.cfm?partnumber=ER6 " xr:uid="{00000000-0004-0000-0A00-000017000000}"/>
-    <hyperlink ref="G44" r:id="rId25" location="BA2L#ad-image-0" xr:uid="{00000000-0004-0000-0A00-000018000000}"/>
-    <hyperlink ref="G45" r:id="rId26" display="https://www.thorlabs.com/thorproduct.cfm?partnumber=LCP01B" xr:uid="{00000000-0004-0000-0A00-000019000000}"/>
-    <hyperlink ref="G47" r:id="rId27" display="https://www.thorlabs.com/thorproduct.cfm?partnumber=TR2 " xr:uid="{00000000-0004-0000-0A00-00001A000000}"/>
-    <hyperlink ref="G48" r:id="rId28" display="https://www.thorlabs.com/thorproduct.cfm?partnumber=RA180" xr:uid="{00000000-0004-0000-0A00-00001B000000}"/>
-    <hyperlink ref="G49" r:id="rId29" display="https://www.thorlabs.com/thorproduct.cfm?partnumber=TR1.5 " xr:uid="{00000000-0004-0000-0A00-00001C000000}"/>
-    <hyperlink ref="G50" r:id="rId30" display="https://www.thorlabs.com/thorproduct.cfm?partnumber=AM45T" xr:uid="{00000000-0004-0000-0A00-00001D000000}"/>
-    <hyperlink ref="G52" r:id="rId31" xr:uid="{00000000-0004-0000-0A00-00001E000000}"/>
-    <hyperlink ref="G54" r:id="rId32" display="https://www.thorlabs.com/thorproduct.cfm?partnumber=FP02" xr:uid="{00000000-0004-0000-0A00-00001F000000}"/>
-    <hyperlink ref="G55" r:id="rId33" display="https://www.thorlabs.com/thorproduct.cfm?partnumber=LCP01B" xr:uid="{00000000-0004-0000-0A00-000020000000}"/>
-    <hyperlink ref="G58" r:id="rId34" display="https://www.thorlabs.com/thorproduct.cfm?partnumber=SM2A55" xr:uid="{00000000-0004-0000-0A00-000021000000}"/>
-    <hyperlink ref="G59" r:id="rId35" display="https://www.thorlabs.com/thorproduct.cfm?partnumber=LCP08" xr:uid="{00000000-0004-0000-0A00-000022000000}"/>
-    <hyperlink ref="G60" r:id="rId36" display="https://www.thorlabs.com/thorproduct.cfm?partnumber=LA1417-B" xr:uid="{00000000-0004-0000-0A00-000023000000}"/>
+    <hyperlink ref="G14" r:id="rId5" display="https://www.thorlabs.com/thorproduct.cfm?partnumber=TRF90 " xr:uid="{00000000-0004-0000-0A00-000004000000}"/>
+    <hyperlink ref="G16" r:id="rId6" xr:uid="{00000000-0004-0000-0A00-000005000000}"/>
+    <hyperlink ref="G17" r:id="rId7" display="https://www.thorlabs.com/thorproduct.cfm?partnumber=FH2 " xr:uid="{00000000-0004-0000-0A00-000006000000}"/>
+    <hyperlink ref="G18" r:id="rId8" display="https://www.thorlabs.com/thorproduct.cfm?partnumber=RA90 " xr:uid="{00000000-0004-0000-0A00-000007000000}"/>
+    <hyperlink ref="G19" r:id="rId9" location="TR2" xr:uid="{00000000-0004-0000-0A00-000008000000}"/>
+    <hyperlink ref="G25" r:id="rId10" location="TR2" xr:uid="{00000000-0004-0000-0A00-000009000000}"/>
+    <hyperlink ref="G26" r:id="rId11" display="https://www.thorlabs.com/thorproduct.cfm?partnumber=PH2 " xr:uid="{00000000-0004-0000-0A00-00000A000000}"/>
+    <hyperlink ref="G27" r:id="rId12" display="https://www.thorlabs.com/thorproduct.cfm?partnumber=BA1S " xr:uid="{00000000-0004-0000-0A00-00000B000000}"/>
+    <hyperlink ref="G29" r:id="rId13" xr:uid="{00000000-0004-0000-0A00-00000C000000}"/>
+    <hyperlink ref="G30" r:id="rId14" xr:uid="{00000000-0004-0000-0A00-00000D000000}"/>
+    <hyperlink ref="G31" r:id="rId15" display="https://www.thorlabs.com/thorproduct.cfm?partnumber=SM1A39" xr:uid="{00000000-0004-0000-0A00-00000E000000}"/>
+    <hyperlink ref="G32" r:id="rId16" display="https://www.thorlabs.com/thorproduct.cfm?partnumber=CP08" xr:uid="{00000000-0004-0000-0A00-00000F000000}"/>
+    <hyperlink ref="G33" r:id="rId17" display="https://www.thorlabs.com/thorproduct.cfm?partnumber=DCP1" xr:uid="{00000000-0004-0000-0A00-000010000000}"/>
+    <hyperlink ref="G36" r:id="rId18" display="https://www.thorlabs.com/thorproduct.cfm?partnumber=ER1.5" xr:uid="{00000000-0004-0000-0A00-000011000000}"/>
+    <hyperlink ref="G38" r:id="rId19" display="https://www.thorlabs.com/thorproduct.cfm?partnumber=LCP02" xr:uid="{00000000-0004-0000-0A00-000012000000}"/>
+    <hyperlink ref="G39" r:id="rId20" display="https://www.thorlabs.com/thorproduct.cfm?partnumber=LCP01" xr:uid="{00000000-0004-0000-0A00-000013000000}"/>
+    <hyperlink ref="G40" r:id="rId21" display="https://www.thorlabs.com/thorproduct.cfm?partnumber=LA1979-B" xr:uid="{00000000-0004-0000-0A00-000014000000}"/>
+    <hyperlink ref="G41" r:id="rId22" display="https://www.thorlabs.com/thorproduct.cfm?partnumber=LA1145-B" xr:uid="{00000000-0004-0000-0A00-000015000000}"/>
+    <hyperlink ref="G42" r:id="rId23" display="https://www.thorlabs.com/thorproduct.cfm?partnumber=ER4" xr:uid="{00000000-0004-0000-0A00-000016000000}"/>
+    <hyperlink ref="G43" r:id="rId24" display="https://www.thorlabs.com/thorproduct.cfm?partnumber=ER6 " xr:uid="{00000000-0004-0000-0A00-000017000000}"/>
+    <hyperlink ref="G45" r:id="rId25" location="BA2L#ad-image-0" xr:uid="{00000000-0004-0000-0A00-000018000000}"/>
+    <hyperlink ref="G46" r:id="rId26" display="https://www.thorlabs.com/thorproduct.cfm?partnumber=LCP01B" xr:uid="{00000000-0004-0000-0A00-000019000000}"/>
+    <hyperlink ref="G48" r:id="rId27" display="https://www.thorlabs.com/thorproduct.cfm?partnumber=TR2 " xr:uid="{00000000-0004-0000-0A00-00001A000000}"/>
+    <hyperlink ref="G49" r:id="rId28" display="https://www.thorlabs.com/thorproduct.cfm?partnumber=RA180" xr:uid="{00000000-0004-0000-0A00-00001B000000}"/>
+    <hyperlink ref="G50" r:id="rId29" display="https://www.thorlabs.com/thorproduct.cfm?partnumber=TR1.5 " xr:uid="{00000000-0004-0000-0A00-00001C000000}"/>
+    <hyperlink ref="G51" r:id="rId30" display="https://www.thorlabs.com/thorproduct.cfm?partnumber=AM45T" xr:uid="{00000000-0004-0000-0A00-00001D000000}"/>
+    <hyperlink ref="G53" r:id="rId31" xr:uid="{00000000-0004-0000-0A00-00001E000000}"/>
+    <hyperlink ref="G55" r:id="rId32" display="https://www.thorlabs.com/thorproduct.cfm?partnumber=FP02" xr:uid="{00000000-0004-0000-0A00-00001F000000}"/>
+    <hyperlink ref="G56" r:id="rId33" display="https://www.thorlabs.com/thorproduct.cfm?partnumber=LCP01B" xr:uid="{00000000-0004-0000-0A00-000020000000}"/>
+    <hyperlink ref="G59" r:id="rId34" display="https://www.thorlabs.com/thorproduct.cfm?partnumber=SM2A55" xr:uid="{00000000-0004-0000-0A00-000021000000}"/>
+    <hyperlink ref="G60" r:id="rId35" display="https://www.thorlabs.com/thorproduct.cfm?partnumber=LCP08" xr:uid="{00000000-0004-0000-0A00-000022000000}"/>
+    <hyperlink ref="G61" r:id="rId36" display="https://www.thorlabs.com/thorproduct.cfm?partnumber=LA1417-B" xr:uid="{00000000-0004-0000-0A00-000023000000}"/>
     <hyperlink ref="G11" r:id="rId37" xr:uid="{872747A7-4078-49EC-A1B4-92F07788914C}"/>
     <hyperlink ref="G10" r:id="rId38" xr:uid="{C6309D5E-E5FB-44D2-B76D-E21BE67D4621}"/>
     <hyperlink ref="G9" r:id="rId39" xr:uid="{2BA5C839-3C70-48AC-A614-C5D24286A9CF}"/>
     <hyperlink ref="G12" r:id="rId40" xr:uid="{1E384043-053F-4A9E-AFA7-C9D7DF37F2B2}"/>
+    <hyperlink ref="G13" r:id="rId41" xr:uid="{479DE42C-B338-4736-9D65-CA212362088A}"/>
+    <hyperlink ref="G63" r:id="rId42" xr:uid="{077DC605-1500-4D92-8859-6293ECD1F931}"/>
+    <hyperlink ref="G64" r:id="rId43" xr:uid="{C6C1B04F-860D-4555-84D4-219DBE87B27E}"/>
+    <hyperlink ref="G65" r:id="rId44" xr:uid="{55F5AA22-C590-4D99-8540-F851C282CF94}"/>
+    <hyperlink ref="I21" r:id="rId45" xr:uid="{84E186AD-E009-49A6-A503-F206AFF8ABDB}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
   <pageSetup firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -12114,7 +12307,7 @@
         <v>54</v>
       </c>
       <c r="E1" s="12" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>56</v>
@@ -12134,15 +12327,15 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B3" s="21" t="s">
-        <v>1932</v>
+        <v>1931</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
+        <v>1932</v>
+      </c>
+      <c r="C4" t="s">
         <v>1933</v>
-      </c>
-      <c r="C4" t="s">
-        <v>1934</v>
       </c>
       <c r="D4">
         <v>2</v>
@@ -12151,15 +12344,15 @@
         <v>19</v>
       </c>
       <c r="F4" s="29" t="s">
+        <v>1934</v>
+      </c>
+      <c r="I4" t="s">
         <v>1935</v>
-      </c>
-      <c r="I4" t="s">
-        <v>1936</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="C5" t="s">
-        <v>1937</v>
+        <v>1936</v>
       </c>
       <c r="D5">
         <v>2</v>
@@ -12168,15 +12361,15 @@
         <v>20</v>
       </c>
       <c r="F5" s="11" t="s">
+        <v>1937</v>
+      </c>
+      <c r="I5" t="s">
         <v>1938</v>
-      </c>
-      <c r="I5" t="s">
-        <v>1939</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="C6" t="s">
-        <v>1940</v>
+        <v>1939</v>
       </c>
       <c r="D6">
         <v>2</v>
@@ -12185,7 +12378,7 @@
         <v>24</v>
       </c>
       <c r="F6" s="29" t="s">
-        <v>1941</v>
+        <v>1940</v>
       </c>
       <c r="I6" t="s">
         <v>9</v>
@@ -12193,7 +12386,7 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="C7" t="s">
-        <v>1942</v>
+        <v>1941</v>
       </c>
       <c r="D7">
         <v>2</v>
@@ -12202,7 +12395,7 @@
         <v>6.91</v>
       </c>
       <c r="F7" s="29" t="s">
-        <v>1943</v>
+        <v>1942</v>
       </c>
       <c r="I7" t="s">
         <v>9</v>
@@ -12213,12 +12406,12 @@
         <v>17</v>
       </c>
       <c r="C8" t="s">
-        <v>1944</v>
+        <v>1943</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B9" t="s">
-        <v>1945</v>
+        <v>1944</v>
       </c>
       <c r="C9" t="s">
         <v>437</v>
@@ -12230,7 +12423,7 @@
         <v>38.700000000000003</v>
       </c>
       <c r="F9" s="29" t="s">
-        <v>1946</v>
+        <v>1945</v>
       </c>
       <c r="I9" t="s">
         <v>9</v>
@@ -12247,7 +12440,7 @@
         <v>52.02</v>
       </c>
       <c r="F10" s="29" t="s">
-        <v>1947</v>
+        <v>1946</v>
       </c>
       <c r="I10" t="s">
         <v>944</v>
@@ -12264,7 +12457,7 @@
         <v>5.2</v>
       </c>
       <c r="F11" s="29" t="s">
-        <v>1881</v>
+        <v>1880</v>
       </c>
       <c r="I11" t="s">
         <v>9</v>
@@ -12272,7 +12465,7 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="C12" t="s">
-        <v>1879</v>
+        <v>1878</v>
       </c>
       <c r="D12">
         <v>1</v>
@@ -12281,7 +12474,7 @@
         <v>7.7</v>
       </c>
       <c r="F12" s="29" t="s">
-        <v>1880</v>
+        <v>1879</v>
       </c>
       <c r="I12" t="s">
         <v>9</v>
@@ -12292,7 +12485,7 @@
         <v>17</v>
       </c>
       <c r="C13" t="s">
-        <v>1874</v>
+        <v>1873</v>
       </c>
       <c r="D13">
         <v>1</v>
@@ -12301,7 +12494,7 @@
         <v>5.19</v>
       </c>
       <c r="F13" s="29" t="s">
-        <v>1875</v>
+        <v>1874</v>
       </c>
       <c r="I13" t="s">
         <v>9</v>
@@ -12314,14 +12507,14 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>2617</v>
+        <v>2616</v>
       </c>
       <c r="B15" s="21"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B16" s="21"/>
       <c r="C16" t="s">
-        <v>1951</v>
+        <v>1950</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -12330,16 +12523,16 @@
         <v>375</v>
       </c>
       <c r="F16" s="29" t="s">
-        <v>1952</v>
+        <v>1951</v>
       </c>
       <c r="G16" t="s">
         <v>682</v>
       </c>
       <c r="H16" t="s">
+        <v>1952</v>
+      </c>
+      <c r="I16" t="s">
         <v>1953</v>
-      </c>
-      <c r="I16" t="s">
-        <v>1954</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.35">
@@ -12348,7 +12541,7 @@
       </c>
       <c r="B17" s="21"/>
       <c r="C17" t="s">
-        <v>2618</v>
+        <v>2617</v>
       </c>
       <c r="D17">
         <v>1</v>
@@ -12357,18 +12550,18 @@
         <v>80.62</v>
       </c>
       <c r="F17" s="29" t="s">
+        <v>2618</v>
+      </c>
+      <c r="G17" t="s">
+        <v>67</v>
+      </c>
+      <c r="H17" t="s">
         <v>2619</v>
-      </c>
-      <c r="G17" t="s">
-        <v>67</v>
-      </c>
-      <c r="H17" t="s">
-        <v>2620</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B18" t="s">
-        <v>1948</v>
+        <v>1947</v>
       </c>
       <c r="E18" s="30">
         <f>SUMPRODUCT(D19:D25,E19:E25)</f>
@@ -12377,7 +12570,7 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="C19" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="D19">
         <v>1</v>
@@ -12386,7 +12579,7 @@
         <v>360</v>
       </c>
       <c r="F19" s="29" t="s">
-        <v>1950</v>
+        <v>1949</v>
       </c>
       <c r="G19" t="s">
         <v>844</v>
@@ -12410,18 +12603,18 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.35">
       <c r="C21" t="s">
+        <v>1954</v>
+      </c>
+      <c r="D21">
+        <v>1</v>
+      </c>
+      <c r="I21" t="s">
         <v>1955</v>
-      </c>
-      <c r="D21">
-        <v>1</v>
-      </c>
-      <c r="I21" t="s">
-        <v>1956</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.35">
       <c r="C22" t="s">
-        <v>1957</v>
+        <v>1956</v>
       </c>
       <c r="D22">
         <v>1</v>
@@ -12430,21 +12623,21 @@
         <v>36</v>
       </c>
       <c r="F22" s="29" t="s">
-        <v>1958</v>
+        <v>1957</v>
       </c>
       <c r="G22" t="s">
         <v>754</v>
       </c>
       <c r="H22" t="s">
+        <v>1958</v>
+      </c>
+      <c r="I22" t="s">
         <v>1959</v>
-      </c>
-      <c r="I22" t="s">
-        <v>1960</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.35">
       <c r="C23" t="s">
-        <v>1870</v>
+        <v>1869</v>
       </c>
       <c r="D23">
         <v>1</v>
@@ -12453,13 +12646,13 @@
         <v>19.690000000000001</v>
       </c>
       <c r="F23" s="29" t="s">
+        <v>1870</v>
+      </c>
+      <c r="G23" t="s">
+        <v>67</v>
+      </c>
+      <c r="H23" t="s">
         <v>1871</v>
-      </c>
-      <c r="G23" t="s">
-        <v>67</v>
-      </c>
-      <c r="H23" t="s">
-        <v>1872</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.35">
@@ -12473,7 +12666,7 @@
         <v>9.76</v>
       </c>
       <c r="F24" s="29" t="s">
-        <v>1873</v>
+        <v>1872</v>
       </c>
       <c r="G24" t="s">
         <v>67</v>
@@ -12487,7 +12680,7 @@
         <v>17</v>
       </c>
       <c r="C25" t="s">
-        <v>1874</v>
+        <v>1873</v>
       </c>
       <c r="D25">
         <v>2</v>
@@ -12496,7 +12689,7 @@
         <v>5.19</v>
       </c>
       <c r="F25" s="29" t="s">
-        <v>1875</v>
+        <v>1874</v>
       </c>
       <c r="G25" t="s">
         <v>67</v>
@@ -12505,7 +12698,7 @@
         <v>162</v>
       </c>
       <c r="I25" t="s">
-        <v>1961</v>
+        <v>1960</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.35">
@@ -12515,10 +12708,10 @@
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B27" t="s">
+        <v>1961</v>
+      </c>
+      <c r="C27" t="s">
         <v>1962</v>
-      </c>
-      <c r="C27" t="s">
-        <v>1963</v>
       </c>
       <c r="I27" t="s">
         <v>9</v>
@@ -12526,7 +12719,7 @@
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.35">
       <c r="C28" t="s">
-        <v>1964</v>
+        <v>1963</v>
       </c>
       <c r="D28">
         <v>1</v>
@@ -12535,7 +12728,7 @@
         <v>220</v>
       </c>
       <c r="F28" s="29" t="s">
-        <v>1965</v>
+        <v>1964</v>
       </c>
       <c r="I28" t="s">
         <v>9</v>
@@ -12543,7 +12736,7 @@
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.35">
       <c r="C29" t="s">
-        <v>1942</v>
+        <v>1941</v>
       </c>
       <c r="D29">
         <v>2</v>
@@ -12552,12 +12745,12 @@
         <v>6.91</v>
       </c>
       <c r="F29" s="29" t="s">
-        <v>1943</v>
+        <v>1942</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.35">
       <c r="C30" t="s">
-        <v>1966</v>
+        <v>1965</v>
       </c>
       <c r="D30">
         <v>1</v>
@@ -12566,7 +12759,7 @@
         <v>9.76</v>
       </c>
       <c r="F30" s="29" t="s">
-        <v>1873</v>
+        <v>1872</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.35">
@@ -12583,12 +12776,12 @@
         <v>23.56</v>
       </c>
       <c r="F31" s="29" t="s">
-        <v>1941</v>
+        <v>1940</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B32" t="s">
-        <v>1967</v>
+        <v>1966</v>
       </c>
     </row>
     <row r="33" spans="2:2" x14ac:dyDescent="0.35">
@@ -12649,7 +12842,7 @@
         <v>1841</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1968</v>
+        <v>1967</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>53</v>
@@ -12658,7 +12851,7 @@
         <v>54</v>
       </c>
       <c r="F1" s="12" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>56</v>
@@ -12675,7 +12868,7 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="F2" s="30">
         <f>SUMPRODUCT(E3:E4,F3:F4)</f>
@@ -12689,7 +12882,7 @@
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
       <c r="D3" t="s">
-        <v>1970</v>
+        <v>1969</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -12713,7 +12906,7 @@
         <v>17</v>
       </c>
       <c r="D4" t="s">
-        <v>1971</v>
+        <v>1970</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -12722,7 +12915,7 @@
         <v>4.74</v>
       </c>
       <c r="G4" s="29" t="s">
-        <v>1972</v>
+        <v>1971</v>
       </c>
       <c r="H4" s="30" t="s">
         <v>67</v>
@@ -12734,7 +12927,7 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>1973</v>
+        <v>1972</v>
       </c>
       <c r="F5" s="30">
         <f>SUMPRODUCT(E6:E7,F6:F7)</f>
@@ -12748,7 +12941,7 @@
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
       <c r="D6" t="s">
-        <v>1974</v>
+        <v>1973</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -12757,7 +12950,7 @@
         <v>7.22</v>
       </c>
       <c r="G6" s="29" t="s">
-        <v>1975</v>
+        <v>1974</v>
       </c>
       <c r="H6" s="30" t="s">
         <v>67</v>
@@ -12772,7 +12965,7 @@
         <v>17</v>
       </c>
       <c r="D7" t="s">
-        <v>1976</v>
+        <v>1975</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -12781,7 +12974,7 @@
         <v>4.97</v>
       </c>
       <c r="G7" s="29" t="s">
-        <v>1977</v>
+        <v>1976</v>
       </c>
       <c r="H7" s="30" t="s">
         <v>67</v>
@@ -12793,7 +12986,7 @@
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>1978</v>
+        <v>1977</v>
       </c>
       <c r="F8" s="30">
         <f>SUMPRODUCT(E9:E10,F9:F10)</f>
@@ -12807,7 +13000,7 @@
     <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9" s="1"/>
       <c r="D9" t="s">
-        <v>1879</v>
+        <v>1878</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -12816,7 +13009,7 @@
         <v>7.7</v>
       </c>
       <c r="G9" s="29" t="s">
-        <v>1880</v>
+        <v>1879</v>
       </c>
       <c r="H9" s="30" t="s">
         <v>67</v>
@@ -12831,7 +13024,7 @@
         <v>17</v>
       </c>
       <c r="D10" t="s">
-        <v>1874</v>
+        <v>1873</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -12840,7 +13033,7 @@
         <v>5.19</v>
       </c>
       <c r="G10" s="29" t="s">
-        <v>1875</v>
+        <v>1874</v>
       </c>
       <c r="H10" s="30" t="s">
         <v>67</v>
@@ -12852,7 +13045,7 @@
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>1979</v>
+        <v>1978</v>
       </c>
       <c r="F11" s="30">
         <f>SUMPRODUCT(E12:E13,F12:F13)</f>
@@ -12875,7 +13068,7 @@
         <v>8.27</v>
       </c>
       <c r="G12" s="29" t="s">
-        <v>1980</v>
+        <v>1979</v>
       </c>
       <c r="H12" s="30" t="s">
         <v>67</v>
@@ -12890,7 +13083,7 @@
         <v>17</v>
       </c>
       <c r="D13" t="s">
-        <v>1981</v>
+        <v>1980</v>
       </c>
       <c r="E13">
         <v>1</v>
@@ -12899,7 +13092,7 @@
         <v>5.42</v>
       </c>
       <c r="G13" s="29" t="s">
-        <v>1982</v>
+        <v>1981</v>
       </c>
       <c r="H13" s="30" t="s">
         <v>67</v>
@@ -12911,7 +13104,7 @@
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A14" s="31" t="s">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="F14" s="30">
         <f>SUMPRODUCT(E15:E18,F15:F18)</f>
@@ -12920,14 +13113,14 @@
       <c r="G14" s="29"/>
       <c r="I14" s="31"/>
       <c r="J14" t="s">
-        <v>1984</v>
+        <v>1983</v>
       </c>
       <c r="L14" s="1"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A15" s="31"/>
       <c r="D15" t="s">
-        <v>1985</v>
+        <v>1984</v>
       </c>
       <c r="E15">
         <v>1</v>
@@ -12936,20 +13129,20 @@
         <v>16.89</v>
       </c>
       <c r="G15" s="29" t="s">
+        <v>1985</v>
+      </c>
+      <c r="H15" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="I15" s="31" t="s">
         <v>1986</v>
-      </c>
-      <c r="H15" s="30" t="s">
-        <v>67</v>
-      </c>
-      <c r="I15" s="31" t="s">
-        <v>1987</v>
       </c>
       <c r="L15" s="1"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A16" s="31"/>
       <c r="D16" t="s">
-        <v>1988</v>
+        <v>1987</v>
       </c>
       <c r="E16">
         <v>1</v>
@@ -12958,19 +13151,19 @@
         <v>13.8</v>
       </c>
       <c r="G16" s="29" t="s">
+        <v>1988</v>
+      </c>
+      <c r="H16" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="I16" s="31" t="s">
         <v>1989</v>
-      </c>
-      <c r="H16" s="30" t="s">
-        <v>67</v>
-      </c>
-      <c r="I16" s="31" t="s">
-        <v>1990</v>
       </c>
       <c r="L16" s="1"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.35">
       <c r="D17" t="s">
-        <v>1991</v>
+        <v>1990</v>
       </c>
       <c r="E17">
         <v>1</v>
@@ -12979,16 +13172,16 @@
         <v>36.979999999999997</v>
       </c>
       <c r="G17" s="29" t="s">
+        <v>1991</v>
+      </c>
+      <c r="H17" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="I17" t="s">
         <v>1992</v>
       </c>
-      <c r="H17" s="30" t="s">
-        <v>67</v>
-      </c>
-      <c r="I17" t="s">
+      <c r="J17" t="s">
         <v>1993</v>
-      </c>
-      <c r="J17" t="s">
-        <v>1994</v>
       </c>
       <c r="L17" s="1"/>
     </row>
@@ -12997,7 +13190,7 @@
         <v>17</v>
       </c>
       <c r="D18" t="s">
-        <v>1995</v>
+        <v>1994</v>
       </c>
       <c r="E18">
         <v>1</v>
@@ -13006,34 +13199,34 @@
         <v>36.979999999999997</v>
       </c>
       <c r="G18" s="29" t="s">
+        <v>1995</v>
+      </c>
+      <c r="H18" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="I18" s="31" t="s">
         <v>1996</v>
-      </c>
-      <c r="H18" s="30" t="s">
-        <v>67</v>
-      </c>
-      <c r="I18" s="31" t="s">
-        <v>1997</v>
       </c>
       <c r="L18" s="1"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="K19" s="21"/>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.35">
       <c r="C20" t="s">
+        <v>1998</v>
+      </c>
+      <c r="D20" t="s">
         <v>1999</v>
-      </c>
-      <c r="D20" t="s">
-        <v>2000</v>
       </c>
       <c r="F20" s="30">
         <v>88</v>
       </c>
       <c r="G20" s="29" t="s">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="H20" s="30" t="s">
         <v>67</v>
@@ -13044,60 +13237,60 @@
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.35">
       <c r="C21" t="s">
-        <v>1999</v>
+        <v>1998</v>
       </c>
       <c r="D21" t="s">
-        <v>2002</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.35">
       <c r="C22" t="s">
-        <v>1999</v>
+        <v>1998</v>
       </c>
       <c r="D22" t="s">
-        <v>2003</v>
+        <v>2002</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.35">
       <c r="C23" t="s">
-        <v>1999</v>
+        <v>1998</v>
       </c>
       <c r="D23" t="s">
-        <v>2004</v>
+        <v>2003</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.35">
       <c r="C24" t="s">
-        <v>1999</v>
+        <v>1998</v>
       </c>
       <c r="D24" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.35">
       <c r="C25" t="s">
-        <v>1999</v>
+        <v>1998</v>
       </c>
       <c r="D25" t="s">
-        <v>2006</v>
+        <v>2005</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.35">
       <c r="C26" t="s">
-        <v>1999</v>
+        <v>1998</v>
       </c>
       <c r="D26" t="s">
-        <v>2007</v>
+        <v>2006</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B27" t="s">
-        <v>2008</v>
+        <v>2007</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.35">
       <c r="D28" t="s">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="E28">
         <v>1</v>
@@ -13106,18 +13299,18 @@
         <v>82.37</v>
       </c>
       <c r="G28" s="29" t="s">
+        <v>2009</v>
+      </c>
+      <c r="H28" s="30" t="s">
         <v>2010</v>
       </c>
-      <c r="H28" s="30" t="s">
+      <c r="I28" t="s">
         <v>2011</v>
-      </c>
-      <c r="I28" t="s">
-        <v>2012</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.35">
       <c r="D29" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="E29">
         <v>1</v>
@@ -13126,18 +13319,18 @@
         <v>30.86</v>
       </c>
       <c r="G29" s="29" t="s">
+        <v>2013</v>
+      </c>
+      <c r="H29" s="30" t="s">
+        <v>2010</v>
+      </c>
+      <c r="I29" t="s">
         <v>2014</v>
-      </c>
-      <c r="H29" s="30" t="s">
-        <v>2011</v>
-      </c>
-      <c r="I29" t="s">
-        <v>2015</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.35">
       <c r="D30" t="s">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="E30">
         <v>1</v>
@@ -13146,13 +13339,13 @@
         <v>34.94</v>
       </c>
       <c r="G30" s="29" t="s">
+        <v>2016</v>
+      </c>
+      <c r="H30" s="30" t="s">
+        <v>2010</v>
+      </c>
+      <c r="I30" t="s">
         <v>2017</v>
-      </c>
-      <c r="H30" s="30" t="s">
-        <v>2011</v>
-      </c>
-      <c r="I30" t="s">
-        <v>2018</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.35">
@@ -13160,7 +13353,7 @@
         <v>17</v>
       </c>
       <c r="D31" t="s">
-        <v>2019</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.35">
@@ -13185,10 +13378,10 @@
     </row>
     <row r="33" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B33" t="s">
+        <v>2019</v>
+      </c>
+      <c r="D33" t="s">
         <v>2020</v>
-      </c>
-      <c r="D33" t="s">
-        <v>2021</v>
       </c>
       <c r="E33">
         <v>1</v>
@@ -13197,18 +13390,18 @@
         <v>40.799999999999997</v>
       </c>
       <c r="G33" s="29" t="s">
+        <v>2021</v>
+      </c>
+      <c r="H33" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="I33" t="s">
         <v>2022</v>
-      </c>
-      <c r="H33" s="30" t="s">
-        <v>67</v>
-      </c>
-      <c r="I33" t="s">
-        <v>2023</v>
       </c>
     </row>
     <row r="34" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D34" t="s">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="E34">
         <v>1</v>
@@ -13217,13 +13410,13 @@
         <v>46.92</v>
       </c>
       <c r="G34" s="29" t="s">
+        <v>2024</v>
+      </c>
+      <c r="H34" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="I34" t="s">
         <v>2025</v>
-      </c>
-      <c r="H34" s="30" t="s">
-        <v>67</v>
-      </c>
-      <c r="I34" t="s">
-        <v>2026</v>
       </c>
     </row>
     <row r="35" spans="2:9" x14ac:dyDescent="0.35">
@@ -13231,7 +13424,7 @@
         <v>17</v>
       </c>
       <c r="D35" t="s">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="E35">
         <v>1</v>
@@ -13246,12 +13439,12 @@
         <v>67</v>
       </c>
       <c r="I35" t="s">
-        <v>2026</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="36" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D36" t="s">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="E36">
         <v>3</v>
@@ -13260,18 +13453,18 @@
         <v>17.54</v>
       </c>
       <c r="G36" s="29" t="s">
+        <v>2028</v>
+      </c>
+      <c r="H36" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="I36" t="s">
         <v>2029</v>
-      </c>
-      <c r="H36" s="30" t="s">
-        <v>67</v>
-      </c>
-      <c r="I36" t="s">
-        <v>2030</v>
       </c>
     </row>
     <row r="37" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D37" t="s">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="E37">
         <v>1</v>
@@ -13280,24 +13473,24 @@
         <v>19.79</v>
       </c>
       <c r="G37" s="29" t="s">
+        <v>2031</v>
+      </c>
+      <c r="H37" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="I37" t="s">
         <v>2032</v>
-      </c>
-      <c r="H37" s="30" t="s">
-        <v>67</v>
-      </c>
-      <c r="I37" t="s">
-        <v>2033</v>
       </c>
     </row>
     <row r="38" spans="2:9" x14ac:dyDescent="0.35">
       <c r="C38" t="s">
-        <v>1999</v>
+        <v>1998</v>
       </c>
       <c r="D38" t="s">
+        <v>2033</v>
+      </c>
+      <c r="G38" s="29" t="s">
         <v>2034</v>
-      </c>
-      <c r="G38" s="29" t="s">
-        <v>2035</v>
       </c>
       <c r="H38" s="30" t="s">
         <v>67</v>
@@ -13305,7 +13498,7 @@
     </row>
     <row r="39" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B39" t="s">
-        <v>2036</v>
+        <v>2035</v>
       </c>
       <c r="D39" s="29" t="str">
         <f>$A$2</f>
@@ -13373,7 +13566,7 @@
         <v>5.2</v>
       </c>
       <c r="G43" s="29" t="s">
-        <v>1881</v>
+        <v>1880</v>
       </c>
       <c r="H43" s="30" t="s">
         <v>67</v>
@@ -13467,7 +13660,7 @@
     </row>
     <row r="48" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B48" t="s">
-        <v>2037</v>
+        <v>2036</v>
       </c>
     </row>
     <row r="49" spans="2:9" x14ac:dyDescent="0.35">
@@ -13481,7 +13674,7 @@
         <v>19.79</v>
       </c>
       <c r="G49" s="29" t="s">
-        <v>1884</v>
+        <v>1883</v>
       </c>
       <c r="H49" s="30" t="s">
         <v>67</v>
@@ -13492,7 +13685,7 @@
     </row>
     <row r="50" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D50" t="s">
-        <v>2038</v>
+        <v>2037</v>
       </c>
       <c r="E50">
         <v>2</v>
@@ -13501,18 +13694,18 @@
         <v>6.48</v>
       </c>
       <c r="G50" s="29" t="s">
+        <v>2038</v>
+      </c>
+      <c r="H50" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="I50" t="s">
         <v>2039</v>
-      </c>
-      <c r="H50" s="30" t="s">
-        <v>67</v>
-      </c>
-      <c r="I50" t="s">
-        <v>2040</v>
       </c>
     </row>
     <row r="51" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D51" t="s">
-        <v>2041</v>
+        <v>2040</v>
       </c>
       <c r="E51">
         <v>1</v>
@@ -13521,13 +13714,13 @@
         <v>42.08</v>
       </c>
       <c r="G51" s="29" t="s">
+        <v>2041</v>
+      </c>
+      <c r="H51" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="I51" t="s">
         <v>2042</v>
-      </c>
-      <c r="H51" s="30" t="s">
-        <v>67</v>
-      </c>
-      <c r="I51" t="s">
-        <v>2043</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.35">
@@ -13541,7 +13734,7 @@
         <v>88</v>
       </c>
       <c r="G52" s="29" t="s">
-        <v>2044</v>
+        <v>2043</v>
       </c>
       <c r="H52" s="30" t="s">
         <v>67</v>
@@ -13601,7 +13794,7 @@
         <v>22.22</v>
       </c>
       <c r="G55" s="29" t="s">
-        <v>2045</v>
+        <v>2044</v>
       </c>
       <c r="H55" s="30" t="s">
         <v>67</v>
@@ -13621,7 +13814,7 @@
         <v>23.18</v>
       </c>
       <c r="G56" s="29" t="s">
-        <v>2046</v>
+        <v>2045</v>
       </c>
       <c r="H56" s="30" t="s">
         <v>67</v>
@@ -13641,7 +13834,7 @@
         <v>25.08</v>
       </c>
       <c r="G57" s="29" t="s">
-        <v>2047</v>
+        <v>2046</v>
       </c>
       <c r="H57" s="30" t="s">
         <v>67</v>
@@ -13701,7 +13894,7 @@
         <v>44.46</v>
       </c>
       <c r="G60" s="29" t="s">
-        <v>2048</v>
+        <v>2047</v>
       </c>
       <c r="H60" s="30" t="s">
         <v>67</v>
@@ -13741,7 +13934,7 @@
         <v>16.8</v>
       </c>
       <c r="G62" s="29" t="s">
-        <v>2049</v>
+        <v>2048</v>
       </c>
       <c r="H62" s="30" t="s">
         <v>67</v>
@@ -13764,7 +13957,7 @@
         <v>25.5</v>
       </c>
       <c r="G63" s="29" t="s">
-        <v>2050</v>
+        <v>2049</v>
       </c>
       <c r="H63" s="30" t="s">
         <v>67</v>
@@ -13775,12 +13968,12 @@
     </row>
     <row r="64" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B64" t="s">
-        <v>2051</v>
+        <v>2050</v>
       </c>
     </row>
     <row r="65" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D65" t="s">
-        <v>2052</v>
+        <v>2051</v>
       </c>
       <c r="E65">
         <v>1</v>
@@ -13789,13 +13982,13 @@
         <v>98</v>
       </c>
       <c r="G65" s="29" t="s">
+        <v>2052</v>
+      </c>
+      <c r="H65" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="I65" t="s">
         <v>2053</v>
-      </c>
-      <c r="H65" s="30" t="s">
-        <v>67</v>
-      </c>
-      <c r="I65" t="s">
-        <v>2054</v>
       </c>
     </row>
     <row r="66" spans="2:9" x14ac:dyDescent="0.35">
@@ -13803,7 +13996,7 @@
         <v>17</v>
       </c>
       <c r="D66" t="s">
-        <v>2055</v>
+        <v>2054</v>
       </c>
       <c r="E66">
         <v>1</v>
@@ -13812,23 +14005,23 @@
         <v>26.75</v>
       </c>
       <c r="G66" s="29" t="s">
+        <v>2055</v>
+      </c>
+      <c r="H66" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="I66" t="s">
         <v>2056</v>
-      </c>
-      <c r="H66" s="30" t="s">
-        <v>67</v>
-      </c>
-      <c r="I66" t="s">
-        <v>2057</v>
       </c>
     </row>
     <row r="67" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B67" t="s">
-        <v>2058</v>
+        <v>2057</v>
       </c>
     </row>
     <row r="68" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D68" t="s">
-        <v>2059</v>
+        <v>2058</v>
       </c>
       <c r="E68">
         <v>2</v>
@@ -13837,7 +14030,7 @@
         <v>17.75</v>
       </c>
       <c r="G68" s="29" t="s">
-        <v>2060</v>
+        <v>2059</v>
       </c>
       <c r="H68" s="30" t="s">
         <v>67</v>
@@ -13857,7 +14050,7 @@
         <v>20.3</v>
       </c>
       <c r="G69" s="29" t="s">
-        <v>2061</v>
+        <v>2060</v>
       </c>
       <c r="H69" s="30" t="s">
         <v>67</v>
@@ -13868,7 +14061,7 @@
     </row>
     <row r="70" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D70" t="s">
-        <v>2062</v>
+        <v>2061</v>
       </c>
       <c r="E70">
         <v>2</v>
@@ -13888,7 +14081,7 @@
     </row>
     <row r="71" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D71" t="s">
-        <v>2063</v>
+        <v>2062</v>
       </c>
       <c r="E71">
         <v>2</v>
@@ -13897,7 +14090,7 @@
         <v>12.59</v>
       </c>
       <c r="G71" s="29" t="s">
-        <v>2064</v>
+        <v>2063</v>
       </c>
       <c r="H71" s="30" t="s">
         <v>67</v>
@@ -13928,7 +14121,7 @@
     </row>
     <row r="73" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D73" t="s">
-        <v>2065</v>
+        <v>2064</v>
       </c>
       <c r="E73">
         <v>2</v>
@@ -13937,13 +14130,13 @@
         <v>12.55</v>
       </c>
       <c r="G73" s="29" t="s">
+        <v>2065</v>
+      </c>
+      <c r="H73" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="I73" t="s">
         <v>2066</v>
-      </c>
-      <c r="H73" s="30" t="s">
-        <v>67</v>
-      </c>
-      <c r="I73" t="s">
-        <v>2067</v>
       </c>
     </row>
     <row r="74" spans="2:9" x14ac:dyDescent="0.35">
@@ -13951,7 +14144,7 @@
         <v>17</v>
       </c>
       <c r="D74" t="s">
-        <v>2068</v>
+        <v>2067</v>
       </c>
       <c r="E74">
         <v>2</v>
@@ -13960,23 +14153,23 @@
         <v>13.87</v>
       </c>
       <c r="G74" s="29" t="s">
+        <v>2068</v>
+      </c>
+      <c r="H74" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="I74" t="s">
         <v>2069</v>
-      </c>
-      <c r="H74" s="30" t="s">
-        <v>67</v>
-      </c>
-      <c r="I74" t="s">
-        <v>2070</v>
       </c>
     </row>
     <row r="75" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B75" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
     </row>
     <row r="76" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D76" t="s">
-        <v>2072</v>
+        <v>2071</v>
       </c>
       <c r="E76">
         <v>2</v>
@@ -13985,18 +14178,18 @@
         <v>5.51</v>
       </c>
       <c r="G76" s="29" t="s">
+        <v>2072</v>
+      </c>
+      <c r="H76" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="I76" t="s">
         <v>2073</v>
-      </c>
-      <c r="H76" s="30" t="s">
-        <v>67</v>
-      </c>
-      <c r="I76" t="s">
-        <v>2074</v>
       </c>
     </row>
     <row r="77" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D77" t="s">
-        <v>2075</v>
+        <v>2074</v>
       </c>
       <c r="E77">
         <v>6</v>
@@ -14005,13 +14198,13 @@
         <v>8.06</v>
       </c>
       <c r="G77" s="29" t="s">
+        <v>2075</v>
+      </c>
+      <c r="H77" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="I77" t="s">
         <v>2076</v>
-      </c>
-      <c r="H77" s="30" t="s">
-        <v>67</v>
-      </c>
-      <c r="I77" t="s">
-        <v>2077</v>
       </c>
     </row>
     <row r="78" spans="2:9" x14ac:dyDescent="0.35">
@@ -14019,18 +14212,18 @@
         <v>17</v>
       </c>
       <c r="D78" t="s">
-        <v>2078</v>
+        <v>2077</v>
       </c>
       <c r="G78" s="29"/>
     </row>
     <row r="79" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B79" t="s">
-        <v>2079</v>
+        <v>2078</v>
       </c>
     </row>
     <row r="80" spans="2:9" x14ac:dyDescent="0.35">
       <c r="D80" t="s">
-        <v>2080</v>
+        <v>2079</v>
       </c>
       <c r="E80">
         <v>5</v>
@@ -14039,7 +14232,7 @@
         <v>4.5</v>
       </c>
       <c r="G80" s="29" t="s">
-        <v>2081</v>
+        <v>2080</v>
       </c>
       <c r="H80" s="30" t="s">
         <v>67</v>
@@ -14082,7 +14275,7 @@
         <v>11.07</v>
       </c>
       <c r="G82" s="29" t="s">
-        <v>2082</v>
+        <v>2081</v>
       </c>
       <c r="H82" s="30" t="s">
         <v>67</v>
@@ -14093,17 +14286,17 @@
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.35">
       <c r="D84" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B85" t="s">
-        <v>2084</v>
+        <v>2083</v>
       </c>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.35">
       <c r="D86" t="s">
-        <v>2085</v>
+        <v>2084</v>
       </c>
       <c r="E86">
         <v>1</v>
@@ -14112,7 +14305,7 @@
         <v>1075.08</v>
       </c>
       <c r="G86" s="29" t="s">
-        <v>2086</v>
+        <v>2085</v>
       </c>
       <c r="H86" s="30" t="s">
         <v>67</v>
@@ -14132,7 +14325,7 @@
         <v>508.98</v>
       </c>
       <c r="G87" s="29" t="s">
-        <v>2087</v>
+        <v>2086</v>
       </c>
       <c r="H87" s="30" t="s">
         <v>67</v>
@@ -14158,7 +14351,7 @@
         <v>704</v>
       </c>
       <c r="G88" s="29" t="s">
-        <v>2088</v>
+        <v>2087</v>
       </c>
       <c r="H88" s="30" t="s">
         <v>67</v>
@@ -14178,7 +14371,7 @@
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.35">
       <c r="D92" t="s">
-        <v>2089</v>
+        <v>2088</v>
       </c>
       <c r="E92">
         <v>4</v>
@@ -14187,18 +14380,18 @@
         <v>5</v>
       </c>
       <c r="G92" s="29" t="s">
+        <v>2089</v>
+      </c>
+      <c r="H92" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="I92" t="s">
         <v>2090</v>
-      </c>
-      <c r="H92" s="30" t="s">
-        <v>67</v>
-      </c>
-      <c r="I92" t="s">
-        <v>2091</v>
       </c>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.35">
       <c r="D93" t="s">
-        <v>2092</v>
+        <v>2091</v>
       </c>
       <c r="E93">
         <v>1</v>
@@ -14207,18 +14400,18 @@
         <v>26.01</v>
       </c>
       <c r="G93" s="29" t="s">
+        <v>2092</v>
+      </c>
+      <c r="H93" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="I93" t="s">
         <v>2093</v>
-      </c>
-      <c r="H93" s="30" t="s">
-        <v>67</v>
-      </c>
-      <c r="I93" t="s">
-        <v>2094</v>
       </c>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.35">
       <c r="D94" t="s">
-        <v>2095</v>
+        <v>2094</v>
       </c>
       <c r="E94">
         <v>1</v>
@@ -14227,18 +14420,18 @@
         <v>20.399999999999999</v>
       </c>
       <c r="G94" s="29" t="s">
+        <v>2095</v>
+      </c>
+      <c r="H94" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="I94" t="s">
         <v>2096</v>
-      </c>
-      <c r="H94" s="30" t="s">
-        <v>67</v>
-      </c>
-      <c r="I94" t="s">
-        <v>2097</v>
       </c>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.35">
       <c r="D95" t="s">
-        <v>2098</v>
+        <v>2097</v>
       </c>
       <c r="E95">
         <v>2</v>
@@ -14247,18 +14440,18 @@
         <v>18.260000000000002</v>
       </c>
       <c r="G95" s="29" t="s">
+        <v>2098</v>
+      </c>
+      <c r="H95" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="I95" t="s">
         <v>2099</v>
-      </c>
-      <c r="H95" s="30" t="s">
-        <v>67</v>
-      </c>
-      <c r="I95" t="s">
-        <v>2100</v>
       </c>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.35">
       <c r="D96" t="s">
-        <v>2101</v>
+        <v>2100</v>
       </c>
       <c r="E96">
         <v>2</v>
@@ -14267,13 +14460,13 @@
         <v>16.22</v>
       </c>
       <c r="G96" s="29" t="s">
+        <v>2101</v>
+      </c>
+      <c r="H96" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="I96" t="s">
         <v>2102</v>
-      </c>
-      <c r="H96" s="30" t="s">
-        <v>67</v>
-      </c>
-      <c r="I96" t="s">
-        <v>2103</v>
       </c>
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.35">
@@ -14281,7 +14474,7 @@
         <v>17</v>
       </c>
       <c r="D97" t="s">
-        <v>2104</v>
+        <v>2103</v>
       </c>
       <c r="E97">
         <v>1</v>
@@ -14290,13 +14483,13 @@
         <v>57.89</v>
       </c>
       <c r="G97" s="29" t="s">
+        <v>2104</v>
+      </c>
+      <c r="H97" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="I97" t="s">
         <v>2105</v>
-      </c>
-      <c r="H97" s="30" t="s">
-        <v>67</v>
-      </c>
-      <c r="I97" t="s">
-        <v>2106</v>
       </c>
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.35">
@@ -14335,7 +14528,7 @@
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.35">
       <c r="D102" t="s">
-        <v>1981</v>
+        <v>1980</v>
       </c>
       <c r="E102">
         <v>10</v>
@@ -14344,7 +14537,7 @@
         <v>5.42</v>
       </c>
       <c r="G102" s="29" t="s">
-        <v>1982</v>
+        <v>1981</v>
       </c>
       <c r="H102" s="30" t="s">
         <v>67</v>
@@ -14355,7 +14548,7 @@
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.35">
       <c r="D103" t="s">
-        <v>2107</v>
+        <v>2106</v>
       </c>
       <c r="E103">
         <v>1</v>
@@ -14364,18 +14557,18 @@
         <v>10.51</v>
       </c>
       <c r="G103" s="29" t="s">
+        <v>2107</v>
+      </c>
+      <c r="H103" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="I103" t="s">
         <v>2108</v>
-      </c>
-      <c r="H103" s="30" t="s">
-        <v>67</v>
-      </c>
-      <c r="I103" t="s">
-        <v>2109</v>
       </c>
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.35">
       <c r="D104" t="s">
-        <v>2110</v>
+        <v>2109</v>
       </c>
       <c r="E104">
         <v>2</v>
@@ -14384,7 +14577,7 @@
         <v>31.52</v>
       </c>
       <c r="G104" s="29" t="s">
-        <v>2111</v>
+        <v>2110</v>
       </c>
       <c r="H104" s="30" t="s">
         <v>67</v>
@@ -14395,7 +14588,7 @@
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.35">
       <c r="D105" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
       <c r="E105">
         <v>4</v>
@@ -14404,7 +14597,7 @@
         <v>14.5</v>
       </c>
       <c r="G105" s="29" t="s">
-        <v>2113</v>
+        <v>2112</v>
       </c>
       <c r="H105" s="30" t="s">
         <v>67</v>
@@ -14424,7 +14617,7 @@
         <v>52.02</v>
       </c>
       <c r="G106" s="29" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
       <c r="H106" s="30" t="s">
         <v>67</v>
@@ -14444,7 +14637,7 @@
         <v>19.329999999999998</v>
       </c>
       <c r="G107" s="29" t="s">
-        <v>2115</v>
+        <v>2114</v>
       </c>
       <c r="H107" s="30" t="s">
         <v>67</v>
@@ -14464,7 +14657,7 @@
         <v>7.3</v>
       </c>
       <c r="G108" s="29" t="s">
-        <v>2116</v>
+        <v>2115</v>
       </c>
       <c r="H108" s="30" t="s">
         <v>67</v>
@@ -14484,7 +14677,7 @@
         <v>50.49</v>
       </c>
       <c r="G109" s="29" t="s">
-        <v>2117</v>
+        <v>2116</v>
       </c>
       <c r="H109" s="31" t="s">
         <v>67</v>
@@ -14496,7 +14689,7 @@
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.35">
       <c r="D110" t="s">
-        <v>2118</v>
+        <v>2117</v>
       </c>
       <c r="E110">
         <v>1</v>
@@ -14505,13 +14698,13 @@
         <v>310.98</v>
       </c>
       <c r="G110" s="29" t="s">
+        <v>2118</v>
+      </c>
+      <c r="H110" s="31" t="s">
+        <v>67</v>
+      </c>
+      <c r="I110" s="31" t="s">
         <v>2119</v>
-      </c>
-      <c r="H110" s="31" t="s">
-        <v>67</v>
-      </c>
-      <c r="I110" s="31" t="s">
-        <v>2120</v>
       </c>
       <c r="J110" s="31"/>
     </row>
@@ -14526,7 +14719,7 @@
         <v>5.05</v>
       </c>
       <c r="G111" s="29" t="s">
-        <v>2121</v>
+        <v>2120</v>
       </c>
       <c r="H111" s="30" t="s">
         <v>67</v>
@@ -14537,7 +14730,7 @@
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.35">
       <c r="D112" t="s">
-        <v>2122</v>
+        <v>2121</v>
       </c>
       <c r="E112">
         <v>1</v>
@@ -14546,30 +14739,30 @@
         <v>75.64</v>
       </c>
       <c r="G112" s="29" t="s">
+        <v>2122</v>
+      </c>
+      <c r="H112" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="I112" t="s">
         <v>2123</v>
-      </c>
-      <c r="H112" s="30" t="s">
-        <v>67</v>
-      </c>
-      <c r="I112" t="s">
-        <v>2124</v>
       </c>
     </row>
     <row r="113" spans="1:11" x14ac:dyDescent="0.35">
       <c r="D113" t="s">
-        <v>2125</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="114" spans="1:11" x14ac:dyDescent="0.35">
       <c r="D114" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="G114" s="30"/>
       <c r="I114" s="30"/>
     </row>
     <row r="115" spans="1:11" x14ac:dyDescent="0.35">
       <c r="D115" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="E115">
         <v>1</v>
@@ -14578,18 +14771,18 @@
         <v>11.76</v>
       </c>
       <c r="G115" s="29" t="s">
+        <v>2127</v>
+      </c>
+      <c r="H115" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="I115" t="s">
         <v>2128</v>
-      </c>
-      <c r="H115" s="30" t="s">
-        <v>67</v>
-      </c>
-      <c r="I115" t="s">
-        <v>2129</v>
       </c>
     </row>
     <row r="116" spans="1:11" x14ac:dyDescent="0.35">
       <c r="D116" t="s">
-        <v>2130</v>
+        <v>2129</v>
       </c>
       <c r="E116">
         <v>1</v>
@@ -14598,18 +14791,18 @@
         <v>12.81</v>
       </c>
       <c r="G116" s="29" t="s">
+        <v>2130</v>
+      </c>
+      <c r="H116" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="I116" t="s">
         <v>2131</v>
-      </c>
-      <c r="H116" s="30" t="s">
-        <v>67</v>
-      </c>
-      <c r="I116" t="s">
-        <v>2132</v>
       </c>
     </row>
     <row r="117" spans="1:11" x14ac:dyDescent="0.35">
       <c r="D117" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
       <c r="E117">
         <v>1</v>
@@ -14618,18 +14811,18 @@
         <v>11.89</v>
       </c>
       <c r="G117" s="29" t="s">
+        <v>2133</v>
+      </c>
+      <c r="H117" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="I117" t="s">
         <v>2134</v>
-      </c>
-      <c r="H117" s="30" t="s">
-        <v>67</v>
-      </c>
-      <c r="I117" t="s">
-        <v>2135</v>
       </c>
     </row>
     <row r="118" spans="1:11" x14ac:dyDescent="0.35">
       <c r="D118" t="s">
-        <v>2136</v>
+        <v>2135</v>
       </c>
       <c r="E118">
         <v>1</v>
@@ -14638,13 +14831,13 @@
         <v>31.52</v>
       </c>
       <c r="G118" s="29" t="s">
+        <v>2136</v>
+      </c>
+      <c r="H118" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="I118" t="s">
         <v>2137</v>
-      </c>
-      <c r="H118" s="30" t="s">
-        <v>67</v>
-      </c>
-      <c r="I118" t="s">
-        <v>2138</v>
       </c>
     </row>
     <row r="119" spans="1:11" x14ac:dyDescent="0.35">
@@ -14652,7 +14845,7 @@
         <v>17</v>
       </c>
       <c r="D119" t="s">
-        <v>2104</v>
+        <v>2103</v>
       </c>
       <c r="E119">
         <v>1</v>
@@ -14661,18 +14854,18 @@
         <v>59.63</v>
       </c>
       <c r="G119" s="29" t="s">
+        <v>2104</v>
+      </c>
+      <c r="H119" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="I119" t="s">
         <v>2105</v>
-      </c>
-      <c r="H119" s="30" t="s">
-        <v>67</v>
-      </c>
-      <c r="I119" t="s">
-        <v>2106</v>
       </c>
     </row>
     <row r="121" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
-        <v>2139</v>
+        <v>2138</v>
       </c>
     </row>
     <row r="122" spans="1:11" x14ac:dyDescent="0.35">
@@ -14693,12 +14886,12 @@
     </row>
     <row r="124" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
-        <v>2140</v>
+        <v>2139</v>
       </c>
     </row>
     <row r="125" spans="1:11" s="18" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D125" s="18" t="s">
-        <v>2141</v>
+        <v>2140</v>
       </c>
       <c r="E125" s="18">
         <v>1</v>
@@ -14707,21 +14900,21 @@
         <v>74.069999999999993</v>
       </c>
       <c r="G125" s="29" t="s">
+        <v>2141</v>
+      </c>
+      <c r="H125" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="I125" s="18" t="s">
         <v>2142</v>
       </c>
-      <c r="H125" s="18" t="s">
-        <v>67</v>
-      </c>
-      <c r="I125" s="18" t="s">
+      <c r="K125" s="18" t="s">
         <v>2143</v>
-      </c>
-      <c r="K125" s="18" t="s">
-        <v>2144</v>
       </c>
     </row>
     <row r="126" spans="1:11" s="18" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D126" s="18" t="s">
-        <v>1885</v>
+        <v>1884</v>
       </c>
       <c r="E126" s="18">
         <v>1</v>
@@ -14730,21 +14923,21 @@
         <v>22.66</v>
       </c>
       <c r="G126" s="29" t="s">
+        <v>1885</v>
+      </c>
+      <c r="H126" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="I126" s="18" t="s">
         <v>1886</v>
       </c>
-      <c r="H126" s="18" t="s">
-        <v>67</v>
-      </c>
-      <c r="I126" s="18" t="s">
-        <v>1887</v>
-      </c>
       <c r="K126" s="18" t="s">
-        <v>2145</v>
+        <v>2144</v>
       </c>
     </row>
     <row r="127" spans="1:11" s="18" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D127" s="18" t="s">
-        <v>2146</v>
+        <v>2145</v>
       </c>
       <c r="E127" s="18">
         <v>1</v>
@@ -14753,21 +14946,21 @@
         <v>66.459999999999994</v>
       </c>
       <c r="G127" s="29" t="s">
+        <v>2146</v>
+      </c>
+      <c r="H127" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="I127" s="18" t="s">
         <v>2147</v>
       </c>
-      <c r="H127" s="18" t="s">
-        <v>67</v>
-      </c>
-      <c r="I127" s="18" t="s">
+      <c r="K127" s="18" t="s">
         <v>2148</v>
-      </c>
-      <c r="K127" s="18" t="s">
-        <v>2149</v>
       </c>
     </row>
     <row r="128" spans="1:11" s="18" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D128" s="18" t="s">
-        <v>2150</v>
+        <v>2149</v>
       </c>
       <c r="E128" s="18">
         <v>1</v>
@@ -14776,18 +14969,18 @@
         <v>18.809999999999999</v>
       </c>
       <c r="G128" s="29" t="s">
+        <v>2150</v>
+      </c>
+      <c r="H128" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="I128" s="18" t="s">
         <v>2151</v>
-      </c>
-      <c r="H128" s="18" t="s">
-        <v>67</v>
-      </c>
-      <c r="I128" s="18" t="s">
-        <v>2152</v>
       </c>
     </row>
     <row r="129" spans="1:16" s="18" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D129" s="18" t="s">
-        <v>2153</v>
+        <v>2152</v>
       </c>
       <c r="E129" s="18">
         <v>1</v>
@@ -14796,13 +14989,13 @@
         <v>81.69</v>
       </c>
       <c r="G129" s="29" t="s">
+        <v>2153</v>
+      </c>
+      <c r="H129" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="I129" s="18" t="s">
         <v>2154</v>
-      </c>
-      <c r="H129" s="18" t="s">
-        <v>67</v>
-      </c>
-      <c r="I129" s="18" t="s">
-        <v>2155</v>
       </c>
     </row>
     <row r="130" spans="1:16" s="18" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -14816,7 +15009,7 @@
         <v>22.22</v>
       </c>
       <c r="G130" s="29" t="s">
-        <v>2045</v>
+        <v>2044</v>
       </c>
       <c r="H130" s="18" t="s">
         <v>67</v>
@@ -14827,7 +15020,7 @@
     </row>
     <row r="131" spans="1:16" s="18" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D131" s="18" t="s">
-        <v>2156</v>
+        <v>2155</v>
       </c>
       <c r="E131" s="18">
         <v>2</v>
@@ -14836,13 +15029,13 @@
         <v>23.18</v>
       </c>
       <c r="G131" s="29" t="s">
-        <v>2046</v>
+        <v>2045</v>
       </c>
       <c r="H131" s="18" t="s">
         <v>67</v>
       </c>
       <c r="I131" s="18" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
     </row>
     <row r="132" spans="1:16" s="18" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -14856,7 +15049,7 @@
         <v>25.08</v>
       </c>
       <c r="G132" s="29" t="s">
-        <v>2047</v>
+        <v>2046</v>
       </c>
       <c r="H132" s="18" t="s">
         <v>67</v>
@@ -14882,12 +15075,12 @@
         <v>67</v>
       </c>
       <c r="I133" s="18" t="s">
-        <v>2158</v>
+        <v>2157</v>
       </c>
     </row>
     <row r="134" spans="1:16" s="18" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D134" s="18" t="s">
-        <v>2159</v>
+        <v>2158</v>
       </c>
       <c r="E134" s="18">
         <v>1</v>
@@ -14896,18 +15089,18 @@
         <v>25.74</v>
       </c>
       <c r="G134" s="29" t="s">
+        <v>2159</v>
+      </c>
+      <c r="H134" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="I134" s="18" t="s">
         <v>2160</v>
-      </c>
-      <c r="H134" s="18" t="s">
-        <v>67</v>
-      </c>
-      <c r="I134" s="18" t="s">
-        <v>2161</v>
       </c>
     </row>
     <row r="135" spans="1:16" s="18" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D135" s="18" t="s">
-        <v>2162</v>
+        <v>2161</v>
       </c>
       <c r="E135" s="18">
         <v>2</v>
@@ -14916,7 +15109,7 @@
         <v>143</v>
       </c>
       <c r="G135" s="29" t="s">
-        <v>2163</v>
+        <v>2162</v>
       </c>
       <c r="H135" s="18" t="s">
         <v>67</v>
@@ -14933,7 +15126,7 @@
     </row>
     <row r="138" spans="1:16" s="18" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D138" s="18" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="E138" s="18">
         <v>1</v>
@@ -14942,13 +15135,13 @@
         <v>212.22</v>
       </c>
       <c r="G138" s="29" t="s">
+        <v>2164</v>
+      </c>
+      <c r="H138" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="I138" s="18" t="s">
         <v>2165</v>
-      </c>
-      <c r="H138" s="18" t="s">
-        <v>67</v>
-      </c>
-      <c r="I138" s="18" t="s">
-        <v>2166</v>
       </c>
     </row>
     <row r="139" spans="1:16" s="18" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -14956,7 +15149,7 @@
         <v>17</v>
       </c>
       <c r="D139" s="18" t="s">
-        <v>2167</v>
+        <v>2166</v>
       </c>
       <c r="E139" s="18">
         <v>1</v>
@@ -14965,23 +15158,23 @@
         <v>22.06</v>
       </c>
       <c r="G139" s="29" t="s">
+        <v>2167</v>
+      </c>
+      <c r="H139" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="I139" s="18" t="s">
         <v>2168</v>
-      </c>
-      <c r="H139" s="18" t="s">
-        <v>67</v>
-      </c>
-      <c r="I139" s="18" t="s">
-        <v>2169</v>
       </c>
     </row>
     <row r="141" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
-        <v>2170</v>
+        <v>2169</v>
       </c>
     </row>
     <row r="142" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D142" s="18" t="s">
-        <v>2171</v>
+        <v>2170</v>
       </c>
       <c r="E142" s="18">
         <v>1</v>
@@ -14990,16 +15183,16 @@
         <v>755</v>
       </c>
       <c r="G142" s="29" t="s">
-        <v>2172</v>
+        <v>2171</v>
       </c>
       <c r="H142" s="18" t="s">
         <v>754</v>
       </c>
       <c r="I142" s="18" t="s">
+        <v>2172</v>
+      </c>
+      <c r="J142" s="18" t="s">
         <v>2173</v>
-      </c>
-      <c r="J142" s="18" t="s">
-        <v>2174</v>
       </c>
       <c r="K142" s="18"/>
       <c r="L142" s="18"/>
@@ -15010,7 +15203,7 @@
     </row>
     <row r="144" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
-        <v>2175</v>
+        <v>2174</v>
       </c>
     </row>
     <row r="145" spans="4:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -15037,7 +15230,7 @@
     </row>
     <row r="146" spans="4:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D146" s="18" t="s">
-        <v>2176</v>
+        <v>2175</v>
       </c>
       <c r="E146" s="18">
         <v>1</v>
@@ -15046,20 +15239,20 @@
         <v>24.39</v>
       </c>
       <c r="G146" s="29" t="s">
+        <v>2176</v>
+      </c>
+      <c r="H146" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="I146" s="18" t="s">
         <v>2177</v>
-      </c>
-      <c r="H146" s="18" t="s">
-        <v>67</v>
-      </c>
-      <c r="I146" s="18" t="s">
-        <v>2178</v>
       </c>
       <c r="J146" s="18"/>
       <c r="K146" s="18"/>
     </row>
     <row r="147" spans="4:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D147" s="18" t="s">
-        <v>2179</v>
+        <v>2178</v>
       </c>
       <c r="E147" s="18">
         <v>1</v>
@@ -15068,20 +15261,20 @@
         <v>26.42</v>
       </c>
       <c r="G147" s="29" t="s">
+        <v>2179</v>
+      </c>
+      <c r="H147" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="I147" s="18" t="s">
         <v>2180</v>
-      </c>
-      <c r="H147" s="18" t="s">
-        <v>67</v>
-      </c>
-      <c r="I147" s="18" t="s">
-        <v>2181</v>
       </c>
       <c r="J147" s="18"/>
       <c r="K147" s="18"/>
     </row>
     <row r="148" spans="4:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D148" s="18" t="s">
-        <v>2182</v>
+        <v>2181</v>
       </c>
       <c r="E148" s="18">
         <v>1</v>
@@ -15090,20 +15283,20 @@
         <v>32.01</v>
       </c>
       <c r="G148" s="29" t="s">
+        <v>2182</v>
+      </c>
+      <c r="H148" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="I148" s="18" t="s">
         <v>2183</v>
-      </c>
-      <c r="H148" s="18" t="s">
-        <v>67</v>
-      </c>
-      <c r="I148" s="18" t="s">
-        <v>2184</v>
       </c>
       <c r="J148" s="18"/>
       <c r="K148" s="18"/>
     </row>
     <row r="149" spans="4:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D149" s="18" t="s">
-        <v>2185</v>
+        <v>2184</v>
       </c>
       <c r="E149" s="18">
         <v>2</v>
@@ -15112,7 +15305,7 @@
         <v>8.5299999999999994</v>
       </c>
       <c r="G149" s="29" t="s">
-        <v>2186</v>
+        <v>2185</v>
       </c>
       <c r="H149" s="18" t="s">
         <v>67</v>
@@ -15125,7 +15318,7 @@
     </row>
     <row r="150" spans="4:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D150" s="18" t="s">
-        <v>2187</v>
+        <v>2186</v>
       </c>
       <c r="E150" s="18">
         <v>1</v>
@@ -15134,13 +15327,13 @@
         <v>41.35</v>
       </c>
       <c r="G150" s="29" t="s">
+        <v>2187</v>
+      </c>
+      <c r="H150" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="I150" s="18" t="s">
         <v>2188</v>
-      </c>
-      <c r="H150" s="18" t="s">
-        <v>67</v>
-      </c>
-      <c r="I150" s="18" t="s">
-        <v>2189</v>
       </c>
       <c r="J150" s="18"/>
       <c r="K150" s="18"/>
@@ -15156,7 +15349,7 @@
         <v>16.8</v>
       </c>
       <c r="G151" s="29" t="s">
-        <v>2049</v>
+        <v>2048</v>
       </c>
       <c r="H151" s="30" t="s">
         <v>67</v>
@@ -15191,7 +15384,7 @@
     </row>
     <row r="153" spans="4:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D153" s="18" t="s">
-        <v>2190</v>
+        <v>2189</v>
       </c>
       <c r="E153" s="18">
         <v>1</v>
@@ -15235,7 +15428,7 @@
     </row>
     <row r="155" spans="4:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D155" s="18" t="s">
-        <v>2191</v>
+        <v>2190</v>
       </c>
       <c r="E155" s="18">
         <v>1</v>
@@ -15244,20 +15437,20 @@
         <v>91.67</v>
       </c>
       <c r="G155" s="29" t="s">
+        <v>2191</v>
+      </c>
+      <c r="H155" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="I155" s="18" t="s">
         <v>2192</v>
-      </c>
-      <c r="H155" s="18" t="s">
-        <v>67</v>
-      </c>
-      <c r="I155" s="18" t="s">
-        <v>2193</v>
       </c>
       <c r="J155" s="18"/>
       <c r="K155" s="18"/>
     </row>
     <row r="156" spans="4:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D156" s="18" t="s">
-        <v>2194</v>
+        <v>2193</v>
       </c>
       <c r="E156" s="18">
         <v>1</v>
@@ -15266,13 +15459,13 @@
         <v>91.67</v>
       </c>
       <c r="G156" s="29" t="s">
+        <v>2194</v>
+      </c>
+      <c r="H156" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="I156" s="18" t="s">
         <v>2195</v>
-      </c>
-      <c r="H156" s="18" t="s">
-        <v>67</v>
-      </c>
-      <c r="I156" s="18" t="s">
-        <v>2196</v>
       </c>
       <c r="J156" s="18"/>
       <c r="K156" s="18"/>
@@ -15301,7 +15494,7 @@
     </row>
     <row r="158" spans="4:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D158" s="18" t="s">
-        <v>2197</v>
+        <v>2196</v>
       </c>
       <c r="E158" s="18">
         <v>2</v>
@@ -15310,18 +15503,18 @@
         <v>16.28</v>
       </c>
       <c r="G158" s="29" t="s">
+        <v>2197</v>
+      </c>
+      <c r="H158" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="I158" s="18" t="s">
         <v>2198</v>
-      </c>
-      <c r="H158" s="18" t="s">
-        <v>67</v>
-      </c>
-      <c r="I158" s="18" t="s">
-        <v>2199</v>
       </c>
     </row>
     <row r="159" spans="4:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D159" s="18" t="s">
-        <v>2200</v>
+        <v>2199</v>
       </c>
       <c r="E159" s="18">
         <v>2</v>
@@ -15330,7 +15523,7 @@
         <v>24.37</v>
       </c>
       <c r="G159" s="29" t="s">
-        <v>2201</v>
+        <v>2200</v>
       </c>
       <c r="H159" s="18" t="s">
         <v>67</v>
@@ -15341,7 +15534,7 @@
     </row>
     <row r="160" spans="4:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D160" s="18" t="s">
-        <v>2202</v>
+        <v>2201</v>
       </c>
       <c r="E160" s="18">
         <v>2</v>
@@ -15361,12 +15554,12 @@
     </row>
     <row r="162" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
-        <v>2203</v>
+        <v>2202</v>
       </c>
     </row>
     <row r="163" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D163" s="18" t="s">
-        <v>2204</v>
+        <v>2203</v>
       </c>
       <c r="E163" s="18">
         <v>1</v>
@@ -15375,21 +15568,21 @@
         <v>206</v>
       </c>
       <c r="G163" s="29" t="s">
+        <v>2204</v>
+      </c>
+      <c r="H163" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="I163" s="18" t="s">
         <v>2205</v>
       </c>
-      <c r="H163" s="18" t="s">
-        <v>67</v>
-      </c>
-      <c r="I163" s="18" t="s">
+      <c r="J163" s="18" t="s">
         <v>2206</v>
-      </c>
-      <c r="J163" s="18" t="s">
-        <v>2207</v>
       </c>
     </row>
     <row r="164" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D164" s="18" t="s">
-        <v>2208</v>
+        <v>2207</v>
       </c>
       <c r="E164" s="18">
         <v>2</v>
@@ -15398,21 +15591,21 @@
         <v>91.67</v>
       </c>
       <c r="G164" s="29" t="s">
+        <v>2208</v>
+      </c>
+      <c r="H164" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="I164" s="18" t="s">
         <v>2209</v>
       </c>
-      <c r="H164" s="18" t="s">
-        <v>67</v>
-      </c>
-      <c r="I164" s="18" t="s">
+      <c r="J164" s="18" t="s">
         <v>2210</v>
-      </c>
-      <c r="J164" s="18" t="s">
-        <v>2211</v>
       </c>
     </row>
     <row r="165" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D165" s="18" t="s">
-        <v>2212</v>
+        <v>2211</v>
       </c>
       <c r="E165" s="18">
         <v>1</v>
@@ -15421,16 +15614,16 @@
         <v>84.84</v>
       </c>
       <c r="G165" s="29" t="s">
+        <v>2212</v>
+      </c>
+      <c r="H165" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="I165" s="18" t="s">
         <v>2213</v>
       </c>
-      <c r="H165" s="18" t="s">
-        <v>67</v>
-      </c>
-      <c r="I165" s="18" t="s">
+      <c r="J165" s="18" t="s">
         <v>2214</v>
-      </c>
-      <c r="J165" s="18" t="s">
-        <v>2215</v>
       </c>
     </row>
     <row r="166" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -15456,20 +15649,20 @@
         <v>303</v>
       </c>
       <c r="J166" s="18" t="s">
-        <v>2216</v>
+        <v>2215</v>
       </c>
     </row>
     <row r="168" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
-        <v>2217</v>
+        <v>2216</v>
       </c>
     </row>
     <row r="169" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D169" s="18" t="s">
+        <v>2217</v>
+      </c>
+      <c r="G169" s="29" t="s">
         <v>2218</v>
-      </c>
-      <c r="G169" s="29" t="s">
-        <v>2219</v>
       </c>
       <c r="H169" s="30" t="s">
         <v>67</v>
@@ -15477,7 +15670,7 @@
     </row>
     <row r="170" spans="1:10" s="18" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D170" s="18" t="s">
-        <v>2220</v>
+        <v>2219</v>
       </c>
       <c r="E170" s="18">
         <v>1</v>
@@ -15486,7 +15679,7 @@
         <v>22.22</v>
       </c>
       <c r="G170" s="29" t="s">
-        <v>2045</v>
+        <v>2044</v>
       </c>
       <c r="H170" s="18" t="s">
         <v>67</v>
@@ -15515,7 +15708,7 @@
         <v>578</v>
       </c>
       <c r="J171" s="18" t="s">
-        <v>2221</v>
+        <v>2220</v>
       </c>
     </row>
     <row r="172" spans="1:10" s="18" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -15523,7 +15716,7 @@
         <v>17</v>
       </c>
       <c r="D172" s="18" t="s">
-        <v>2222</v>
+        <v>2221</v>
       </c>
       <c r="E172" s="18">
         <v>1</v>
@@ -15532,7 +15725,7 @@
         <v>181.75</v>
       </c>
       <c r="G172" s="29" t="s">
-        <v>2223</v>
+        <v>2222</v>
       </c>
       <c r="H172" s="18" t="s">
         <v>67</v>
@@ -15541,7 +15734,7 @@
         <v>307</v>
       </c>
       <c r="J172" s="18" t="s">
-        <v>2224</v>
+        <v>2223</v>
       </c>
     </row>
   </sheetData>
@@ -15708,10 +15901,10 @@
         <v>54</v>
       </c>
       <c r="G1" s="15" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>2225</v>
+        <v>2224</v>
       </c>
       <c r="I1" s="16" t="s">
         <v>1844</v>
@@ -15743,12 +15936,12 @@
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.35">
       <c r="D3" t="s">
-        <v>2226</v>
+        <v>2225</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.35">
       <c r="E4" t="s">
-        <v>2227</v>
+        <v>2226</v>
       </c>
       <c r="F4">
         <v>2</v>
@@ -15757,18 +15950,18 @@
         <v>12.18</v>
       </c>
       <c r="H4" t="s">
+        <v>2227</v>
+      </c>
+      <c r="I4" t="s">
+        <v>67</v>
+      </c>
+      <c r="J4" t="s">
         <v>2228</v>
-      </c>
-      <c r="I4" t="s">
-        <v>67</v>
-      </c>
-      <c r="J4" t="s">
-        <v>2229</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.35">
       <c r="E5" t="s">
-        <v>2230</v>
+        <v>2229</v>
       </c>
       <c r="F5">
         <v>4</v>
@@ -15777,18 +15970,18 @@
         <v>27.04</v>
       </c>
       <c r="H5" t="s">
+        <v>2230</v>
+      </c>
+      <c r="I5" t="s">
+        <v>67</v>
+      </c>
+      <c r="J5" t="s">
         <v>2231</v>
-      </c>
-      <c r="I5" t="s">
-        <v>67</v>
-      </c>
-      <c r="J5" t="s">
-        <v>2232</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.35">
       <c r="E6" t="s">
-        <v>2233</v>
+        <v>2232</v>
       </c>
       <c r="F6">
         <v>2</v>
@@ -15797,18 +15990,18 @@
         <v>10.3</v>
       </c>
       <c r="H6" t="s">
+        <v>2233</v>
+      </c>
+      <c r="I6" t="s">
+        <v>67</v>
+      </c>
+      <c r="J6" t="s">
         <v>2234</v>
-      </c>
-      <c r="I6" t="s">
-        <v>67</v>
-      </c>
-      <c r="J6" t="s">
-        <v>2235</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.35">
       <c r="E7" t="s">
-        <v>2236</v>
+        <v>2235</v>
       </c>
       <c r="F7">
         <v>1</v>
@@ -15817,18 +16010,18 @@
         <v>30.21</v>
       </c>
       <c r="H7" t="s">
-        <v>2234</v>
+        <v>2233</v>
       </c>
       <c r="I7" t="s">
         <v>67</v>
       </c>
       <c r="J7" t="s">
-        <v>2237</v>
+        <v>2236</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.35">
       <c r="E8" t="s">
-        <v>2238</v>
+        <v>2237</v>
       </c>
       <c r="F8">
         <v>2</v>
@@ -15837,18 +16030,18 @@
         <v>10.93</v>
       </c>
       <c r="H8" t="s">
+        <v>2238</v>
+      </c>
+      <c r="I8" t="s">
+        <v>67</v>
+      </c>
+      <c r="J8" t="s">
         <v>2239</v>
-      </c>
-      <c r="I8" t="s">
-        <v>67</v>
-      </c>
-      <c r="J8" t="s">
-        <v>2240</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.35">
       <c r="E9" t="s">
-        <v>2241</v>
+        <v>2240</v>
       </c>
       <c r="F9">
         <v>4</v>
@@ -15857,18 +16050,18 @@
         <v>20.38</v>
       </c>
       <c r="H9" t="s">
-        <v>2242</v>
+        <v>2241</v>
       </c>
       <c r="I9" t="s">
         <v>67</v>
       </c>
       <c r="J9" t="s">
-        <v>2033</v>
+        <v>2032</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.35">
       <c r="E10" t="s">
-        <v>2243</v>
+        <v>2242</v>
       </c>
       <c r="F10">
         <v>4</v>
@@ -15877,18 +16070,18 @@
         <v>67.239999999999995</v>
       </c>
       <c r="H10" s="29" t="s">
+        <v>2243</v>
+      </c>
+      <c r="I10" t="s">
+        <v>67</v>
+      </c>
+      <c r="J10" t="s">
         <v>2244</v>
-      </c>
-      <c r="I10" t="s">
-        <v>67</v>
-      </c>
-      <c r="J10" t="s">
-        <v>2245</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.35">
       <c r="E11" t="s">
-        <v>2246</v>
+        <v>2245</v>
       </c>
       <c r="F11">
         <v>2</v>
@@ -15897,18 +16090,18 @@
         <v>25.95</v>
       </c>
       <c r="H11" t="s">
+        <v>2246</v>
+      </c>
+      <c r="I11" t="s">
+        <v>67</v>
+      </c>
+      <c r="J11" t="s">
         <v>2247</v>
-      </c>
-      <c r="I11" t="s">
-        <v>67</v>
-      </c>
-      <c r="J11" t="s">
-        <v>2248</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.35">
       <c r="E12" t="s">
-        <v>2249</v>
+        <v>2248</v>
       </c>
       <c r="F12">
         <v>4</v>
@@ -15917,13 +16110,13 @@
         <v>34.94</v>
       </c>
       <c r="H12" t="s">
-        <v>2247</v>
+        <v>2246</v>
       </c>
       <c r="I12" t="s">
         <v>67</v>
       </c>
       <c r="J12" t="s">
-        <v>2250</v>
+        <v>2249</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.35">
@@ -15931,7 +16124,7 @@
         <v>17</v>
       </c>
       <c r="E13" t="s">
-        <v>2251</v>
+        <v>2250</v>
       </c>
       <c r="F13">
         <v>2</v>
@@ -15940,18 +16133,18 @@
         <v>37.299999999999997</v>
       </c>
       <c r="H13" t="s">
-        <v>2247</v>
+        <v>2246</v>
       </c>
       <c r="I13" t="s">
         <v>67</v>
       </c>
       <c r="J13" t="s">
-        <v>2252</v>
+        <v>2251</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.35">
       <c r="E15" t="s">
-        <v>2253</v>
+        <v>2252</v>
       </c>
       <c r="F15">
         <v>1</v>
@@ -15960,18 +16153,18 @@
         <v>55.78</v>
       </c>
       <c r="H15" t="s">
-        <v>2254</v>
+        <v>2253</v>
       </c>
       <c r="I15" t="s">
         <v>1206</v>
       </c>
       <c r="J15" t="s">
-        <v>2255</v>
+        <v>2254</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.35">
       <c r="E16" t="s">
-        <v>2256</v>
+        <v>2255</v>
       </c>
       <c r="F16">
         <v>1</v>
@@ -15980,23 +16173,23 @@
         <v>20</v>
       </c>
       <c r="H16" t="s">
-        <v>2257</v>
+        <v>2256</v>
       </c>
       <c r="I16" t="s">
         <v>754</v>
       </c>
       <c r="J16" t="s">
-        <v>2258</v>
+        <v>2257</v>
       </c>
     </row>
     <row r="18" spans="3:13" x14ac:dyDescent="0.35">
       <c r="C18" t="s">
-        <v>2259</v>
+        <v>2258</v>
       </c>
     </row>
     <row r="19" spans="3:13" x14ac:dyDescent="0.35">
       <c r="D19" t="s">
-        <v>2260</v>
+        <v>2259</v>
       </c>
       <c r="G19">
         <f>SUMPRODUCT(F20:F24,G20:G24)</f>
@@ -16005,7 +16198,7 @@
     </row>
     <row r="20" spans="3:13" x14ac:dyDescent="0.35">
       <c r="E20" t="s">
-        <v>2249</v>
+        <v>2248</v>
       </c>
       <c r="F20">
         <v>5</v>
@@ -16014,18 +16207,18 @@
         <v>34.94</v>
       </c>
       <c r="H20" s="29" t="s">
-        <v>2247</v>
+        <v>2246</v>
       </c>
       <c r="I20" t="s">
         <v>67</v>
       </c>
       <c r="J20" t="s">
-        <v>2250</v>
+        <v>2249</v>
       </c>
     </row>
     <row r="21" spans="3:13" x14ac:dyDescent="0.35">
       <c r="E21" t="s">
-        <v>2246</v>
+        <v>2245</v>
       </c>
       <c r="F21">
         <v>1</v>
@@ -16034,18 +16227,18 @@
         <v>25.95</v>
       </c>
       <c r="H21" t="s">
+        <v>2246</v>
+      </c>
+      <c r="I21" t="s">
+        <v>67</v>
+      </c>
+      <c r="J21" t="s">
         <v>2247</v>
-      </c>
-      <c r="I21" t="s">
-        <v>67</v>
-      </c>
-      <c r="J21" t="s">
-        <v>2248</v>
       </c>
     </row>
     <row r="22" spans="3:13" x14ac:dyDescent="0.35">
       <c r="E22" t="s">
-        <v>2261</v>
+        <v>2260</v>
       </c>
       <c r="F22">
         <v>2</v>
@@ -16054,18 +16247,18 @@
         <v>24.35</v>
       </c>
       <c r="H22" s="29" t="s">
+        <v>2261</v>
+      </c>
+      <c r="I22" t="s">
+        <v>67</v>
+      </c>
+      <c r="J22" t="s">
         <v>2262</v>
-      </c>
-      <c r="I22" t="s">
-        <v>67</v>
-      </c>
-      <c r="J22" t="s">
-        <v>2263</v>
       </c>
     </row>
     <row r="23" spans="3:13" x14ac:dyDescent="0.35">
       <c r="E23" t="s">
-        <v>2264</v>
+        <v>2263</v>
       </c>
       <c r="F23">
         <v>3</v>
@@ -16074,16 +16267,16 @@
         <v>31.38</v>
       </c>
       <c r="H23" s="29" t="s">
+        <v>2264</v>
+      </c>
+      <c r="I23" t="s">
+        <v>67</v>
+      </c>
+      <c r="J23" t="s">
         <v>2265</v>
       </c>
-      <c r="I23" t="s">
-        <v>67</v>
-      </c>
-      <c r="J23" t="s">
+      <c r="M23" t="s">
         <v>2266</v>
-      </c>
-      <c r="M23" t="s">
-        <v>2267</v>
       </c>
     </row>
     <row r="24" spans="3:13" x14ac:dyDescent="0.35">
@@ -16091,7 +16284,7 @@
         <v>17</v>
       </c>
       <c r="E24" t="s">
-        <v>2268</v>
+        <v>2267</v>
       </c>
       <c r="F24">
         <v>1</v>
@@ -16100,18 +16293,18 @@
         <v>16.23</v>
       </c>
       <c r="H24" s="29" t="s">
+        <v>2268</v>
+      </c>
+      <c r="I24" t="s">
+        <v>67</v>
+      </c>
+      <c r="J24" t="s">
         <v>2269</v>
-      </c>
-      <c r="I24" t="s">
-        <v>67</v>
-      </c>
-      <c r="J24" t="s">
-        <v>2270</v>
       </c>
     </row>
     <row r="25" spans="3:13" x14ac:dyDescent="0.35">
       <c r="D25" t="s">
-        <v>2271</v>
+        <v>2270</v>
       </c>
       <c r="G25">
         <f>SUMPRODUCT(F26:F30,G26:G30)</f>
@@ -16120,7 +16313,7 @@
     </row>
     <row r="26" spans="3:13" x14ac:dyDescent="0.35">
       <c r="E26" t="s">
-        <v>2272</v>
+        <v>2271</v>
       </c>
       <c r="F26">
         <v>5</v>
@@ -16130,13 +16323,13 @@
         <v>14.84</v>
       </c>
       <c r="H26" s="29" t="s">
-        <v>2273</v>
+        <v>2272</v>
       </c>
       <c r="I26" t="s">
         <v>1206</v>
       </c>
       <c r="J26" t="s">
-        <v>2250</v>
+        <v>2249</v>
       </c>
       <c r="K26">
         <v>5</v>
@@ -16144,7 +16337,7 @@
     </row>
     <row r="27" spans="3:13" x14ac:dyDescent="0.35">
       <c r="E27" t="s">
-        <v>2274</v>
+        <v>2273</v>
       </c>
       <c r="F27">
         <v>1</v>
@@ -16154,13 +16347,13 @@
         <v>10.600000000000001</v>
       </c>
       <c r="H27" s="29" t="s">
-        <v>2273</v>
+        <v>2272</v>
       </c>
       <c r="I27" t="s">
         <v>1206</v>
       </c>
       <c r="J27" t="s">
-        <v>2248</v>
+        <v>2247</v>
       </c>
       <c r="K27">
         <v>5</v>
@@ -16168,7 +16361,7 @@
     </row>
     <row r="28" spans="3:13" x14ac:dyDescent="0.35">
       <c r="E28" t="s">
-        <v>2275</v>
+        <v>2274</v>
       </c>
       <c r="F28">
         <v>2</v>
@@ -16178,13 +16371,13 @@
         <v>9.5400000000000009</v>
       </c>
       <c r="H28" s="29" t="s">
-        <v>2273</v>
+        <v>2272</v>
       </c>
       <c r="I28" t="s">
         <v>1206</v>
       </c>
       <c r="J28" t="s">
-        <v>2263</v>
+        <v>2262</v>
       </c>
       <c r="K28">
         <v>5</v>
@@ -16192,7 +16385,7 @@
     </row>
     <row r="29" spans="3:13" x14ac:dyDescent="0.35">
       <c r="E29" t="s">
-        <v>2276</v>
+        <v>2275</v>
       </c>
       <c r="F29">
         <v>3</v>
@@ -16202,13 +16395,13 @@
         <v>11.66</v>
       </c>
       <c r="H29" s="29" t="s">
-        <v>2273</v>
+        <v>2272</v>
       </c>
       <c r="I29" t="s">
         <v>1206</v>
       </c>
       <c r="J29" t="s">
-        <v>2266</v>
+        <v>2265</v>
       </c>
       <c r="K29">
         <v>5</v>
@@ -16219,7 +16412,7 @@
         <v>17</v>
       </c>
       <c r="E30" t="s">
-        <v>2277</v>
+        <v>2276</v>
       </c>
       <c r="F30">
         <v>1</v>
@@ -16229,13 +16422,13 @@
         <v>4.7700000000000005</v>
       </c>
       <c r="H30" s="29" t="s">
-        <v>2273</v>
+        <v>2272</v>
       </c>
       <c r="I30" t="s">
         <v>1206</v>
       </c>
       <c r="J30" t="s">
-        <v>2270</v>
+        <v>2269</v>
       </c>
       <c r="K30">
         <v>5</v>
@@ -16243,7 +16436,7 @@
     </row>
     <row r="31" spans="3:13" x14ac:dyDescent="0.35">
       <c r="D31" t="s">
-        <v>2278</v>
+        <v>2277</v>
       </c>
       <c r="G31">
         <f>SUMPRODUCT(F32:F33,G32:G33)</f>
@@ -16253,7 +16446,7 @@
     </row>
     <row r="32" spans="3:13" x14ac:dyDescent="0.35">
       <c r="E32" t="s">
-        <v>2279</v>
+        <v>2278</v>
       </c>
       <c r="F32">
         <v>6</v>
@@ -16262,16 +16455,16 @@
         <v>15.36</v>
       </c>
       <c r="H32" s="29" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="I32" t="s">
         <v>1206</v>
       </c>
       <c r="J32" t="s">
+        <v>2280</v>
+      </c>
+      <c r="M32" t="s">
         <v>2281</v>
-      </c>
-      <c r="M32" t="s">
-        <v>2282</v>
       </c>
     </row>
     <row r="33" spans="2:13" x14ac:dyDescent="0.35">
@@ -16279,7 +16472,7 @@
         <v>17</v>
       </c>
       <c r="E33" t="s">
-        <v>2283</v>
+        <v>2282</v>
       </c>
       <c r="F33">
         <v>5</v>
@@ -16288,21 +16481,21 @@
         <v>11.05</v>
       </c>
       <c r="H33" s="29" t="s">
-        <v>2284</v>
+        <v>2283</v>
       </c>
       <c r="I33" t="s">
         <v>1206</v>
       </c>
       <c r="J33" t="s">
-        <v>2281</v>
+        <v>2280</v>
       </c>
       <c r="M33" t="s">
-        <v>2285</v>
+        <v>2284</v>
       </c>
     </row>
     <row r="34" spans="2:13" x14ac:dyDescent="0.35">
       <c r="D34" t="s">
-        <v>2286</v>
+        <v>2285</v>
       </c>
       <c r="G34">
         <f>SUMPRODUCT(F35:F38,G35:G38)</f>
@@ -16311,7 +16504,7 @@
     </row>
     <row r="35" spans="2:13" x14ac:dyDescent="0.35">
       <c r="E35" t="s">
-        <v>2241</v>
+        <v>2240</v>
       </c>
       <c r="F35">
         <v>2</v>
@@ -16320,21 +16513,21 @@
         <v>20.38</v>
       </c>
       <c r="H35" s="29" t="s">
-        <v>2242</v>
+        <v>2241</v>
       </c>
       <c r="I35" t="s">
         <v>67</v>
       </c>
       <c r="J35" t="s">
-        <v>2033</v>
+        <v>2032</v>
       </c>
       <c r="M35" t="s">
-        <v>2287</v>
+        <v>2286</v>
       </c>
     </row>
     <row r="36" spans="2:13" x14ac:dyDescent="0.35">
       <c r="E36" t="s">
-        <v>2288</v>
+        <v>2287</v>
       </c>
       <c r="F36">
         <v>7</v>
@@ -16343,18 +16536,18 @@
         <v>12.04</v>
       </c>
       <c r="H36" s="29" t="s">
-        <v>2289</v>
+        <v>2288</v>
       </c>
       <c r="I36" t="s">
         <v>1206</v>
       </c>
       <c r="J36" t="s">
-        <v>2290</v>
+        <v>2289</v>
       </c>
     </row>
     <row r="37" spans="2:13" x14ac:dyDescent="0.35">
       <c r="E37" t="s">
-        <v>2291</v>
+        <v>2290</v>
       </c>
       <c r="F37">
         <v>1</v>
@@ -16363,13 +16556,13 @@
         <v>11.47</v>
       </c>
       <c r="H37" s="29" t="s">
-        <v>2292</v>
+        <v>2291</v>
       </c>
       <c r="I37" t="s">
         <v>1206</v>
       </c>
       <c r="J37" t="s">
-        <v>2293</v>
+        <v>2292</v>
       </c>
     </row>
     <row r="38" spans="2:13" x14ac:dyDescent="0.35">
@@ -16377,7 +16570,7 @@
         <v>17</v>
       </c>
       <c r="E38" t="s">
-        <v>2294</v>
+        <v>2293</v>
       </c>
       <c r="F38">
         <v>2</v>
@@ -16386,39 +16579,39 @@
         <v>8.75</v>
       </c>
       <c r="H38" s="29" t="s">
-        <v>2295</v>
+        <v>2294</v>
       </c>
       <c r="I38" t="s">
         <v>1206</v>
       </c>
       <c r="J38" t="s">
-        <v>2296</v>
+        <v>2295</v>
       </c>
     </row>
     <row r="39" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B39" t="s">
-        <v>2297</v>
+        <v>2296</v>
       </c>
     </row>
     <row r="40" spans="2:13" x14ac:dyDescent="0.35">
       <c r="C40" t="s">
-        <v>2298</v>
+        <v>2297</v>
       </c>
     </row>
     <row r="41" spans="2:13" x14ac:dyDescent="0.35">
       <c r="E41" t="s">
-        <v>2299</v>
+        <v>2298</v>
       </c>
       <c r="K41">
         <v>14</v>
       </c>
       <c r="M41" t="s">
-        <v>2300</v>
+        <v>2299</v>
       </c>
     </row>
     <row r="42" spans="2:13" x14ac:dyDescent="0.35">
       <c r="E42" t="s">
-        <v>2301</v>
+        <v>2300</v>
       </c>
       <c r="I42" t="s">
         <v>67</v>
@@ -16427,12 +16620,12 @@
         <v>14</v>
       </c>
       <c r="M42" t="s">
-        <v>2302</v>
+        <v>2301</v>
       </c>
     </row>
     <row r="43" spans="2:13" x14ac:dyDescent="0.35">
       <c r="E43" t="s">
-        <v>2303</v>
+        <v>2302</v>
       </c>
       <c r="I43" t="s">
         <v>67</v>
@@ -16441,12 +16634,12 @@
         <v>14</v>
       </c>
       <c r="M43" t="s">
-        <v>2304</v>
+        <v>2303</v>
       </c>
     </row>
     <row r="44" spans="2:13" x14ac:dyDescent="0.35">
       <c r="E44" t="s">
-        <v>2305</v>
+        <v>2304</v>
       </c>
       <c r="I44" t="s">
         <v>67</v>
@@ -16455,12 +16648,12 @@
         <v>14</v>
       </c>
       <c r="M44" t="s">
-        <v>2306</v>
+        <v>2305</v>
       </c>
     </row>
     <row r="45" spans="2:13" x14ac:dyDescent="0.35">
       <c r="E45" t="s">
-        <v>2307</v>
+        <v>2306</v>
       </c>
       <c r="I45" t="s">
         <v>67</v>
@@ -16469,12 +16662,12 @@
         <v>14</v>
       </c>
       <c r="M45" t="s">
-        <v>2308</v>
+        <v>2307</v>
       </c>
     </row>
     <row r="46" spans="2:13" x14ac:dyDescent="0.35">
       <c r="E46" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
       <c r="I46" t="s">
         <v>67</v>
@@ -16483,7 +16676,7 @@
         <v>14</v>
       </c>
       <c r="M46" t="s">
-        <v>2310</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="47" spans="2:13" x14ac:dyDescent="0.35">
@@ -16491,7 +16684,7 @@
         <v>17</v>
       </c>
       <c r="E47" t="s">
-        <v>2311</v>
+        <v>2310</v>
       </c>
       <c r="I47" t="s">
         <v>67</v>
@@ -16500,17 +16693,17 @@
         <v>14</v>
       </c>
       <c r="M47" t="s">
-        <v>2312</v>
+        <v>2311</v>
       </c>
     </row>
     <row r="48" spans="2:13" x14ac:dyDescent="0.35">
       <c r="C48" t="s">
-        <v>2313</v>
+        <v>2312</v>
       </c>
     </row>
     <row r="49" spans="3:11" x14ac:dyDescent="0.35">
       <c r="D49" t="s">
-        <v>2313</v>
+        <v>2312</v>
       </c>
     </row>
     <row r="50" spans="3:11" x14ac:dyDescent="0.35">
@@ -16518,7 +16711,7 @@
         <v>17</v>
       </c>
       <c r="E50" t="s">
-        <v>2314</v>
+        <v>2313</v>
       </c>
       <c r="F50">
         <v>3</v>
@@ -16532,12 +16725,12 @@
     </row>
     <row r="51" spans="3:11" x14ac:dyDescent="0.35">
       <c r="E51" t="s">
-        <v>2299</v>
+        <v>2298</v>
       </c>
     </row>
     <row r="52" spans="3:11" x14ac:dyDescent="0.35">
       <c r="E52" t="s">
-        <v>2305</v>
+        <v>2304</v>
       </c>
     </row>
     <row r="53" spans="3:11" x14ac:dyDescent="0.35">
@@ -16545,12 +16738,12 @@
         <v>17</v>
       </c>
       <c r="E53" t="s">
-        <v>2311</v>
+        <v>2310</v>
       </c>
     </row>
     <row r="54" spans="3:11" x14ac:dyDescent="0.35">
       <c r="E54" t="s">
-        <v>2243</v>
+        <v>2242</v>
       </c>
       <c r="F54">
         <v>2</v>
@@ -16559,13 +16752,13 @@
         <v>67.239999999999995</v>
       </c>
       <c r="H54" s="29" t="s">
+        <v>2243</v>
+      </c>
+      <c r="I54" t="s">
+        <v>67</v>
+      </c>
+      <c r="J54" t="s">
         <v>2244</v>
-      </c>
-      <c r="I54" t="s">
-        <v>67</v>
-      </c>
-      <c r="J54" t="s">
-        <v>2245</v>
       </c>
     </row>
   </sheetData>
@@ -16641,10 +16834,10 @@
         <v>54</v>
       </c>
       <c r="G1" s="15" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>2225</v>
+        <v>2224</v>
       </c>
       <c r="I1" s="16" t="s">
         <v>1844</v>
@@ -16676,22 +16869,22 @@
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.35">
       <c r="E3" t="s">
-        <v>2315</v>
+        <v>2314</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.35">
       <c r="C4" t="s">
-        <v>2316</v>
+        <v>2315</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.35">
       <c r="J5" t="s">
-        <v>2015</v>
+        <v>2014</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.35">
       <c r="J6" t="s">
-        <v>2214</v>
+        <v>2213</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.35">
@@ -16699,15 +16892,15 @@
         <v>17</v>
       </c>
       <c r="E7" t="s">
+        <v>2316</v>
+      </c>
+      <c r="J7" t="s">
         <v>2317</v>
-      </c>
-      <c r="J7" t="s">
-        <v>2318</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.35">
       <c r="D9" t="s">
-        <v>2319</v>
+        <v>2318</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.35">
@@ -16734,13 +16927,13 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B1" t="s">
+        <v>2319</v>
+      </c>
+      <c r="C1" t="s">
         <v>2320</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>2321</v>
-      </c>
-      <c r="D1" t="s">
-        <v>2322</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
@@ -16748,10 +16941,10 @@
         <v>515</v>
       </c>
       <c r="B2" t="s">
+        <v>2322</v>
+      </c>
+      <c r="C2" t="s">
         <v>2323</v>
-      </c>
-      <c r="C2" t="s">
-        <v>2324</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
@@ -16759,10 +16952,10 @@
         <v>583</v>
       </c>
       <c r="B3" t="s">
+        <v>2324</v>
+      </c>
+      <c r="C3" t="s">
         <v>2325</v>
-      </c>
-      <c r="C3" t="s">
-        <v>2326</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
@@ -16770,10 +16963,10 @@
         <v>566</v>
       </c>
       <c r="B4" t="s">
+        <v>2326</v>
+      </c>
+      <c r="D4" t="s">
         <v>2327</v>
-      </c>
-      <c r="D4" t="s">
-        <v>2328</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
@@ -16781,10 +16974,10 @@
         <v>570</v>
       </c>
       <c r="B5" t="s">
+        <v>2328</v>
+      </c>
+      <c r="D5" t="s">
         <v>2329</v>
-      </c>
-      <c r="D5" t="s">
-        <v>2330</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
@@ -16792,10 +16985,10 @@
         <v>1084</v>
       </c>
       <c r="B6" t="s">
+        <v>2330</v>
+      </c>
+      <c r="D6" t="s">
         <v>2331</v>
-      </c>
-      <c r="D6" t="s">
-        <v>2332</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
@@ -16815,7 +17008,7 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>2333</v>
+        <v>2332</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
@@ -16823,7 +17016,7 @@
         <v>533</v>
       </c>
       <c r="B11" t="s">
-        <v>2334</v>
+        <v>2333</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
@@ -16833,12 +17026,12 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>2333</v>
+        <v>2332</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>2335</v>
+        <v>2334</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
@@ -16846,15 +17039,15 @@
         <v>547</v>
       </c>
       <c r="B15" t="s">
+        <v>2335</v>
+      </c>
+      <c r="D15" t="s">
         <v>2336</v>
-      </c>
-      <c r="D15" t="s">
-        <v>2337</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>2338</v>
+        <v>2337</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
@@ -16872,18 +17065,18 @@
         <v>1268</v>
       </c>
       <c r="B19" t="s">
+        <v>2338</v>
+      </c>
+      <c r="D19" t="s">
         <v>2339</v>
-      </c>
-      <c r="D19" t="s">
-        <v>2340</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
+        <v>2340</v>
+      </c>
+      <c r="B20" t="s">
         <v>2341</v>
-      </c>
-      <c r="B20" t="s">
-        <v>2342</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
@@ -16891,7 +17084,7 @@
         <v>1394</v>
       </c>
       <c r="B21" t="s">
-        <v>2343</v>
+        <v>2342</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
@@ -16899,7 +17092,7 @@
         <v>766</v>
       </c>
       <c r="B22" t="s">
-        <v>2344</v>
+        <v>2343</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
@@ -16907,18 +17100,18 @@
         <v>552</v>
       </c>
       <c r="B23" t="s">
+        <v>2344</v>
+      </c>
+      <c r="D23" t="s">
         <v>2345</v>
-      </c>
-      <c r="D23" t="s">
-        <v>2346</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
+        <v>2346</v>
+      </c>
+      <c r="B24" t="s">
         <v>2347</v>
-      </c>
-      <c r="B24" t="s">
-        <v>2348</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
@@ -16926,7 +17119,7 @@
         <v>1397</v>
       </c>
       <c r="B25" t="s">
-        <v>2349</v>
+        <v>2348</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.35">
@@ -16934,10 +17127,10 @@
         <v>562</v>
       </c>
       <c r="B26" t="s">
-        <v>2345</v>
+        <v>2344</v>
       </c>
       <c r="D26" t="s">
-        <v>2350</v>
+        <v>2349</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
@@ -16947,10 +17140,10 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
+        <v>2350</v>
+      </c>
+      <c r="B28" t="s">
         <v>2351</v>
-      </c>
-      <c r="B28" t="s">
-        <v>2352</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.35">
@@ -16958,28 +17151,28 @@
         <v>557</v>
       </c>
       <c r="B29" t="s">
-        <v>2345</v>
+        <v>2344</v>
       </c>
       <c r="D29" t="s">
-        <v>2353</v>
+        <v>2352</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
+        <v>2353</v>
+      </c>
+      <c r="B30" t="s">
         <v>2354</v>
-      </c>
-      <c r="B30" t="s">
-        <v>2355</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>2356</v>
+        <v>2355</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>2356</v>
+        <v>2355</v>
       </c>
     </row>
   </sheetData>
@@ -17008,7 +17201,7 @@
         <v>931</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1968</v>
+        <v>1967</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>53</v>
@@ -17017,7 +17210,7 @@
         <v>54</v>
       </c>
       <c r="F1" s="12" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>56</v>
@@ -17034,7 +17227,7 @@
     </row>
     <row r="2" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D2" t="s">
-        <v>2357</v>
+        <v>2356</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -17043,15 +17236,15 @@
         <v>280000</v>
       </c>
       <c r="H2" t="s">
+        <v>2357</v>
+      </c>
+      <c r="J2" t="s">
         <v>2358</v>
-      </c>
-      <c r="J2" t="s">
-        <v>2359</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="D3" t="s">
-        <v>2360</v>
+        <v>2359</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -17066,7 +17259,7 @@
         <v>716</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>2361</v>
+        <v>2360</v>
       </c>
       <c r="F4" s="30">
         <v>5500</v>
@@ -17086,17 +17279,17 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
-        <v>2362</v>
+        <v>2361</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>2363</v>
+        <v>2362</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="D9" t="s">
-        <v>2364</v>
+        <v>2363</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -17105,7 +17298,7 @@
         <v>261.19</v>
       </c>
       <c r="G9" s="29" t="s">
-        <v>2365</v>
+        <v>2364</v>
       </c>
       <c r="H9" t="s">
         <v>844</v>
@@ -17113,7 +17306,7 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="D10" t="s">
-        <v>2366</v>
+        <v>2365</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -17122,7 +17315,7 @@
         <v>239.95</v>
       </c>
       <c r="G10" s="29" t="s">
-        <v>2367</v>
+        <v>2366</v>
       </c>
       <c r="H10" t="s">
         <v>844</v>
@@ -17130,7 +17323,7 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="D12" t="s">
-        <v>2368</v>
+        <v>2367</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -17139,7 +17332,7 @@
         <v>83.99</v>
       </c>
       <c r="G12" s="29" t="s">
-        <v>2369</v>
+        <v>2368</v>
       </c>
       <c r="H12" t="s">
         <v>844</v>
@@ -17147,7 +17340,7 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="D13" t="s">
-        <v>2370</v>
+        <v>2369</v>
       </c>
       <c r="E13">
         <v>1</v>
@@ -17156,7 +17349,7 @@
         <v>47.6</v>
       </c>
       <c r="G13" s="29" t="s">
-        <v>2371</v>
+        <v>2370</v>
       </c>
       <c r="H13" t="s">
         <v>844</v>
@@ -17164,7 +17357,7 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="D14" t="s">
-        <v>2372</v>
+        <v>2371</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -17173,7 +17366,7 @@
         <v>53.95</v>
       </c>
       <c r="G14" s="29" t="s">
-        <v>2373</v>
+        <v>2372</v>
       </c>
       <c r="H14" t="s">
         <v>844</v>
@@ -17181,7 +17374,7 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="D15" t="s">
-        <v>2374</v>
+        <v>2373</v>
       </c>
       <c r="E15">
         <v>1</v>
@@ -17190,7 +17383,7 @@
         <v>53.75</v>
       </c>
       <c r="G15" s="29" t="s">
-        <v>2375</v>
+        <v>2374</v>
       </c>
       <c r="H15" t="s">
         <v>844</v>
@@ -17198,7 +17391,7 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="D16" t="s">
-        <v>2376</v>
+        <v>2375</v>
       </c>
       <c r="E16">
         <v>1</v>
@@ -17207,7 +17400,7 @@
         <v>79.989999999999995</v>
       </c>
       <c r="G16" s="29" t="s">
-        <v>2377</v>
+        <v>2376</v>
       </c>
       <c r="H16" t="s">
         <v>844</v>
@@ -17215,7 +17408,7 @@
     </row>
     <row r="17" spans="4:8" x14ac:dyDescent="0.35">
       <c r="D17" t="s">
-        <v>2378</v>
+        <v>2377</v>
       </c>
       <c r="E17">
         <v>1</v>
@@ -17224,7 +17417,7 @@
         <v>149.94999999999999</v>
       </c>
       <c r="G17" s="29" t="s">
-        <v>2379</v>
+        <v>2378</v>
       </c>
       <c r="H17" t="s">
         <v>844</v>
@@ -17232,7 +17425,7 @@
     </row>
     <row r="19" spans="4:8" x14ac:dyDescent="0.35">
       <c r="D19" t="s">
-        <v>2380</v>
+        <v>2379</v>
       </c>
       <c r="E19">
         <v>1</v>
@@ -17241,7 +17434,7 @@
         <v>79.989999999999995</v>
       </c>
       <c r="G19" s="29" t="s">
-        <v>2381</v>
+        <v>2380</v>
       </c>
       <c r="H19" t="s">
         <v>844</v>
@@ -17277,22 +17470,22 @@
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
+        <v>2381</v>
+      </c>
+      <c r="B1" t="s">
         <v>2382</v>
-      </c>
-      <c r="B1" t="s">
-        <v>2383</v>
       </c>
       <c r="C1" t="s">
         <v>931</v>
       </c>
       <c r="D1" t="s">
+        <v>2383</v>
+      </c>
+      <c r="E1" s="22" t="s">
         <v>2384</v>
       </c>
-      <c r="E1" s="22" t="s">
+      <c r="F1" s="36" t="s">
         <v>2385</v>
-      </c>
-      <c r="F1" s="36" t="s">
-        <v>2386</v>
       </c>
       <c r="G1" s="22" t="s">
         <v>56</v>
@@ -17301,48 +17494,48 @@
         <v>57</v>
       </c>
       <c r="I1" s="14" t="s">
+        <v>2386</v>
+      </c>
+      <c r="J1" t="s">
         <v>2387</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>2388</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>2389</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>2390</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>2391</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
+        <v>2385</v>
+      </c>
+      <c r="P1" t="s">
         <v>2392</v>
-      </c>
-      <c r="O1" t="s">
-        <v>2386</v>
-      </c>
-      <c r="P1" t="s">
-        <v>2393</v>
       </c>
     </row>
     <row r="3" spans="1:16" s="18" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="18" t="s">
-        <v>2394</v>
+        <v>2393</v>
       </c>
       <c r="F3" s="35"/>
       <c r="G3" s="29" t="s">
-        <v>2395</v>
+        <v>2394</v>
       </c>
       <c r="H3" s="18" t="s">
         <v>824</v>
       </c>
       <c r="M3" s="18" t="s">
-        <v>2396</v>
+        <v>2395</v>
       </c>
     </row>
     <row r="4" spans="1:16" s="18" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D4" s="23" t="s">
-        <v>2397</v>
+        <v>2396</v>
       </c>
       <c r="E4" s="18">
         <v>3</v>
@@ -17351,23 +17544,23 @@
         <v>14.77</v>
       </c>
       <c r="G4" s="29" t="s">
-        <v>2398</v>
+        <v>2397</v>
       </c>
       <c r="H4" s="24" t="s">
         <v>824</v>
       </c>
       <c r="I4" s="23" t="s">
+        <v>2398</v>
+      </c>
+      <c r="J4" s="23" t="s">
         <v>2399</v>
-      </c>
-      <c r="J4" s="23" t="s">
-        <v>2400</v>
       </c>
       <c r="L4" s="23"/>
       <c r="N4" s="23"/>
     </row>
     <row r="5" spans="1:16" s="18" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D5" s="23" t="s">
-        <v>2401</v>
+        <v>2400</v>
       </c>
       <c r="E5" s="18">
         <v>3</v>
@@ -17376,23 +17569,23 @@
         <v>16.52</v>
       </c>
       <c r="G5" s="29" t="s">
-        <v>2402</v>
+        <v>2401</v>
       </c>
       <c r="H5" s="24" t="s">
         <v>824</v>
       </c>
       <c r="I5" s="23" t="s">
+        <v>2402</v>
+      </c>
+      <c r="J5" s="23" t="s">
         <v>2403</v>
-      </c>
-      <c r="J5" s="23" t="s">
-        <v>2404</v>
       </c>
       <c r="L5" s="23"/>
       <c r="N5" s="23"/>
     </row>
     <row r="6" spans="1:16" s="18" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D6" s="18" t="s">
-        <v>2405</v>
+        <v>2404</v>
       </c>
       <c r="E6" s="18">
         <v>2</v>
@@ -17401,13 +17594,13 @@
         <v>9.09</v>
       </c>
       <c r="G6" s="29" t="s">
-        <v>2406</v>
+        <v>2405</v>
       </c>
       <c r="H6" s="18" t="s">
         <v>844</v>
       </c>
       <c r="M6" s="18" t="s">
-        <v>2407</v>
+        <v>2406</v>
       </c>
     </row>
     <row r="7" spans="1:16" s="18" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -17415,7 +17608,7 @@
         <v>17</v>
       </c>
       <c r="D7" s="18" t="s">
-        <v>2408</v>
+        <v>2407</v>
       </c>
       <c r="E7" s="18">
         <v>1</v>
@@ -17424,27 +17617,27 @@
         <v>9.99</v>
       </c>
       <c r="G7" s="29" t="s">
-        <v>2409</v>
+        <v>2408</v>
       </c>
       <c r="H7" s="18" t="s">
         <v>844</v>
       </c>
       <c r="M7" s="18" t="s">
-        <v>2407</v>
+        <v>2406</v>
       </c>
     </row>
     <row r="8" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
+        <v>2409</v>
+      </c>
+      <c r="G8" t="s">
         <v>2410</v>
-      </c>
-      <c r="G8" t="s">
-        <v>2411</v>
       </c>
       <c r="H8" s="18" t="s">
         <v>824</v>
       </c>
       <c r="K8" t="s">
-        <v>2412</v>
+        <v>2411</v>
       </c>
     </row>
     <row r="9" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -17452,7 +17645,7 @@
         <v>17</v>
       </c>
       <c r="D9" t="s">
-        <v>2413</v>
+        <v>2412</v>
       </c>
       <c r="E9" s="18">
         <v>25</v>
@@ -17461,32 +17654,32 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="G9" s="29" t="s">
-        <v>2414</v>
+        <v>2413</v>
       </c>
       <c r="H9" t="s">
         <v>824</v>
       </c>
       <c r="I9" t="s">
+        <v>2414</v>
+      </c>
+      <c r="J9" t="s">
         <v>2415</v>
       </c>
-      <c r="J9" t="s">
+      <c r="K9" t="s">
         <v>2416</v>
-      </c>
-      <c r="K9" t="s">
-        <v>2417</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
+        <v>2417</v>
+      </c>
+      <c r="K10" t="s">
         <v>2418</v>
-      </c>
-      <c r="K10" t="s">
-        <v>2419</v>
       </c>
     </row>
     <row r="11" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D11" t="s">
-        <v>2420</v>
+        <v>2419</v>
       </c>
       <c r="E11" s="18">
         <v>10</v>
@@ -17495,13 +17688,13 @@
         <v>4.55</v>
       </c>
       <c r="G11" s="29" t="s">
-        <v>2421</v>
+        <v>2420</v>
       </c>
       <c r="H11" s="18" t="s">
         <v>824</v>
       </c>
       <c r="I11" t="s">
-        <v>2422</v>
+        <v>2421</v>
       </c>
       <c r="J11" s="14">
         <v>112443</v>
@@ -17512,7 +17705,7 @@
         <v>17</v>
       </c>
       <c r="D12" t="s">
-        <v>2420</v>
+        <v>2419</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -17521,38 +17714,38 @@
         <v>18.38</v>
       </c>
       <c r="G12" s="29" t="s">
-        <v>2423</v>
+        <v>2422</v>
       </c>
       <c r="H12" s="18" t="s">
         <v>824</v>
       </c>
       <c r="I12" t="s">
+        <v>2423</v>
+      </c>
+      <c r="J12" t="s">
         <v>2424</v>
-      </c>
-      <c r="J12" t="s">
-        <v>2425</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.35">
       <c r="B14" t="s">
-        <v>2426</v>
+        <v>2425</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.35">
       <c r="C15" t="s">
-        <v>2427</v>
+        <v>2426</v>
       </c>
       <c r="F15">
         <f>SUMPRODUCT(E16:E18,F16:F18)</f>
         <v>2868</v>
       </c>
       <c r="G15" s="29" t="s">
-        <v>2428</v>
+        <v>2427</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.35">
       <c r="D16" t="s">
-        <v>2429</v>
+        <v>2428</v>
       </c>
       <c r="E16">
         <v>1</v>
@@ -17561,18 +17754,18 @@
         <v>2380</v>
       </c>
       <c r="G16" s="29" t="s">
+        <v>2429</v>
+      </c>
+      <c r="H16" t="s">
         <v>2430</v>
       </c>
-      <c r="H16" t="s">
+      <c r="I16" t="s">
         <v>2431</v>
-      </c>
-      <c r="I16" t="s">
-        <v>2432</v>
       </c>
     </row>
     <row r="17" spans="2:11" x14ac:dyDescent="0.35">
       <c r="D17" t="s">
-        <v>2433</v>
+        <v>2432</v>
       </c>
       <c r="E17">
         <v>1</v>
@@ -17581,13 +17774,13 @@
         <v>340</v>
       </c>
       <c r="H17" t="s">
-        <v>2431</v>
+        <v>2430</v>
       </c>
       <c r="I17" t="s">
+        <v>2433</v>
+      </c>
+      <c r="K17" t="s">
         <v>2434</v>
-      </c>
-      <c r="K17" t="s">
-        <v>2435</v>
       </c>
     </row>
     <row r="18" spans="2:11" x14ac:dyDescent="0.35">
@@ -17595,7 +17788,7 @@
         <v>17</v>
       </c>
       <c r="D18" t="s">
-        <v>2436</v>
+        <v>2435</v>
       </c>
       <c r="E18">
         <v>1</v>
@@ -17604,18 +17797,18 @@
         <v>148</v>
       </c>
       <c r="H18" t="s">
-        <v>2431</v>
+        <v>2430</v>
       </c>
       <c r="I18" t="s">
-        <v>2437</v>
+        <v>2436</v>
       </c>
       <c r="K18" t="s">
-        <v>2435</v>
+        <v>2434</v>
       </c>
     </row>
     <row r="19" spans="2:11" x14ac:dyDescent="0.35">
       <c r="D19" t="s">
-        <v>2549</v>
+        <v>2548</v>
       </c>
       <c r="E19">
         <v>1</v>
@@ -17623,7 +17816,7 @@
     </row>
     <row r="28" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B28" t="s">
-        <v>2438</v>
+        <v>2437</v>
       </c>
     </row>
     <row r="29" spans="2:11" x14ac:dyDescent="0.35">
@@ -18019,7 +18212,7 @@
     </row>
     <row r="18" spans="3:15" x14ac:dyDescent="0.35">
       <c r="E18" t="s">
-        <v>2603</v>
+        <v>2602</v>
       </c>
       <c r="F18">
         <v>1</v>
@@ -18028,18 +18221,18 @@
         <v>10.06</v>
       </c>
       <c r="H18" s="29" t="s">
-        <v>2604</v>
+        <v>2603</v>
       </c>
       <c r="I18" s="30" t="s">
         <v>67</v>
       </c>
       <c r="J18" s="31" t="s">
-        <v>2599</v>
+        <v>2598</v>
       </c>
     </row>
     <row r="19" spans="3:15" x14ac:dyDescent="0.35">
       <c r="E19" t="s">
-        <v>2600</v>
+        <v>2599</v>
       </c>
       <c r="F19">
         <v>1</v>
@@ -18048,19 +18241,19 @@
         <v>10.06</v>
       </c>
       <c r="H19" s="29" t="s">
-        <v>2602</v>
+        <v>2601</v>
       </c>
       <c r="I19" s="30" t="s">
         <v>67</v>
       </c>
       <c r="J19" s="31" t="s">
-        <v>2601</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="20" spans="3:15" x14ac:dyDescent="0.35">
       <c r="C20"/>
       <c r="E20" t="s">
-        <v>2606</v>
+        <v>2605</v>
       </c>
       <c r="F20">
         <v>1</v>
@@ -18069,18 +18262,18 @@
         <v>8.77</v>
       </c>
       <c r="H20" s="29" t="s">
-        <v>2607</v>
+        <v>2606</v>
       </c>
       <c r="I20" s="30" t="s">
         <v>67</v>
       </c>
       <c r="J20" t="s">
-        <v>2605</v>
+        <v>2604</v>
       </c>
     </row>
     <row r="21" spans="3:15" x14ac:dyDescent="0.35">
       <c r="E21" t="s">
-        <v>2545</v>
+        <v>2544</v>
       </c>
       <c r="F21">
         <v>5</v>
@@ -18089,13 +18282,13 @@
         <v>41.4</v>
       </c>
       <c r="H21" s="29" t="s">
-        <v>2544</v>
+        <v>2543</v>
       </c>
       <c r="I21" t="s">
         <v>67</v>
       </c>
       <c r="J21" t="s">
-        <v>2543</v>
+        <v>2542</v>
       </c>
     </row>
     <row r="22" spans="3:15" x14ac:dyDescent="0.35">
@@ -19761,7 +19954,7 @@
     </row>
     <row r="104" spans="3:11" x14ac:dyDescent="0.35">
       <c r="E104" t="s">
-        <v>2519</v>
+        <v>2518</v>
       </c>
       <c r="F104">
         <v>1</v>
@@ -19770,7 +19963,7 @@
         <v>21.86</v>
       </c>
       <c r="H104" s="29" t="s">
-        <v>2520</v>
+        <v>2519</v>
       </c>
       <c r="I104" t="s">
         <v>67</v>
@@ -20316,7 +20509,7 @@
     </row>
     <row r="135" spans="5:15" x14ac:dyDescent="0.35">
       <c r="E135" t="s">
-        <v>2611</v>
+        <v>2610</v>
       </c>
       <c r="F135">
         <v>1</v>
@@ -20325,19 +20518,19 @@
         <v>37.869999999999997</v>
       </c>
       <c r="H135" s="29" t="s">
-        <v>2610</v>
+        <v>2609</v>
       </c>
       <c r="I135" t="s">
         <v>67</v>
       </c>
       <c r="J135" s="31" t="s">
-        <v>2609</v>
+        <v>2608</v>
       </c>
       <c r="K135" s="29"/>
     </row>
     <row r="136" spans="5:15" x14ac:dyDescent="0.35">
       <c r="E136" t="s">
-        <v>2612</v>
+        <v>2611</v>
       </c>
       <c r="F136">
         <v>1</v>
@@ -20346,13 +20539,13 @@
         <v>40.04</v>
       </c>
       <c r="H136" s="29" t="s">
+        <v>2612</v>
+      </c>
+      <c r="I136" t="s">
+        <v>67</v>
+      </c>
+      <c r="J136" s="31" t="s">
         <v>2613</v>
-      </c>
-      <c r="I136" t="s">
-        <v>67</v>
-      </c>
-      <c r="J136" s="31" t="s">
-        <v>2614</v>
       </c>
       <c r="K136" s="29"/>
     </row>
@@ -20647,7 +20840,7 @@
     </row>
     <row r="150" spans="1:15" x14ac:dyDescent="0.35">
       <c r="E150" t="s">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="F150">
         <v>1</v>
@@ -20656,13 +20849,13 @@
         <v>44.13</v>
       </c>
       <c r="H150" s="29" t="s">
-        <v>2541</v>
+        <v>2540</v>
       </c>
       <c r="I150" t="s">
         <v>67</v>
       </c>
       <c r="J150" s="31" t="s">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="K150" s="29"/>
     </row>
@@ -22244,7 +22437,7 @@
         <v>718</v>
       </c>
       <c r="J232" s="31" t="s">
-        <v>2540</v>
+        <v>2539</v>
       </c>
       <c r="O232" t="s">
         <v>719</v>
@@ -23362,7 +23555,7 @@
     <row r="312" spans="1:15" x14ac:dyDescent="0.35">
       <c r="C312"/>
       <c r="E312" t="s">
-        <v>2538</v>
+        <v>2537</v>
       </c>
       <c r="H312" s="29" t="s">
         <v>1739</v>
@@ -26509,7 +26702,7 @@
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.35">
       <c r="D24" t="s">
-        <v>2615</v>
+        <v>2614</v>
       </c>
       <c r="G24" s="29"/>
       <c r="K24" s="31"/>
@@ -26518,7 +26711,7 @@
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.35">
       <c r="F25" t="s">
-        <v>2616</v>
+        <v>2615</v>
       </c>
       <c r="I25" s="30">
         <f>SUMPRODUCT(H26:H28,I26:I28)</f>
@@ -32223,7 +32416,7 @@
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.35">
       <c r="C3" t="s">
-        <v>2511</v>
+        <v>2510</v>
       </c>
       <c r="F3" s="30">
         <f>SUMPRODUCT(E4:E5,F4:F5)</f>
@@ -32276,7 +32469,7 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.35">
       <c r="C6" t="s">
-        <v>2512</v>
+        <v>2511</v>
       </c>
       <c r="F6" s="6">
         <f>SUMPRODUCT(E7:E9,F7:F9)</f>
@@ -32348,7 +32541,7 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B10" t="s">
-        <v>2514</v>
+        <v>2513</v>
       </c>
       <c r="O10" s="21"/>
     </row>
@@ -32372,7 +32565,7 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.35">
       <c r="C12" t="s">
-        <v>2513</v>
+        <v>2512</v>
       </c>
       <c r="F12" s="6">
         <f>SUMPRODUCT(E13:E17,F13:F17)</f>
@@ -34935,7 +35128,7 @@
     </row>
     <row r="139" spans="1:14" x14ac:dyDescent="0.35">
       <c r="D139" t="s">
-        <v>2519</v>
+        <v>2518</v>
       </c>
       <c r="E139">
         <v>1</v>
@@ -34944,7 +35137,7 @@
         <v>21.86</v>
       </c>
       <c r="G139" s="29" t="s">
-        <v>2520</v>
+        <v>2519</v>
       </c>
       <c r="H139" t="s">
         <v>67</v>
@@ -35833,14 +36026,14 @@
     </row>
     <row r="189" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B189" t="s">
-        <v>2622</v>
+        <v>2621</v>
       </c>
       <c r="C189" s="21"/>
       <c r="F189" s="6"/>
     </row>
     <row r="190" spans="2:16" x14ac:dyDescent="0.35">
       <c r="C190" t="s">
-        <v>2621</v>
+        <v>2620</v>
       </c>
       <c r="F190" s="6"/>
       <c r="P190" s="6"/>
@@ -36114,7 +36307,7 @@
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>2458</v>
+        <v>2457</v>
       </c>
       <c r="N2" t="s">
         <v>1314</v>
@@ -36122,7 +36315,7 @@
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.35">
       <c r="D3" t="s">
-        <v>2515</v>
+        <v>2514</v>
       </c>
       <c r="G3" s="6">
         <f>SUMPRODUCT(F4:F5,G4:G5)</f>
@@ -36177,7 +36370,7 @@
         <v>254</v>
       </c>
       <c r="H5" s="29" t="s">
-        <v>2466</v>
+        <v>2465</v>
       </c>
       <c r="I5" t="s">
         <v>709</v>
@@ -36198,7 +36391,7 @@
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.35">
       <c r="D6" t="s">
-        <v>2506</v>
+        <v>2505</v>
       </c>
       <c r="G6" s="6">
         <f>SUMPRODUCT(F7:F8,G7:G8)</f>
@@ -36290,7 +36483,7 @@
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.35">
       <c r="D9" t="s">
-        <v>2504</v>
+        <v>2503</v>
       </c>
       <c r="G9" s="6">
         <f>SUMPRODUCT(F10:F12,G10:G12)</f>
@@ -36298,7 +36491,7 @@
       </c>
       <c r="H9" s="29"/>
       <c r="K9" s="29" t="s">
-        <v>2440</v>
+        <v>2439</v>
       </c>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.35">
@@ -36372,7 +36565,7 @@
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.35">
       <c r="D13" t="s">
-        <v>2505</v>
+        <v>2504</v>
       </c>
       <c r="G13" s="6">
         <f>SUMPRODUCT(F15:F17,G15:G17)</f>
@@ -36450,7 +36643,7 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.35">
       <c r="C19" t="s">
-        <v>2477</v>
+        <v>2476</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.35">
@@ -36516,13 +36709,13 @@
         <v>17</v>
       </c>
       <c r="E23" t="s">
+        <v>2477</v>
+      </c>
+      <c r="F23">
+        <v>1</v>
+      </c>
+      <c r="H23" s="29" t="s">
         <v>2478</v>
-      </c>
-      <c r="F23">
-        <v>1</v>
-      </c>
-      <c r="H23" s="29" t="s">
-        <v>2479</v>
       </c>
       <c r="I23" t="s">
         <v>1225</v>
@@ -36531,7 +36724,7 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.35">
       <c r="C24" t="s">
-        <v>2445</v>
+        <v>2444</v>
       </c>
       <c r="N24" t="s">
         <v>9</v>
@@ -36559,7 +36752,7 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.35">
       <c r="E26" t="s">
-        <v>2446</v>
+        <v>2445</v>
       </c>
       <c r="F26">
         <v>1</v>
@@ -36568,7 +36761,7 @@
         <v>140</v>
       </c>
       <c r="H26" s="29" t="s">
-        <v>2447</v>
+        <v>2446</v>
       </c>
       <c r="I26" t="s">
         <v>844</v>
@@ -36577,7 +36770,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.35">
       <c r="E27" t="s">
-        <v>2449</v>
+        <v>2448</v>
       </c>
       <c r="F27">
         <v>1</v>
@@ -36590,13 +36783,13 @@
         <v>17</v>
       </c>
       <c r="E28" t="s">
+        <v>2479</v>
+      </c>
+      <c r="F28">
+        <v>1</v>
+      </c>
+      <c r="H28" s="29" t="s">
         <v>2480</v>
-      </c>
-      <c r="F28">
-        <v>1</v>
-      </c>
-      <c r="H28" s="29" t="s">
-        <v>2481</v>
       </c>
       <c r="I28" t="s">
         <v>1225</v>
@@ -36605,14 +36798,14 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.35">
       <c r="C29" t="s">
-        <v>2451</v>
+        <v>2450</v>
       </c>
       <c r="H29" s="29"/>
       <c r="K29" s="29"/>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.35">
       <c r="E30" t="s">
-        <v>2450</v>
+        <v>2449</v>
       </c>
       <c r="F30">
         <v>1</v>
@@ -36626,7 +36819,7 @@
         <v>17</v>
       </c>
       <c r="E31" t="s">
-        <v>2482</v>
+        <v>2481</v>
       </c>
       <c r="F31">
         <v>1</v>
@@ -36637,7 +36830,7 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.35">
       <c r="D32" t="s">
-        <v>2448</v>
+        <v>2447</v>
       </c>
       <c r="G32" s="6">
         <f>SUMPRODUCT(F33:F36,G33:G36)</f>
@@ -36775,7 +36968,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.35">
       <c r="D37" t="s">
-        <v>2444</v>
+        <v>2443</v>
       </c>
       <c r="G37" s="6">
         <f>SUMPRODUCT(F38:F41,G38:G41)</f>
@@ -36939,13 +37132,13 @@
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>2459</v>
+        <v>2458</v>
       </c>
       <c r="H42" s="29"/>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.35">
       <c r="D43" t="s">
-        <v>2495</v>
+        <v>2494</v>
       </c>
       <c r="G43">
         <f>SUMPRODUCT(F44:F45,G44:G45)</f>
@@ -37035,7 +37228,7 @@
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.35">
       <c r="D46" t="s">
-        <v>2496</v>
+        <v>2495</v>
       </c>
       <c r="G46" s="6">
         <f>SUMPRODUCT(F47:F48,G47:G48)</f>
@@ -37138,16 +37331,16 @@
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>2467</v>
+        <v>2466</v>
       </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.35">
       <c r="B51" t="s">
-        <v>2468</v>
+        <v>2467</v>
       </c>
       <c r="H51" s="29"/>
       <c r="N51" t="s">
-        <v>2469</v>
+        <v>2468</v>
       </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.35">
@@ -37156,7 +37349,7 @@
       </c>
       <c r="H52" s="29"/>
       <c r="N52" t="s">
-        <v>2470</v>
+        <v>2469</v>
       </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.35">
@@ -37228,7 +37421,7 @@
       </c>
       <c r="H56" s="29"/>
       <c r="N56" t="s">
-        <v>2471</v>
+        <v>2470</v>
       </c>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.35">
@@ -37242,7 +37435,7 @@
         <v>405</v>
       </c>
       <c r="H57" s="29" t="s">
-        <v>2638</v>
+        <v>2637</v>
       </c>
       <c r="I57" t="s">
         <v>682</v>
@@ -37279,7 +37472,7 @@
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.35">
       <c r="D59" t="s">
-        <v>2510</v>
+        <v>2509</v>
       </c>
       <c r="G59" s="6">
         <f>SUMPRODUCT(F60:F61,G60:G61)</f>
@@ -37369,7 +37562,7 @@
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.35">
       <c r="C62" t="s">
-        <v>2473</v>
+        <v>2472</v>
       </c>
       <c r="H62" s="29"/>
     </row>
@@ -37398,7 +37591,7 @@
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.35">
       <c r="C64" t="s">
-        <v>2472</v>
+        <v>2471</v>
       </c>
       <c r="H64" s="29"/>
     </row>
@@ -37422,7 +37615,7 @@
         <v>1397</v>
       </c>
       <c r="N65" t="s">
-        <v>2475</v>
+        <v>2474</v>
       </c>
     </row>
     <row r="66" spans="3:14" x14ac:dyDescent="0.35">
@@ -37453,7 +37646,7 @@
     </row>
     <row r="67" spans="3:14" x14ac:dyDescent="0.35">
       <c r="D67" t="s">
-        <v>2474</v>
+        <v>2473</v>
       </c>
       <c r="G67" s="6">
         <f>SUMPRODUCT(F68:F70,G68:G70)</f>
@@ -37609,7 +37802,7 @@
     </row>
     <row r="73" spans="3:14" x14ac:dyDescent="0.35">
       <c r="E73" t="s">
-        <v>2485</v>
+        <v>2484</v>
       </c>
       <c r="F73">
         <v>1</v>
@@ -37735,7 +37928,7 @@
     </row>
     <row r="80" spans="3:14" x14ac:dyDescent="0.35">
       <c r="D80" t="s">
-        <v>2488</v>
+        <v>2487</v>
       </c>
       <c r="G80" s="6">
         <f>SUMPRODUCT(F81:F82,G81:G82)</f>
@@ -37822,7 +38015,7 @@
     </row>
     <row r="83" spans="1:14" x14ac:dyDescent="0.35">
       <c r="E83" t="s">
-        <v>2489</v>
+        <v>2488</v>
       </c>
       <c r="F83">
         <v>1</v>
@@ -37837,7 +38030,7 @@
         <v>17</v>
       </c>
       <c r="E84" t="s">
-        <v>2492</v>
+        <v>2491</v>
       </c>
       <c r="F84">
         <v>1</v>
@@ -37849,19 +38042,19 @@
     </row>
     <row r="85" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>2500</v>
+        <v>2499</v>
       </c>
       <c r="J85"/>
       <c r="K85"/>
       <c r="L85"/>
       <c r="M85"/>
       <c r="N85" t="s">
-        <v>2503</v>
+        <v>2502</v>
       </c>
     </row>
     <row r="86" spans="1:14" x14ac:dyDescent="0.35">
       <c r="B86" t="s">
-        <v>2501</v>
+        <v>2500</v>
       </c>
       <c r="J86"/>
       <c r="K86"/>
@@ -37870,7 +38063,7 @@
     </row>
     <row r="87" spans="1:14" x14ac:dyDescent="0.35">
       <c r="E87" t="s">
-        <v>2441</v>
+        <v>2440</v>
       </c>
       <c r="F87">
         <v>1</v>
@@ -37910,7 +38103,7 @@
     </row>
     <row r="89" spans="1:14" x14ac:dyDescent="0.35">
       <c r="D89" t="s">
-        <v>2502</v>
+        <v>2501</v>
       </c>
       <c r="G89" s="6">
         <f>SUMPRODUCT(F90:F91,G90:G91)</f>
@@ -37971,7 +38164,7 @@
     </row>
     <row r="93" spans="1:14" x14ac:dyDescent="0.35">
       <c r="C93" t="s">
-        <v>2483</v>
+        <v>2482</v>
       </c>
     </row>
     <row r="94" spans="1:14" x14ac:dyDescent="0.35">
@@ -37999,7 +38192,7 @@
     </row>
     <row r="95" spans="1:14" x14ac:dyDescent="0.35">
       <c r="D95" t="s">
-        <v>2484</v>
+        <v>2483</v>
       </c>
       <c r="G95" s="6">
         <f>SUMPRODUCT(F96:F97,G96:G97)</f>
@@ -38054,7 +38247,7 @@
     </row>
     <row r="98" spans="1:14" x14ac:dyDescent="0.35">
       <c r="D98" t="s">
-        <v>2491</v>
+        <v>2490</v>
       </c>
       <c r="H98" s="29"/>
     </row>
@@ -38087,7 +38280,7 @@
     </row>
     <row r="103" spans="1:14" x14ac:dyDescent="0.35">
       <c r="D103" t="s">
-        <v>2497</v>
+        <v>2496</v>
       </c>
       <c r="G103" s="6">
         <f>SUMPRODUCT(F104:F107,G104:G107)</f>
@@ -38252,7 +38445,7 @@
     </row>
     <row r="108" spans="1:14" x14ac:dyDescent="0.35">
       <c r="D108" t="s">
-        <v>2498</v>
+        <v>2497</v>
       </c>
       <c r="G108" s="6">
         <f>SUMPRODUCT(F109:F110,G109:G110)</f>
@@ -38339,7 +38532,7 @@
     </row>
     <row r="111" spans="1:14" x14ac:dyDescent="0.35">
       <c r="D111" t="s">
-        <v>2499</v>
+        <v>2498</v>
       </c>
       <c r="G111" s="6">
         <f>SUMPRODUCT(F112:F118,G112:G118)</f>
@@ -38347,7 +38540,7 @@
       </c>
       <c r="H111" s="29"/>
       <c r="K111" s="29" t="s">
-        <v>2443</v>
+        <v>2442</v>
       </c>
     </row>
     <row r="112" spans="1:14" x14ac:dyDescent="0.35">
@@ -38389,7 +38582,7 @@
     </row>
     <row r="113" spans="3:13" x14ac:dyDescent="0.35">
       <c r="E113" t="s">
-        <v>2442</v>
+        <v>2441</v>
       </c>
       <c r="F113">
         <v>1</v>
@@ -38592,12 +38785,12 @@
     </row>
     <row r="119" spans="3:13" x14ac:dyDescent="0.35">
       <c r="C119" t="s">
-        <v>2494</v>
+        <v>2493</v>
       </c>
     </row>
     <row r="120" spans="3:13" x14ac:dyDescent="0.35">
       <c r="D120" t="s">
-        <v>2507</v>
+        <v>2506</v>
       </c>
       <c r="G120" s="6">
         <f>SUMPRODUCT(F121:F125,G121:G125)</f>
@@ -38794,7 +38987,7 @@
     </row>
     <row r="126" spans="3:13" x14ac:dyDescent="0.35">
       <c r="D126" t="s">
-        <v>2508</v>
+        <v>2507</v>
       </c>
       <c r="G126" s="6">
         <f>SUMPRODUCT(F127:F131,G127:G131)</f>
@@ -38991,7 +39184,7 @@
     </row>
     <row r="132" spans="1:14" x14ac:dyDescent="0.35">
       <c r="D132" t="s">
-        <v>2509</v>
+        <v>2508</v>
       </c>
       <c r="G132" s="6">
         <f>SUMPRODUCT(F133:F137,G133:G137)</f>
@@ -39191,7 +39384,7 @@
         <v>34.549999999999997</v>
       </c>
       <c r="K140" s="29" t="s">
-        <v>2439</v>
+        <v>2438</v>
       </c>
       <c r="N140" t="s">
         <v>1418</v>
@@ -39434,13 +39627,13 @@
     </row>
     <row r="148" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B148" t="s">
-        <v>2476</v>
+        <v>2475</v>
       </c>
       <c r="H148" s="29"/>
     </row>
     <row r="149" spans="2:14" x14ac:dyDescent="0.35">
       <c r="D149" t="s">
-        <v>2490</v>
+        <v>2489</v>
       </c>
       <c r="G149" s="6">
         <f>SUMPRODUCT(F150:F156,G150:G156)</f>
@@ -39524,7 +39717,7 @@
     </row>
     <row r="152" spans="2:14" x14ac:dyDescent="0.35">
       <c r="C152" t="s">
-        <v>2486</v>
+        <v>2485</v>
       </c>
       <c r="E152" t="str">
         <f>$E$94</f>
@@ -39670,7 +39863,7 @@
     </row>
     <row r="157" spans="2:14" x14ac:dyDescent="0.35">
       <c r="D157" t="s">
-        <v>2487</v>
+        <v>2486</v>
       </c>
       <c r="G157" s="6">
         <f>SUMPRODUCT(F158:F162,G158:G162)</f>
@@ -39857,7 +40050,7 @@
     </row>
     <row r="166" spans="1:21" x14ac:dyDescent="0.35">
       <c r="D166" s="31" t="s">
-        <v>2452</v>
+        <v>2451</v>
       </c>
       <c r="G166" s="6">
         <f>SUMPRODUCT(F167:F169,G167:G169)</f>
@@ -39965,7 +40158,7 @@
     </row>
     <row r="170" spans="1:21" x14ac:dyDescent="0.35">
       <c r="D170" s="31" t="s">
-        <v>2455</v>
+        <v>2454</v>
       </c>
       <c r="G170" s="6">
         <f>SUMPRODUCT(F171:F172,G171:G172)</f>
@@ -40100,7 +40293,7 @@
     </row>
     <row r="177" spans="2:21" x14ac:dyDescent="0.35">
       <c r="E177" t="s">
-        <v>2456</v>
+        <v>2455</v>
       </c>
       <c r="F177">
         <v>1</v>
@@ -40112,7 +40305,7 @@
         <v>17</v>
       </c>
       <c r="E178" t="s">
-        <v>2453</v>
+        <v>2452</v>
       </c>
       <c r="F178">
         <v>1</v>
@@ -40167,7 +40360,7 @@
     </row>
     <row r="182" spans="2:21" x14ac:dyDescent="0.35">
       <c r="E182" t="s">
-        <v>2457</v>
+        <v>2456</v>
       </c>
       <c r="F182">
         <v>1</v>
@@ -40182,7 +40375,7 @@
         <v>17</v>
       </c>
       <c r="E183" t="s">
-        <v>2454</v>
+        <v>2453</v>
       </c>
       <c r="F183">
         <v>1</v>
@@ -40436,7 +40629,7 @@
     </row>
     <row r="198" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A198" s="31" t="s">
-        <v>2521</v>
+        <v>2520</v>
       </c>
       <c r="N198" t="s">
         <v>1384</v>
@@ -40444,12 +40637,12 @@
     </row>
     <row r="199" spans="1:21" x14ac:dyDescent="0.35">
       <c r="B199" s="31" t="s">
-        <v>2522</v>
+        <v>2521</v>
       </c>
     </row>
     <row r="200" spans="1:21" x14ac:dyDescent="0.35">
       <c r="C200" s="31" t="s">
-        <v>2523</v>
+        <v>2522</v>
       </c>
     </row>
     <row r="201" spans="1:21" x14ac:dyDescent="0.35">
@@ -40498,7 +40691,7 @@
         <v>17</v>
       </c>
       <c r="E202" t="s">
-        <v>2524</v>
+        <v>2523</v>
       </c>
       <c r="F202">
         <v>1</v>
@@ -40507,13 +40700,13 @@
         <v>1225</v>
       </c>
       <c r="K202" s="29" t="s">
-        <v>2525</v>
+        <v>2524</v>
       </c>
     </row>
     <row r="203" spans="1:21" x14ac:dyDescent="0.35">
       <c r="C203" s="31"/>
       <c r="D203" s="31" t="s">
-        <v>2547</v>
+        <v>2546</v>
       </c>
       <c r="G203" s="6">
         <f>SUMPRODUCT(F204:F205,G204:G205)</f>
@@ -40610,14 +40803,14 @@
     </row>
     <row r="206" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
-        <v>2526</v>
+        <v>2525</v>
       </c>
       <c r="C206" s="31"/>
     </row>
     <row r="207" spans="1:21" x14ac:dyDescent="0.35">
       <c r="C207" s="31"/>
       <c r="D207" t="s">
-        <v>2527</v>
+        <v>2526</v>
       </c>
       <c r="G207" s="6">
         <f>SUMPRODUCT(F208,G208)</f>
@@ -40645,7 +40838,7 @@
     </row>
     <row r="209" spans="1:14" x14ac:dyDescent="0.35">
       <c r="D209" t="s">
-        <v>2528</v>
+        <v>2527</v>
       </c>
       <c r="G209" s="6">
         <f>SUMPRODUCT(G210:G212)</f>
@@ -40728,7 +40921,7 @@
     </row>
     <row r="213" spans="1:14" x14ac:dyDescent="0.35">
       <c r="D213" t="s">
-        <v>2529</v>
+        <v>2528</v>
       </c>
       <c r="H213" s="29"/>
     </row>
@@ -40743,7 +40936,7 @@
     </row>
     <row r="215" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
-        <v>2493</v>
+        <v>2492</v>
       </c>
       <c r="H215" s="29"/>
       <c r="N215" t="s">
@@ -40752,13 +40945,13 @@
     </row>
     <row r="216" spans="1:14" x14ac:dyDescent="0.35">
       <c r="B216" t="s">
-        <v>2542</v>
+        <v>2541</v>
       </c>
       <c r="H216" s="29"/>
     </row>
     <row r="217" spans="1:14" x14ac:dyDescent="0.35">
       <c r="D217" t="s">
-        <v>2546</v>
+        <v>2545</v>
       </c>
       <c r="G217" s="6">
         <f>SUMPRODUCT(F218:F223,G218:G223)</f>
@@ -42869,7 +43062,7 @@
       </c>
       <c r="H112" s="29"/>
       <c r="K112" t="s">
-        <v>2608</v>
+        <v>2607</v>
       </c>
     </row>
     <row r="113" spans="4:14" x14ac:dyDescent="0.35">
@@ -45075,7 +45268,7 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.35">
       <c r="F5" t="s">
-        <v>2556</v>
+        <v>2555</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -45098,7 +45291,7 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.35">
       <c r="E6" t="s">
-        <v>2566</v>
+        <v>2565</v>
       </c>
       <c r="H6" s="30">
         <f>SUMPRODUCT(G7:G8,H7:H8)</f>
@@ -45150,7 +45343,7 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.35">
       <c r="E9" t="s">
-        <v>2565</v>
+        <v>2564</v>
       </c>
       <c r="H9" s="30">
         <f>SUMPRODUCT(G10:G11,H10:H11)</f>
@@ -45203,7 +45396,7 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.35">
       <c r="C12" t="s">
-        <v>2567</v>
+        <v>2566</v>
       </c>
       <c r="I12" s="29"/>
     </row>
@@ -45259,7 +45452,7 @@
         <v>17</v>
       </c>
       <c r="F15" t="s">
-        <v>2568</v>
+        <v>2567</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -45268,13 +45461,13 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.35">
       <c r="D16" t="s">
-        <v>2539</v>
+        <v>2538</v>
       </c>
       <c r="I16" s="29"/>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.35">
       <c r="E17" t="s">
-        <v>2558</v>
+        <v>2557</v>
       </c>
       <c r="H17" s="30">
         <f>SUMPRODUCT(G18:G19,H18:H19)</f>
@@ -45304,7 +45497,7 @@
         <v>17</v>
       </c>
       <c r="F19" t="s">
-        <v>2557</v>
+        <v>2556</v>
       </c>
       <c r="G19">
         <v>1</v>
@@ -45313,7 +45506,7 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.35">
       <c r="E20" t="s">
-        <v>2569</v>
+        <v>2568</v>
       </c>
       <c r="H20" s="30">
         <f>SUMPRODUCT(G21:G22,H21:H22)</f>
@@ -45352,7 +45545,7 @@
         <v>17</v>
       </c>
       <c r="F22" t="s">
-        <v>2570</v>
+        <v>2569</v>
       </c>
       <c r="G22">
         <v>1</v>
@@ -45428,12 +45621,12 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B28" t="s">
-        <v>2562</v>
+        <v>2561</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.35">
       <c r="F29" t="s">
-        <v>2594</v>
+        <v>2593</v>
       </c>
       <c r="G29">
         <v>1</v>
@@ -45456,10 +45649,10 @@
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.35">
       <c r="F30" t="s">
-        <v>2598</v>
+        <v>2597</v>
       </c>
       <c r="I30" s="29" t="s">
-        <v>2597</v>
+        <v>2596</v>
       </c>
       <c r="J30" t="s">
         <v>718</v>
@@ -45467,7 +45660,7 @@
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.35">
       <c r="F31" t="s">
-        <v>2593</v>
+        <v>2592</v>
       </c>
       <c r="G31">
         <v>1</v>
@@ -45476,13 +45669,13 @@
         <v>80.62</v>
       </c>
       <c r="I31" s="29" t="s">
+        <v>2590</v>
+      </c>
+      <c r="J31" t="s">
+        <v>67</v>
+      </c>
+      <c r="K31" t="s">
         <v>2591</v>
-      </c>
-      <c r="J31" t="s">
-        <v>67</v>
-      </c>
-      <c r="K31" t="s">
-        <v>2592</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.35">
@@ -45490,10 +45683,10 @@
         <v>17</v>
       </c>
       <c r="F32" t="s">
+        <v>2594</v>
+      </c>
+      <c r="I32" s="29" t="s">
         <v>2595</v>
-      </c>
-      <c r="I32" s="29" t="s">
-        <v>2596</v>
       </c>
       <c r="J32" t="s">
         <v>67</v>
@@ -45501,7 +45694,7 @@
     </row>
     <row r="33" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B33" t="s">
-        <v>2563</v>
+        <v>2562</v>
       </c>
       <c r="I33" s="29"/>
     </row>
@@ -45536,7 +45729,7 @@
         <v>1107</v>
       </c>
       <c r="I35" s="29" t="s">
-        <v>2559</v>
+        <v>2558</v>
       </c>
       <c r="J35" t="s">
         <v>718</v>
@@ -45553,7 +45746,7 @@
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.35">
       <c r="D37" t="s">
-        <v>2530</v>
+        <v>2529</v>
       </c>
       <c r="I37" s="29"/>
       <c r="K37" s="14"/>
@@ -45563,7 +45756,7 @@
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.35">
       <c r="F38" t="s">
-        <v>2535</v>
+        <v>2534</v>
       </c>
       <c r="G38">
         <v>1</v>
@@ -45572,13 +45765,13 @@
         <v>17.95</v>
       </c>
       <c r="I38" s="29" t="s">
-        <v>2534</v>
+        <v>2533</v>
       </c>
       <c r="J38" t="s">
         <v>824</v>
       </c>
       <c r="K38" t="s">
-        <v>2533</v>
+        <v>2532</v>
       </c>
       <c r="L38" s="14"/>
       <c r="M38" s="14"/>
@@ -45586,10 +45779,10 @@
     </row>
     <row r="39" spans="2:14" x14ac:dyDescent="0.35">
       <c r="F39" t="s">
-        <v>2532</v>
+        <v>2531</v>
       </c>
       <c r="I39" s="29" t="s">
-        <v>2531</v>
+        <v>2530</v>
       </c>
       <c r="J39" t="s">
         <v>824</v>
@@ -45644,7 +45837,7 @@
     </row>
     <row r="42" spans="2:14" x14ac:dyDescent="0.35">
       <c r="D42" t="s">
-        <v>2536</v>
+        <v>2535</v>
       </c>
       <c r="I42" s="29"/>
       <c r="K42" s="14"/>
@@ -45677,7 +45870,7 @@
         <v>17</v>
       </c>
       <c r="F44" t="s">
-        <v>2560</v>
+        <v>2559</v>
       </c>
       <c r="G44">
         <v>1</v>
@@ -45692,7 +45885,7 @@
         <v>824</v>
       </c>
       <c r="K44" s="14" t="s">
-        <v>2561</v>
+        <v>2560</v>
       </c>
       <c r="L44" s="14"/>
       <c r="M44" s="14"/>
@@ -45700,7 +45893,7 @@
     </row>
     <row r="45" spans="2:14" x14ac:dyDescent="0.35">
       <c r="C45" t="s">
-        <v>2590</v>
+        <v>2589</v>
       </c>
       <c r="H45"/>
       <c r="I45" s="29"/>
@@ -45950,7 +46143,7 @@
     </row>
     <row r="57" spans="4:14" x14ac:dyDescent="0.35">
       <c r="E57" t="s">
-        <v>2584</v>
+        <v>2583</v>
       </c>
       <c r="H57">
         <f>SUMPRODUCT(G58:G59,H58:H59)</f>
@@ -45990,7 +46183,7 @@
         <v>17</v>
       </c>
       <c r="F59" t="s">
-        <v>2586</v>
+        <v>2585</v>
       </c>
       <c r="G59">
         <v>1</v>
@@ -45999,7 +46192,7 @@
         <v>5.99</v>
       </c>
       <c r="I59" s="29" t="s">
-        <v>2585</v>
+        <v>2584</v>
       </c>
       <c r="J59" t="s">
         <v>900</v>
@@ -46013,7 +46206,7 @@
     </row>
     <row r="60" spans="4:14" x14ac:dyDescent="0.35">
       <c r="E60" t="s">
-        <v>2587</v>
+        <v>2586</v>
       </c>
       <c r="H60">
         <f>SUMPRODUCT(G61:G62,H61:H62)</f>
@@ -46027,7 +46220,7 @@
     </row>
     <row r="61" spans="4:14" x14ac:dyDescent="0.35">
       <c r="F61" t="s">
-        <v>2586</v>
+        <v>2585</v>
       </c>
       <c r="G61">
         <v>1</v>
@@ -46036,7 +46229,7 @@
         <v>5.99</v>
       </c>
       <c r="I61" s="29" t="s">
-        <v>2585</v>
+        <v>2584</v>
       </c>
       <c r="J61" t="s">
         <v>900</v>
@@ -46076,7 +46269,7 @@
     </row>
     <row r="63" spans="4:14" x14ac:dyDescent="0.35">
       <c r="D63" t="s">
-        <v>2579</v>
+        <v>2578</v>
       </c>
       <c r="H63"/>
       <c r="I63" s="29"/>
@@ -46087,7 +46280,7 @@
     </row>
     <row r="64" spans="4:14" x14ac:dyDescent="0.35">
       <c r="F64" t="s">
-        <v>2580</v>
+        <v>2579</v>
       </c>
       <c r="G64">
         <v>1</v>
@@ -46096,13 +46289,13 @@
         <v>45.64</v>
       </c>
       <c r="I64" s="29" t="s">
+        <v>2581</v>
+      </c>
+      <c r="J64" t="s">
         <v>2582</v>
       </c>
-      <c r="J64" t="s">
-        <v>2583</v>
-      </c>
       <c r="K64" s="14" t="s">
-        <v>2581</v>
+        <v>2580</v>
       </c>
       <c r="L64" s="14"/>
       <c r="M64" s="14"/>
@@ -46110,7 +46303,7 @@
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.35">
       <c r="E65" t="s">
-        <v>2588</v>
+        <v>2587</v>
       </c>
       <c r="H65" s="30">
         <f>SUMPRODUCT(G66:G68,H66:H68)</f>
@@ -46244,7 +46437,7 @@
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.35">
       <c r="C69" t="s">
-        <v>2564</v>
+        <v>2563</v>
       </c>
       <c r="H69"/>
       <c r="I69" s="29"/>
@@ -46255,7 +46448,7 @@
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.35">
       <c r="E70" t="s">
-        <v>2571</v>
+        <v>2570</v>
       </c>
       <c r="H70" s="30">
         <f>SUMPRODUCT(G71:G74,H71:H74)</f>
@@ -46403,7 +46596,7 @@
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.35">
       <c r="E75" t="s">
-        <v>2572</v>
+        <v>2571</v>
       </c>
       <c r="H75" s="30">
         <f>SUMPRODUCT(G76:G78,H76:H78)</f>
@@ -46484,7 +46677,7 @@
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>2578</v>
+        <v>2577</v>
       </c>
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.35">
@@ -46611,7 +46804,7 @@
     </row>
     <row r="90" spans="3:15" x14ac:dyDescent="0.35">
       <c r="E90" t="s">
-        <v>2577</v>
+        <v>2576</v>
       </c>
       <c r="H90" s="30">
         <f>SUMPRODUCT(G91:G93,H91:H93)</f>
@@ -46942,7 +47135,7 @@
     </row>
     <row r="117" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B117" t="s">
-        <v>2576</v>
+        <v>2575</v>
       </c>
       <c r="I117" s="29"/>
     </row>
@@ -46954,7 +47147,7 @@
         <v>17</v>
       </c>
       <c r="F118" s="25" t="s">
-        <v>2573</v>
+        <v>2572</v>
       </c>
       <c r="G118">
         <v>1</v>
@@ -46963,18 +47156,18 @@
         <v>957.67</v>
       </c>
       <c r="I118" s="29" t="s">
+        <v>2573</v>
+      </c>
+      <c r="J118" s="25" t="s">
+        <v>67</v>
+      </c>
+      <c r="K118" s="25" t="s">
         <v>2574</v>
-      </c>
-      <c r="J118" s="25" t="s">
-        <v>67</v>
-      </c>
-      <c r="K118" s="25" t="s">
-        <v>2575</v>
       </c>
     </row>
     <row r="119" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
-        <v>2589</v>
+        <v>2588</v>
       </c>
       <c r="F119" s="25"/>
       <c r="H119"/>
@@ -47487,7 +47680,7 @@
     </row>
     <row r="157" spans="1:15" x14ac:dyDescent="0.35">
       <c r="F157" t="s">
-        <v>2553</v>
+        <v>2552</v>
       </c>
       <c r="G157">
         <v>1</v>
@@ -47501,7 +47694,7 @@
     </row>
     <row r="158" spans="1:15" x14ac:dyDescent="0.35">
       <c r="E158" t="s">
-        <v>2554</v>
+        <v>2553</v>
       </c>
       <c r="H158" s="30">
         <f>SUMPRODUCT(G159:G160,H159:H160)</f>
@@ -47553,7 +47746,7 @@
         <v>17</v>
       </c>
       <c r="F160" t="s">
-        <v>2555</v>
+        <v>2554</v>
       </c>
       <c r="G160">
         <v>1</v>
@@ -47748,7 +47941,7 @@
         <v>1830</v>
       </c>
       <c r="J176" t="s">
-        <v>2537</v>
+        <v>2536</v>
       </c>
     </row>
     <row r="177" spans="4:15" x14ac:dyDescent="0.35">
